--- a/equipment_sequence/manual.xlsx
+++ b/equipment_sequence/manual.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17775" tabRatio="767" firstSheet="1" activeTab="4"/>
+    <workbookView windowWidth="27945" windowHeight="12375" tabRatio="485" firstSheet="1" activeTab="7"/>
   </bookViews>
   <sheets>
     <sheet name="secs指令" sheetId="14" r:id="rId1"/>
@@ -130,7 +130,7 @@
           <t xml:space="preserve">S6F11 W
   &lt;L [3]
     &lt;U1 1 &gt;
-    &lt;U2 1001 &gt;
+    &lt;U2 5001 &gt;
     &lt;L [1]
       &lt;L [2]
         &lt;U4 1 &gt; 
@@ -144,7 +144,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B3" authorId="0">
+    <comment ref="B3" authorId="1">
       <text>
         <r>
           <rPr>
@@ -155,13 +155,37 @@
           <t xml:space="preserve">S6F11 W
   &lt;L [3]
     &lt;U1 1 &gt;
-    &lt;U2 1002 &gt;
+    &lt;U2 5002 &gt;
     &lt;L [1]
       &lt;L [2]
-        &lt;U4 2 &gt;
-        &lt;L [2]
-          &lt;U4 2&gt;
-          &lt;U4 1&gt;
+        &lt;U4 2&gt; 
+        &lt;L [1]
+          &lt;U4 3&gt; 
+        &gt;
+      &gt;
+    &gt;
+  &gt; .
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B4" authorId="1">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">S6F11 W
+  &lt;L [3]
+    &lt;U1 1 &gt;
+    &lt;U2 5003 &gt;
+    &lt;L [1]
+      &lt;L [2]
+        &lt;U4 3 &gt; 
+        &lt;L [1]
+          &lt;U4 7&gt; 
         &gt;
       &gt;
     &gt;
@@ -181,12 +205,12 @@
           <t xml:space="preserve">S6F11 W
   &lt;L [3]
     &lt;U1 1 &gt;
-    &lt;U2 1003 &gt;
+    &lt;U2 5004 &gt;
     &lt;L [1]
-      &lt;L [2]
-        &lt;U4 3 &gt; 
+      &lt;L [5]
+        &lt;U4 4 &gt; 
         &lt;L [1]
-          &lt;U4 3&gt; 
+          &lt;U4 8&gt; 
         &gt;
       &gt;
     &gt;
@@ -195,7 +219,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B6" authorId="1">
+    <comment ref="B6" authorId="0">
       <text>
         <r>
           <rPr>
@@ -206,37 +230,13 @@
           <t xml:space="preserve">S6F11 W
   &lt;L [3]
     &lt;U1 1 &gt;
-    &lt;U2 1004 &gt;
+    &lt;U2 5005 &gt;
     &lt;L [1]
       &lt;L [2]
-        &lt;U4 4 &gt; 
-        &lt;L [1]
-          &lt;U4 7&gt; 
-        &gt;
-      &gt;
-    &gt;
-  &gt; .
-</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="B7" authorId="1">
-      <text>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">S6F11 W
-  &lt;L [3]
-    &lt;U1 1 &gt;
-    &lt;U2 1005 &gt;
-    &lt;L [1]
-      &lt;L [5]
-        &lt;U4 1 &gt; 
-        &lt;L [1]
-          &lt;U4 8&gt; 
+        &lt;U4 5 &gt;
+        &lt;L [2]
+          &lt;U4 2&gt;
+          &lt;U4 1&gt;
         &gt;
       &gt;
     &gt;
@@ -308,7 +308,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="647" uniqueCount="414">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="653" uniqueCount="423">
   <si>
     <t>direction</t>
   </si>
@@ -699,31 +699,37 @@
     <t>description</t>
   </si>
   <si>
-    <t>值描述</t>
-  </si>
-  <si>
     <t>ControlStateChange</t>
   </si>
   <si>
     <t>控制状态变化</t>
   </si>
   <si>
-    <t>ControlState</t>
+    <t>control_state</t>
   </si>
   <si>
     <t>U4</t>
   </si>
   <si>
-    <t>当前控制状态</t>
-  </si>
-  <si>
-    <t>OFFLINE = 2
-EQUIPMENT_OFFLINE = 3
-ATTEMPT_ONLINE = 4
-HOST_OFFLINE = 5
-ONLINE = 6
-ONLINE_LOCAL = 7
-ONLINE_REMOTE = 8</t>
+    <t>当前控制状态, 2: OFFLINE,3: EQUIPMENT_OFFLINE,4: ATTEMPT_ONLINE,5: HOST_OFFLINE,6: ONLINE,7: ONLINE_LOCAL,8: ONLINE_REMOTE</t>
+  </si>
+  <si>
+    <t>EquipmentOffline</t>
+  </si>
+  <si>
+    <t>设备离线</t>
+  </si>
+  <si>
+    <t>ControlStateOnlineLocal</t>
+  </si>
+  <si>
+    <t>控制状态变为 OnlineLocal</t>
+  </si>
+  <si>
+    <t>ControlStateOnlineRemote</t>
+  </si>
+  <si>
+    <t>控制状态变为 OnlineRemote</t>
   </si>
   <si>
     <t>ProcessStateChange</t>
@@ -735,13 +741,7 @@
     <t>process_state</t>
   </si>
   <si>
-    <t>当前运行状态</t>
-  </si>
-  <si>
-    <t>1:Manual 手动模式，黄灯
-2:Auto 自动模式 黄灯闪
-3:AutoRun 自动运行中，绿灯
-4:Alarm 报警停止中，红灯</t>
+    <t>当前运行状态, 1:Manual 手动模式，黄灯，待命 2:Auto 自动模式，绿灯 3:AutoRun 自动运行作业中，绿灯 4:Alarm 报警停止中，红灯</t>
   </si>
   <si>
     <t>previous_process_state</t>
@@ -750,373 +750,387 @@
     <t>设备上一个运行状态</t>
   </si>
   <si>
-    <t>EquipmentOffline</t>
-  </si>
-  <si>
-    <t>设备离线</t>
-  </si>
-  <si>
-    <t>ControlStateOnlineLocal</t>
-  </si>
-  <si>
-    <t>控制状态变为 OnlineLocal</t>
-  </si>
-  <si>
-    <t>ControlStateOnlineRemote</t>
-  </si>
-  <si>
-    <t>控制状态变为 OnlineRemote</t>
-  </si>
-  <si>
-    <t>end_lot</t>
-  </si>
-  <si>
-    <t>结束工单事件</t>
+    <t>sv_id</t>
+  </si>
+  <si>
+    <t>sv_name</t>
+  </si>
+  <si>
+    <t>base_value_type</t>
+  </si>
+  <si>
+    <t>value</t>
+  </si>
+  <si>
+    <t>sv_description</t>
+  </si>
+  <si>
+    <t>clock</t>
+  </si>
+  <si>
+    <t>ASCII</t>
+  </si>
+  <si>
+    <t>设备时间, 格式:"YYYYMMDDhhmmsscc"</t>
+  </si>
+  <si>
+    <t>model_name</t>
+  </si>
+  <si>
+    <t>CYG equipment</t>
+  </si>
+  <si>
+    <t>设备型号名称</t>
+  </si>
+  <si>
+    <t>softer_version</t>
+  </si>
+  <si>
+    <t>软件版本</t>
   </si>
   <si>
     <t>lot_name</t>
   </si>
   <si>
-    <t>ASCII</t>
-  </si>
-  <si>
     <t>当前工单名称</t>
   </si>
   <si>
-    <t>alarm_occur</t>
-  </si>
-  <si>
-    <t>出现报警事件</t>
-  </si>
-  <si>
-    <t>alarm_id</t>
+    <t>lot_quantity</t>
+  </si>
+  <si>
+    <t>要生产的工单数量</t>
+  </si>
+  <si>
+    <t>do_quantity</t>
+  </si>
+  <si>
+    <t>当前生产的工单数量</t>
+  </si>
+  <si>
+    <t>new_lot_cmd</t>
+  </si>
+  <si>
+    <t>新工单标识</t>
+  </si>
+  <si>
+    <t>end_lot_cmd</t>
+  </si>
+  <si>
+    <t>工单结束标识</t>
+  </si>
+  <si>
+    <t>can_run_cmd</t>
+  </si>
+  <si>
+    <t>工单可以运行标识</t>
+  </si>
+  <si>
+    <t>recipe_id</t>
+  </si>
+  <si>
+    <t>当前配方id</t>
+  </si>
+  <si>
+    <t>recipe_name</t>
+  </si>
+  <si>
+    <t>当前配方名称</t>
+  </si>
+  <si>
+    <t>pp_select_recipe_id</t>
+  </si>
+  <si>
+    <t>要切换的配方id</t>
+  </si>
+  <si>
+    <t>pp_select_recipe_name</t>
+  </si>
+  <si>
+    <t>要切换的配方名称</t>
+  </si>
+  <si>
+    <t>pp_select_cmd</t>
+  </si>
+  <si>
+    <t>通知切换配方标识</t>
+  </si>
+  <si>
+    <t>pp_select_cmd_clean</t>
+  </si>
+  <si>
+    <t>清空通知切换配方标识</t>
+  </si>
+  <si>
+    <t>pp_select_state</t>
+  </si>
+  <si>
+    <t>配方切换结果, 1:切换成功, 2:切换失败</t>
+  </si>
+  <si>
+    <t>data_id</t>
+  </si>
+  <si>
+    <t>dv_name</t>
+  </si>
+  <si>
+    <t>carrier_code_in</t>
+  </si>
+  <si>
+    <t>进站托盘码</t>
+  </si>
+  <si>
+    <t>product_codes_carrier_in</t>
+  </si>
+  <si>
+    <t>ARRAY</t>
+  </si>
+  <si>
+    <t>回复的进站托盘里面的产品码列表</t>
+  </si>
+  <si>
+    <t>product_states_carrier_in</t>
+  </si>
+  <si>
+    <t>回复的进站托盘里面的产品状态列表</t>
+  </si>
+  <si>
+    <t>is_allow_carrier_in</t>
+  </si>
+  <si>
+    <t>是否允许托盘进站,1:允许, 2:不允许</t>
+  </si>
+  <si>
+    <t>is_allow_carrier_in_reply</t>
+  </si>
+  <si>
+    <t>BOOL</t>
+  </si>
+  <si>
+    <t>是否回复了托盘进站请求</t>
+  </si>
+  <si>
+    <t>carrier_code_out</t>
+  </si>
+  <si>
+    <t>出站托盘码</t>
+  </si>
+  <si>
+    <t>product_codes_carrier_out</t>
+  </si>
+  <si>
+    <t>托盘出站时里面的产品码列表</t>
+  </si>
+  <si>
+    <t>product_states_carrier_out</t>
+  </si>
+  <si>
+    <t>托盘出站时里面的产品状态列表</t>
+  </si>
+  <si>
+    <t>is_allow_carrier_out</t>
+  </si>
+  <si>
+    <t>是否允许托盘出站</t>
+  </si>
+  <si>
+    <t>is_allow_carrier_out_reply</t>
+  </si>
+  <si>
+    <t>是否回复了托盘出站请求</t>
+  </si>
+  <si>
+    <t>product_code_in</t>
+  </si>
+  <si>
+    <t>进站产品码</t>
+  </si>
+  <si>
+    <t>is_allow_product_in</t>
+  </si>
+  <si>
+    <t>是否允许产品进站, 1:允许, 2:不允许</t>
+  </si>
+  <si>
+    <t>is_allow_product_in_reply</t>
+  </si>
+  <si>
+    <t>是否已经回复产品进站请求</t>
+  </si>
+  <si>
+    <t>ec_id</t>
+  </si>
+  <si>
+    <t>ec_name</t>
+  </si>
+  <si>
+    <t>secs_ip</t>
+  </si>
+  <si>
+    <t>127.0.0.1</t>
+  </si>
+  <si>
+    <t>secs 服务 ip</t>
+  </si>
+  <si>
+    <t>secs_port</t>
+  </si>
+  <si>
+    <t>secs 服务 port</t>
+  </si>
+  <si>
+    <t>log_save_day</t>
+  </si>
+  <si>
+    <t>日志保存天数</t>
+  </si>
+  <si>
+    <t>wait_time_eap_reply</t>
+  </si>
+  <si>
+    <t>等待 eap 回复的时间</t>
+  </si>
+  <si>
+    <t>is_monitor_plc</t>
+  </si>
+  <si>
+    <t>是否监控 plc</t>
+  </si>
+  <si>
+    <t>plc_type</t>
+  </si>
+  <si>
+    <t>tag</t>
+  </si>
+  <si>
+    <t>plc 类型, snap7: 西门子 plc, tag: 汇川标签通讯 plc, modbus: modbus 通讯 plc, mit: 三菱 plc</t>
+  </si>
+  <si>
+    <t>plc_ip</t>
+  </si>
+  <si>
+    <t>10.21.142.90</t>
+  </si>
+  <si>
+    <t>plc ip 地址</t>
+  </si>
+  <si>
+    <t>plc_port</t>
+  </si>
+  <si>
+    <t>plc 端口</t>
+  </si>
+  <si>
+    <t>db_num</t>
+  </si>
+  <si>
+    <t>西门子 plc db num</t>
+  </si>
+  <si>
+    <t>mes_heart_gap</t>
+  </si>
+  <si>
+    <t>MES心跳间隔时间</t>
+  </si>
+  <si>
+    <t>alarm_state</t>
+  </si>
+  <si>
+    <t>报警状态</t>
+  </si>
+  <si>
+    <t>mysql_user_name</t>
+  </si>
+  <si>
+    <t>root</t>
+  </si>
+  <si>
+    <t>数据库用户名</t>
+  </si>
+  <si>
+    <t>mysql_password</t>
+  </si>
+  <si>
+    <t>liuwei.520</t>
+  </si>
+  <si>
+    <t>数据库密码</t>
+  </si>
+  <si>
+    <t>mysql_host</t>
+  </si>
+  <si>
+    <t>数据库 ip 地址</t>
+  </si>
+  <si>
+    <t>mysql_database</t>
+  </si>
+  <si>
+    <t>数据库名称</t>
+  </si>
+  <si>
+    <t>socket_ip</t>
+  </si>
+  <si>
+    <t>socket 服务 ip</t>
+  </si>
+  <si>
+    <t>socket_port_secs</t>
+  </si>
+  <si>
+    <t>给 secs 使用的 socket 服务端口</t>
+  </si>
+  <si>
+    <t>socket_port_low</t>
+  </si>
+  <si>
+    <t>给下位机使用的 socket 服务端口</t>
+  </si>
+  <si>
+    <t>low_ip_port_list</t>
+  </si>
+  <si>
+    <t>Host 服务监控设备端的服务ip和端口列表</t>
+  </si>
+  <si>
+    <t>remote_command</t>
+  </si>
+  <si>
+    <t>remote_command_description</t>
+  </si>
+  <si>
+    <t>param_name</t>
+  </si>
+  <si>
+    <t>param_value_type</t>
+  </si>
+  <si>
+    <t>param_description</t>
+  </si>
+  <si>
+    <t>pp_select</t>
+  </si>
+  <si>
+    <t>工厂通知设备切换配方</t>
+  </si>
+  <si>
+    <t>配方名称</t>
+  </si>
+  <si>
+    <t>new_lot</t>
+  </si>
+  <si>
+    <t>工厂开工单</t>
+  </si>
+  <si>
+    <t>工单名称</t>
+  </si>
+  <si>
+    <t>UINT_4</t>
   </si>
   <si>
     <t>报警 id</t>
   </si>
   <si>
-    <t>alarm_text</t>
-  </si>
-  <si>
-    <t>报警内容</t>
-  </si>
-  <si>
-    <t>alarm_clean</t>
-  </si>
-  <si>
-    <t>清除报警事件</t>
-  </si>
-  <si>
-    <t>sv_id</t>
-  </si>
-  <si>
-    <t>sv_name</t>
-  </si>
-  <si>
-    <t>sv_value_type</t>
-  </si>
-  <si>
-    <t>sv_description</t>
-  </si>
-  <si>
-    <t>values</t>
-  </si>
-  <si>
-    <t>1:Manual 手动模式，黄灯，待命
-2:Auto 自动模式，绿灯
-3:AutoRun 自动运行作业中，绿灯
-4:Alarm 报警停止中，红灯</t>
-  </si>
-  <si>
-    <t>lot_quantity</t>
-  </si>
-  <si>
-    <t>要生产的工单数量</t>
-  </si>
-  <si>
-    <t>recipe_name</t>
-  </si>
-  <si>
-    <t>当前配方名称</t>
-  </si>
-  <si>
-    <t>do_quantity</t>
-  </si>
-  <si>
-    <t>当前生产的工单数量</t>
-  </si>
-  <si>
-    <t>recipe_id</t>
-  </si>
-  <si>
-    <t>当前配方id</t>
-  </si>
-  <si>
-    <t>pp_select_recipe_name</t>
-  </si>
-  <si>
-    <t>要切换配方名称</t>
-  </si>
-  <si>
-    <t>pp_select_recipe_id</t>
-  </si>
-  <si>
-    <t>要切换配方id</t>
-  </si>
-  <si>
-    <t>pp_select_state</t>
-  </si>
-  <si>
-    <t>配方切换结果</t>
-  </si>
-  <si>
-    <t>1：切换成功
-2：切换失败</t>
-  </si>
-  <si>
-    <t>pp_select_cmd</t>
-  </si>
-  <si>
-    <t>通知plc切换配方的信号值</t>
-  </si>
-  <si>
-    <t>pp_select_cmd_clean</t>
-  </si>
-  <si>
-    <t>清空通知plc切换配方信号值</t>
-  </si>
-  <si>
-    <t>model_name</t>
-  </si>
-  <si>
-    <t>设备型号名称</t>
-  </si>
-  <si>
-    <t>secsgem</t>
-  </si>
-  <si>
-    <t>softer_version</t>
-  </si>
-  <si>
-    <t>软件版本</t>
-  </si>
-  <si>
-    <t>0.1.0</t>
-  </si>
-  <si>
-    <t>new_lot_cmd</t>
-  </si>
-  <si>
-    <t>新工单标识</t>
-  </si>
-  <si>
-    <t>can_run_cmd</t>
-  </si>
-  <si>
-    <t>可以运行标识</t>
-  </si>
-  <si>
-    <t>Clock</t>
-  </si>
-  <si>
-    <t>data_id</t>
-  </si>
-  <si>
-    <t>name</t>
-  </si>
-  <si>
-    <t>ec_id</t>
-  </si>
-  <si>
-    <t>value</t>
-  </si>
-  <si>
-    <t>occur_alarm_code</t>
-  </si>
-  <si>
-    <t>发生报警代码</t>
-  </si>
-  <si>
-    <t>clean_alarm_code</t>
-  </si>
-  <si>
-    <t>清除报警代码</t>
-  </si>
-  <si>
-    <t>mes_heart_gap</t>
-  </si>
-  <si>
-    <t>MES心跳间隔时间</t>
-  </si>
-  <si>
-    <t>alarm_state</t>
-  </si>
-  <si>
-    <t>报警状态</t>
-  </si>
-  <si>
-    <t>mysql_user_name</t>
-  </si>
-  <si>
-    <t>数据库用户名</t>
-  </si>
-  <si>
-    <t>root</t>
-  </si>
-  <si>
-    <t>mysql_password</t>
-  </si>
-  <si>
-    <t>数据库密码</t>
-  </si>
-  <si>
-    <t>liuwei.520</t>
-  </si>
-  <si>
-    <t>mysql_host</t>
-  </si>
-  <si>
-    <t>数据库 ip 地址</t>
-  </si>
-  <si>
-    <t>127.0.0.1</t>
-  </si>
-  <si>
-    <t>mysql_database</t>
-  </si>
-  <si>
-    <t>数据库名称</t>
-  </si>
-  <si>
-    <t>big_beauty</t>
-  </si>
-  <si>
-    <t>wait_time_eap_reply</t>
-  </si>
-  <si>
-    <t>等待 eap 回复的时间</t>
-  </si>
-  <si>
-    <t>secs_ip</t>
-  </si>
-  <si>
-    <t>secs 服务 ip</t>
-  </si>
-  <si>
-    <t>secs_port</t>
-  </si>
-  <si>
-    <t>secs 服务 port</t>
-  </si>
-  <si>
-    <t>is_monitor_plc</t>
-  </si>
-  <si>
-    <t>BOOL</t>
-  </si>
-  <si>
-    <t>是否监控 plc</t>
-  </si>
-  <si>
-    <t>plc_ip</t>
-  </si>
-  <si>
-    <t>plc ip 地址</t>
-  </si>
-  <si>
-    <t>10.21.142.90</t>
-  </si>
-  <si>
-    <t>plc_port</t>
-  </si>
-  <si>
-    <t>plc 端口</t>
-  </si>
-  <si>
-    <t>db_num</t>
-  </si>
-  <si>
-    <t>西门子 plc db num</t>
-  </si>
-  <si>
-    <t>plc_type</t>
-  </si>
-  <si>
-    <t>plc 类型</t>
-  </si>
-  <si>
-    <t>tag</t>
-  </si>
-  <si>
-    <t>socket_ip</t>
-  </si>
-  <si>
-    <t>socket 服务 ip</t>
-  </si>
-  <si>
-    <t>socket_port_secs</t>
-  </si>
-  <si>
-    <t>给 secs 使用的 socket 服务端口</t>
-  </si>
-  <si>
-    <t>low_ip_port_list</t>
-  </si>
-  <si>
-    <t>ARRAY</t>
-  </si>
-  <si>
-    <t>Host 服务监控设备端的服务ip和端口列表</t>
-  </si>
-  <si>
-    <t>socket_port_low</t>
-  </si>
-  <si>
-    <t>给下位机使用的 socket 服务端口</t>
-  </si>
-  <si>
-    <t>log_save_day</t>
-  </si>
-  <si>
-    <t>日志保存天数</t>
-  </si>
-  <si>
-    <t>remote_command</t>
-  </si>
-  <si>
-    <t>remote_command_description</t>
-  </si>
-  <si>
-    <t>param_name</t>
-  </si>
-  <si>
-    <t>param_value_type</t>
-  </si>
-  <si>
-    <t>param_description</t>
-  </si>
-  <si>
-    <t>pp_select</t>
-  </si>
-  <si>
-    <t>工厂通知设备切换配方</t>
-  </si>
-  <si>
-    <t>配方名称</t>
-  </si>
-  <si>
-    <t>new_lot</t>
-  </si>
-  <si>
-    <t>工厂开工单</t>
-  </si>
-  <si>
-    <t>工单名称</t>
-  </si>
-  <si>
-    <t>UINT_4</t>
-  </si>
-  <si>
     <t>中文报警内容</t>
   </si>
   <si>
@@ -1133,6 +1147,18 @@
   </si>
   <si>
     <t>操作方式</t>
+  </si>
+  <si>
+    <t>DB1998.DBX2530.0</t>
+  </si>
+  <si>
+    <t>bool</t>
+  </si>
+  <si>
+    <t>mes 写</t>
+  </si>
+  <si>
+    <t>MES 心跳</t>
   </si>
   <si>
     <t>DB1998.DBX0.1</t>
@@ -1163,7 +1189,7 @@
     <t>mes 读</t>
   </si>
   <si>
-    <t>设备的控制状态</t>
+    <t>本地模式 | 远程模式</t>
   </si>
   <si>
     <t>DB1998.DBX2.0</t>
@@ -1172,7 +1198,7 @@
     <t>int</t>
   </si>
   <si>
-    <t>设备的运行状态</t>
+    <t>设备运行状态</t>
   </si>
   <si>
     <t>DB1998.DBX4.0</t>
@@ -1181,49 +1207,37 @@
     <t>str</t>
   </si>
   <si>
-    <t>出现报警时报警 id</t>
-  </si>
-  <si>
-    <t>DB1998.DBX2530.0</t>
-  </si>
-  <si>
-    <t>bool</t>
-  </si>
-  <si>
-    <t>mes 写</t>
-  </si>
-  <si>
-    <t>MES 心跳</t>
+    <t>出现报警时的报警代码</t>
+  </si>
+  <si>
+    <t>DB1998.DBW2532</t>
+  </si>
+  <si>
+    <t>工厂暂停设备</t>
+  </si>
+  <si>
+    <t>DB1998.DBW2746</t>
+  </si>
+  <si>
+    <t>工厂暂停原因</t>
+  </si>
+  <si>
+    <t>DB1998.DBW2534</t>
+  </si>
+  <si>
+    <t>DB1998.DBD2618</t>
+  </si>
+  <si>
+    <t>Dint</t>
+  </si>
+  <si>
+    <t>工单数量</t>
   </si>
   <si>
     <t>DB1998.DBW120</t>
   </si>
   <si>
     <t>当前配方</t>
-  </si>
-  <si>
-    <t>DB1998.DBW2532</t>
-  </si>
-  <si>
-    <t>控制设备暂停</t>
-  </si>
-  <si>
-    <t>DB1998.DBW2746</t>
-  </si>
-  <si>
-    <t>暂停原因</t>
-  </si>
-  <si>
-    <t>DB1998.DBW2534</t>
-  </si>
-  <si>
-    <t>DB1998.DBD2618</t>
-  </si>
-  <si>
-    <t>Dint</t>
-  </si>
-  <si>
-    <t>工单</t>
   </si>
   <si>
     <t>DB1998.DBW2624</t>
@@ -1840,17 +1854,17 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="16"/>
-      <color rgb="FF000000"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
       <sz val="14"/>
       <color rgb="FFFF0000"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="16"/>
+      <color rgb="FF000000"/>
+      <name val="宋体"/>
+      <charset val="134"/>
     </font>
     <font>
       <u/>
@@ -2810,7 +2824,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="117">
+  <cellXfs count="110">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -3058,18 +3072,18 @@
     <xf numFmtId="0" fontId="0" fillId="10" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="11" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -3082,17 +3096,35 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="14" fillId="13" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="13" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -3100,28 +3132,13 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
@@ -3130,35 +3147,11 @@
     <xf numFmtId="0" fontId="10" fillId="13" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="13" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -3545,39 +3538,39 @@
       </c>
     </row>
     <row r="2" spans="1:7">
-      <c r="A2" s="84" t="s">
+      <c r="A2" s="86" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="84" t="s">
+      <c r="B2" s="86" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="84" t="s">
+      <c r="C2" s="86" t="s">
         <v>5</v>
       </c>
-      <c r="E2" s="84" t="s">
+      <c r="E2" s="86" t="s">
         <v>6</v>
       </c>
-      <c r="F2" s="84" t="s">
+      <c r="F2" s="86" t="s">
         <v>7</v>
       </c>
-      <c r="G2" s="84" t="s">
+      <c r="G2" s="86" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="3" ht="27" spans="1:7">
-      <c r="A3" s="84" t="s">
+      <c r="A3" s="86" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="84" t="s">
+      <c r="B3" s="86" t="s">
         <v>9</v>
       </c>
-      <c r="C3" s="84" t="s">
+      <c r="C3" s="86" t="s">
         <v>10</v>
       </c>
-      <c r="E3" s="84" t="s">
+      <c r="E3" s="86" t="s">
         <v>6</v>
       </c>
-      <c r="F3" s="84" t="s">
+      <c r="F3" s="86" t="s">
         <v>11</v>
       </c>
       <c r="G3" s="90" t="s">
@@ -3585,19 +3578,19 @@
       </c>
     </row>
     <row r="4" s="81" customFormat="1" ht="40.5" spans="1:7">
-      <c r="A4" s="86" t="s">
+      <c r="A4" s="84" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="86" t="s">
+      <c r="B4" s="84" t="s">
         <v>13</v>
       </c>
-      <c r="C4" s="86" t="s">
+      <c r="C4" s="84" t="s">
         <v>14</v>
       </c>
-      <c r="E4" s="84" t="s">
+      <c r="E4" s="86" t="s">
         <v>6</v>
       </c>
-      <c r="F4" s="84" t="s">
+      <c r="F4" s="86" t="s">
         <v>15</v>
       </c>
       <c r="G4" s="90" t="s">
@@ -3605,19 +3598,19 @@
       </c>
     </row>
     <row r="5" s="81" customFormat="1" spans="1:7">
-      <c r="A5" s="86" t="s">
+      <c r="A5" s="84" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="86" t="s">
+      <c r="B5" s="84" t="s">
         <v>17</v>
       </c>
-      <c r="C5" s="86" t="s">
+      <c r="C5" s="84" t="s">
         <v>18</v>
       </c>
-      <c r="E5" s="84" t="s">
+      <c r="E5" s="86" t="s">
         <v>6</v>
       </c>
-      <c r="F5" s="86" t="s">
+      <c r="F5" s="84" t="s">
         <v>19</v>
       </c>
       <c r="G5" s="90" t="s">
@@ -3625,19 +3618,19 @@
       </c>
     </row>
     <row r="6" s="81" customFormat="1" ht="40.5" spans="1:7">
-      <c r="A6" s="86" t="s">
+      <c r="A6" s="84" t="s">
         <v>3</v>
       </c>
-      <c r="B6" s="86" t="s">
+      <c r="B6" s="84" t="s">
         <v>21</v>
       </c>
-      <c r="C6" s="86" t="s">
+      <c r="C6" s="84" t="s">
         <v>22</v>
       </c>
-      <c r="E6" s="84" t="s">
+      <c r="E6" s="86" t="s">
         <v>6</v>
       </c>
-      <c r="F6" s="86" t="s">
+      <c r="F6" s="84" t="s">
         <v>23</v>
       </c>
       <c r="G6" s="90" t="s">
@@ -3645,19 +3638,19 @@
       </c>
     </row>
     <row r="7" ht="67.5" spans="1:7">
-      <c r="A7" s="84" t="s">
+      <c r="A7" s="86" t="s">
         <v>3</v>
       </c>
-      <c r="B7" s="84" t="s">
+      <c r="B7" s="86" t="s">
         <v>25</v>
       </c>
-      <c r="C7" s="86" t="s">
+      <c r="C7" s="84" t="s">
         <v>26</v>
       </c>
-      <c r="E7" s="84" t="s">
+      <c r="E7" s="86" t="s">
         <v>6</v>
       </c>
-      <c r="F7" s="84" t="s">
+      <c r="F7" s="86" t="s">
         <v>27</v>
       </c>
       <c r="G7" s="90" t="s">
@@ -3665,19 +3658,19 @@
       </c>
     </row>
     <row r="8" ht="81" spans="1:7">
-      <c r="A8" s="84" t="s">
+      <c r="A8" s="86" t="s">
         <v>3</v>
       </c>
-      <c r="B8" s="84" t="s">
+      <c r="B8" s="86" t="s">
         <v>29</v>
       </c>
-      <c r="C8" s="86" t="s">
+      <c r="C8" s="84" t="s">
         <v>30</v>
       </c>
-      <c r="E8" s="84" t="s">
+      <c r="E8" s="86" t="s">
         <v>6</v>
       </c>
-      <c r="F8" s="84" t="s">
+      <c r="F8" s="86" t="s">
         <v>31</v>
       </c>
       <c r="G8" s="90" t="s">
@@ -3685,19 +3678,19 @@
       </c>
     </row>
     <row r="9" ht="54" spans="1:7">
-      <c r="A9" s="84" t="s">
+      <c r="A9" s="86" t="s">
         <v>3</v>
       </c>
-      <c r="B9" s="84" t="s">
+      <c r="B9" s="86" t="s">
         <v>33</v>
       </c>
-      <c r="C9" s="86" t="s">
+      <c r="C9" s="84" t="s">
         <v>34</v>
       </c>
-      <c r="E9" s="84" t="s">
+      <c r="E9" s="86" t="s">
         <v>6</v>
       </c>
-      <c r="F9" s="84" t="s">
+      <c r="F9" s="86" t="s">
         <v>35</v>
       </c>
       <c r="G9" s="90" t="s">
@@ -3705,19 +3698,19 @@
       </c>
     </row>
     <row r="10" ht="81" spans="1:7">
-      <c r="A10" s="84" t="s">
+      <c r="A10" s="86" t="s">
         <v>3</v>
       </c>
-      <c r="B10" s="84" t="s">
+      <c r="B10" s="86" t="s">
         <v>37</v>
       </c>
-      <c r="C10" s="84" t="s">
+      <c r="C10" s="86" t="s">
         <v>38</v>
       </c>
-      <c r="E10" s="84" t="s">
+      <c r="E10" s="86" t="s">
         <v>6</v>
       </c>
-      <c r="F10" s="84" t="s">
+      <c r="F10" s="86" t="s">
         <v>39</v>
       </c>
       <c r="G10" s="90" t="s">
@@ -3725,19 +3718,19 @@
       </c>
     </row>
     <row r="11" ht="148.5" spans="1:7">
-      <c r="A11" s="84" t="s">
+      <c r="A11" s="86" t="s">
         <v>3</v>
       </c>
-      <c r="B11" s="84" t="s">
+      <c r="B11" s="86" t="s">
         <v>41</v>
       </c>
-      <c r="C11" s="84" t="s">
+      <c r="C11" s="86" t="s">
         <v>42</v>
       </c>
-      <c r="E11" s="84" t="s">
+      <c r="E11" s="86" t="s">
         <v>6</v>
       </c>
-      <c r="F11" s="84" t="s">
+      <c r="F11" s="86" t="s">
         <v>43</v>
       </c>
       <c r="G11" s="90" t="s">
@@ -3745,19 +3738,19 @@
       </c>
     </row>
     <row r="12" ht="40.5" spans="1:7">
-      <c r="A12" s="84" t="s">
+      <c r="A12" s="86" t="s">
         <v>3</v>
       </c>
-      <c r="B12" s="84" t="s">
+      <c r="B12" s="86" t="s">
         <v>45</v>
       </c>
-      <c r="C12" s="84" t="s">
+      <c r="C12" s="86" t="s">
         <v>46</v>
       </c>
-      <c r="E12" s="84" t="s">
+      <c r="E12" s="86" t="s">
         <v>6</v>
       </c>
-      <c r="F12" s="84" t="s">
+      <c r="F12" s="86" t="s">
         <v>47</v>
       </c>
       <c r="G12" s="90" t="s">
@@ -3765,27 +3758,27 @@
       </c>
     </row>
     <row r="13" spans="1:7">
-      <c r="A13" s="84"/>
-      <c r="B13" s="84"/>
-      <c r="C13" s="84"/>
-      <c r="E13" s="84" t="s">
+      <c r="A13" s="86"/>
+      <c r="B13" s="86"/>
+      <c r="C13" s="86"/>
+      <c r="E13" s="86" t="s">
         <v>6</v>
       </c>
-      <c r="F13" s="84" t="s">
+      <c r="F13" s="86" t="s">
         <v>49</v>
       </c>
-      <c r="G13" s="84" t="s">
+      <c r="G13" s="86" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="14" ht="81" spans="1:7">
-      <c r="A14" s="84"/>
-      <c r="B14" s="84"/>
-      <c r="C14" s="84"/>
-      <c r="E14" s="84" t="s">
+      <c r="A14" s="86"/>
+      <c r="B14" s="86"/>
+      <c r="C14" s="86"/>
+      <c r="E14" s="86" t="s">
         <v>6</v>
       </c>
-      <c r="F14" s="84" t="s">
+      <c r="F14" s="86" t="s">
         <v>51</v>
       </c>
       <c r="G14" s="90" t="s">
@@ -3793,19 +3786,19 @@
       </c>
     </row>
     <row r="15" ht="40.5" spans="1:7">
-      <c r="A15" s="84" t="s">
+      <c r="A15" s="86" t="s">
         <v>3</v>
       </c>
-      <c r="B15" s="84" t="s">
+      <c r="B15" s="86" t="s">
         <v>53</v>
       </c>
       <c r="C15" s="90" t="s">
         <v>54</v>
       </c>
-      <c r="E15" s="84" t="s">
+      <c r="E15" s="86" t="s">
         <v>6</v>
       </c>
-      <c r="F15" s="84" t="s">
+      <c r="F15" s="86" t="s">
         <v>55</v>
       </c>
       <c r="G15" s="90" t="s">
@@ -3813,19 +3806,19 @@
       </c>
     </row>
     <row r="16" ht="94.5" spans="1:7">
-      <c r="A16" s="84" t="s">
+      <c r="A16" s="86" t="s">
         <v>57</v>
       </c>
-      <c r="B16" s="84" t="s">
+      <c r="B16" s="86" t="s">
         <v>58</v>
       </c>
       <c r="C16" s="90" t="s">
         <v>59</v>
       </c>
-      <c r="E16" s="84" t="s">
+      <c r="E16" s="86" t="s">
         <v>60</v>
       </c>
-      <c r="F16" s="84" t="s">
+      <c r="F16" s="86" t="s">
         <v>61</v>
       </c>
       <c r="G16" s="90" t="s">
@@ -3833,19 +3826,19 @@
       </c>
     </row>
     <row r="17" ht="108" spans="1:7">
-      <c r="A17" s="84" t="s">
+      <c r="A17" s="86" t="s">
         <v>57</v>
       </c>
-      <c r="B17" s="84" t="s">
+      <c r="B17" s="86" t="s">
         <v>63</v>
       </c>
       <c r="C17" s="90" t="s">
         <v>64</v>
       </c>
-      <c r="E17" s="84" t="s">
+      <c r="E17" s="86" t="s">
         <v>60</v>
       </c>
-      <c r="F17" s="84" t="s">
+      <c r="F17" s="86" t="s">
         <v>65</v>
       </c>
       <c r="G17" s="90" t="s">
@@ -3853,19 +3846,19 @@
       </c>
     </row>
     <row r="18" ht="40.5" spans="1:7">
-      <c r="A18" s="84" t="s">
+      <c r="A18" s="86" t="s">
         <v>57</v>
       </c>
-      <c r="B18" s="84" t="s">
+      <c r="B18" s="86" t="s">
         <v>67</v>
       </c>
       <c r="C18" s="90" t="s">
         <v>68</v>
       </c>
-      <c r="E18" s="84" t="s">
+      <c r="E18" s="86" t="s">
         <v>60</v>
       </c>
-      <c r="F18" s="84" t="s">
+      <c r="F18" s="86" t="s">
         <v>69</v>
       </c>
       <c r="G18" s="90" t="s">
@@ -3873,13 +3866,13 @@
       </c>
     </row>
     <row r="19" ht="27" spans="1:7">
-      <c r="A19" s="84"/>
-      <c r="B19" s="84"/>
+      <c r="A19" s="86"/>
+      <c r="B19" s="86"/>
       <c r="C19" s="90"/>
-      <c r="E19" s="84" t="s">
+      <c r="E19" s="86" t="s">
         <v>6</v>
       </c>
-      <c r="F19" s="84" t="s">
+      <c r="F19" s="86" t="s">
         <v>71</v>
       </c>
       <c r="G19" s="90" t="s">
@@ -3887,19 +3880,19 @@
       </c>
     </row>
     <row r="20" ht="108" spans="1:7">
-      <c r="A20" s="84" t="s">
+      <c r="A20" s="86" t="s">
         <v>3</v>
       </c>
-      <c r="B20" s="84" t="s">
+      <c r="B20" s="86" t="s">
         <v>73</v>
       </c>
       <c r="C20" s="90" t="s">
         <v>74</v>
       </c>
-      <c r="E20" s="84" t="s">
+      <c r="E20" s="86" t="s">
         <v>6</v>
       </c>
-      <c r="F20" s="84" t="s">
+      <c r="F20" s="86" t="s">
         <v>75</v>
       </c>
       <c r="G20" s="90" t="s">
@@ -3907,19 +3900,19 @@
       </c>
     </row>
     <row r="21" ht="108" spans="1:7">
-      <c r="A21" s="84" t="s">
+      <c r="A21" s="86" t="s">
         <v>3</v>
       </c>
-      <c r="B21" s="84" t="s">
+      <c r="B21" s="86" t="s">
         <v>76</v>
       </c>
       <c r="C21" s="90" t="s">
         <v>77</v>
       </c>
-      <c r="E21" s="84" t="s">
+      <c r="E21" s="86" t="s">
         <v>6</v>
       </c>
-      <c r="F21" s="84" t="s">
+      <c r="F21" s="86" t="s">
         <v>78</v>
       </c>
       <c r="G21" s="90" t="s">
@@ -3927,19 +3920,19 @@
       </c>
     </row>
     <row r="22" ht="108" spans="1:7">
-      <c r="A22" s="84" t="s">
+      <c r="A22" s="86" t="s">
         <v>3</v>
       </c>
-      <c r="B22" s="84" t="s">
+      <c r="B22" s="86" t="s">
         <v>79</v>
       </c>
       <c r="C22" s="90" t="s">
         <v>80</v>
       </c>
-      <c r="E22" s="84" t="s">
+      <c r="E22" s="86" t="s">
         <v>6</v>
       </c>
-      <c r="F22" s="84" t="s">
+      <c r="F22" s="86" t="s">
         <v>81</v>
       </c>
       <c r="G22" s="90" t="s">
@@ -3947,19 +3940,19 @@
       </c>
     </row>
     <row r="23" ht="108" spans="1:7">
-      <c r="A23" s="84" t="s">
+      <c r="A23" s="86" t="s">
         <v>3</v>
       </c>
-      <c r="B23" s="84" t="s">
+      <c r="B23" s="86" t="s">
         <v>82</v>
       </c>
       <c r="C23" s="90" t="s">
         <v>83</v>
       </c>
-      <c r="E23" s="84" t="s">
+      <c r="E23" s="86" t="s">
         <v>6</v>
       </c>
-      <c r="F23" s="84" t="s">
+      <c r="F23" s="86" t="s">
         <v>84</v>
       </c>
       <c r="G23" s="90" t="s">
@@ -3967,39 +3960,39 @@
       </c>
     </row>
     <row r="24" spans="1:7">
-      <c r="A24" s="84" t="s">
+      <c r="A24" s="86" t="s">
         <v>3</v>
       </c>
-      <c r="B24" s="84" t="s">
+      <c r="B24" s="86" t="s">
         <v>85</v>
       </c>
-      <c r="C24" s="84" t="s">
+      <c r="C24" s="86" t="s">
         <v>86</v>
       </c>
-      <c r="E24" s="84" t="s">
+      <c r="E24" s="86" t="s">
         <v>6</v>
       </c>
-      <c r="F24" s="84" t="s">
+      <c r="F24" s="86" t="s">
         <v>87</v>
       </c>
-      <c r="G24" s="84" t="s">
+      <c r="G24" s="86" t="s">
         <v>88</v>
       </c>
     </row>
     <row r="25" ht="108" spans="1:7">
-      <c r="A25" s="84" t="s">
+      <c r="A25" s="86" t="s">
         <v>57</v>
       </c>
-      <c r="B25" s="84" t="s">
+      <c r="B25" s="86" t="s">
         <v>89</v>
       </c>
       <c r="C25" s="90" t="s">
         <v>90</v>
       </c>
-      <c r="E25" s="84" t="s">
+      <c r="E25" s="86" t="s">
         <v>60</v>
       </c>
-      <c r="F25" s="84" t="s">
+      <c r="F25" s="86" t="s">
         <v>91</v>
       </c>
       <c r="G25" s="90" t="s">
@@ -4007,19 +4000,19 @@
       </c>
     </row>
     <row r="26" ht="27" spans="1:7">
-      <c r="A26" s="84" t="s">
+      <c r="A26" s="86" t="s">
         <v>57</v>
       </c>
-      <c r="B26" s="84" t="s">
+      <c r="B26" s="86" t="s">
         <v>92</v>
       </c>
       <c r="C26" s="90" t="s">
         <v>68</v>
       </c>
-      <c r="E26" s="84" t="s">
+      <c r="E26" s="86" t="s">
         <v>60</v>
       </c>
-      <c r="F26" s="84" t="s">
+      <c r="F26" s="86" t="s">
         <v>69</v>
       </c>
       <c r="G26" s="90" t="s">
@@ -4027,19 +4020,19 @@
       </c>
     </row>
     <row r="27" ht="40.5" spans="1:7">
-      <c r="A27" s="84" t="s">
+      <c r="A27" s="86" t="s">
         <v>3</v>
       </c>
-      <c r="B27" s="84" t="s">
+      <c r="B27" s="86" t="s">
         <v>94</v>
       </c>
-      <c r="C27" s="84" t="s">
+      <c r="C27" s="86" t="s">
         <v>95</v>
       </c>
-      <c r="E27" s="84" t="s">
+      <c r="E27" s="86" t="s">
         <v>6</v>
       </c>
-      <c r="F27" s="84" t="s">
+      <c r="F27" s="86" t="s">
         <v>96</v>
       </c>
       <c r="G27" s="90" t="s">
@@ -4068,41 +4061,41 @@
   <sheetData>
     <row r="1" ht="21" spans="1:6">
       <c r="A1" s="74" t="s">
-        <v>294</v>
+        <v>303</v>
       </c>
       <c r="B1" s="74" t="s">
-        <v>295</v>
+        <v>304</v>
       </c>
       <c r="C1" s="74" t="s">
-        <v>296</v>
+        <v>305</v>
       </c>
       <c r="D1" s="74" t="s">
-        <v>297</v>
+        <v>306</v>
       </c>
       <c r="E1" s="74" t="s">
-        <v>298</v>
+        <v>307</v>
       </c>
     </row>
     <row r="2" ht="21" spans="1:6">
       <c r="A2" s="74" t="s">
-        <v>299</v>
+        <v>308</v>
       </c>
       <c r="B2" s="16" t="s">
-        <v>300</v>
+        <v>309</v>
       </c>
       <c r="C2" s="16" t="s">
-        <v>301</v>
+        <v>310</v>
       </c>
       <c r="D2" s="16" t="s">
-        <v>302</v>
+        <v>311</v>
       </c>
       <c r="E2" s="75" t="s">
-        <v>303</v>
+        <v>312</v>
       </c>
     </row>
     <row r="3" ht="21" spans="1:6">
       <c r="A3" s="74" t="s">
-        <v>304</v>
+        <v>313</v>
       </c>
       <c r="B3" s="16">
         <v>5</v>
@@ -4119,44 +4112,44 @@
     </row>
     <row r="4" ht="21" spans="1:6">
       <c r="A4" s="74" t="s">
-        <v>305</v>
+        <v>314</v>
       </c>
       <c r="B4" s="16" t="s">
-        <v>306</v>
+        <v>315</v>
       </c>
       <c r="C4" s="16" t="s">
-        <v>306</v>
+        <v>315</v>
       </c>
       <c r="D4" s="16" t="s">
-        <v>306</v>
+        <v>315</v>
       </c>
       <c r="E4" s="75" t="s">
-        <v>306</v>
+        <v>315</v>
       </c>
       <c r="F4" t="s">
-        <v>307</v>
+        <v>316</v>
       </c>
     </row>
     <row r="5" ht="21" spans="1:6">
       <c r="A5" s="74" t="s">
-        <v>308</v>
+        <v>317</v>
       </c>
       <c r="B5" s="16" t="s">
-        <v>300</v>
+        <v>309</v>
       </c>
       <c r="C5" s="16" t="s">
-        <v>309</v>
+        <v>318</v>
       </c>
       <c r="D5" s="16" t="s">
-        <v>302</v>
+        <v>311</v>
       </c>
       <c r="E5" s="75" t="s">
-        <v>310</v>
+        <v>319</v>
       </c>
     </row>
     <row r="6" ht="21" spans="1:6">
       <c r="A6" s="74" t="s">
-        <v>304</v>
+        <v>313</v>
       </c>
       <c r="B6" s="16">
         <v>1</v>
@@ -4173,22 +4166,22 @@
     </row>
     <row r="7" ht="21" spans="1:6">
       <c r="A7" s="74" t="s">
-        <v>311</v>
+        <v>320</v>
       </c>
       <c r="B7" s="16" t="s">
-        <v>312</v>
+        <v>321</v>
       </c>
       <c r="C7" s="16" t="s">
-        <v>313</v>
+        <v>322</v>
       </c>
       <c r="D7" s="16"/>
       <c r="E7" s="75" t="s">
-        <v>313</v>
+        <v>322</v>
       </c>
     </row>
     <row r="8" ht="21" spans="1:6">
       <c r="A8" s="74" t="s">
-        <v>304</v>
+        <v>313</v>
       </c>
       <c r="B8" s="75">
         <v>0</v>
@@ -4205,7 +4198,7 @@
     </row>
     <row r="9" ht="21" spans="1:6">
       <c r="A9" s="74" t="s">
-        <v>304</v>
+        <v>313</v>
       </c>
       <c r="B9" s="75">
         <v>0</v>
@@ -4243,13 +4236,13 @@
   <sheetData>
     <row r="1" ht="14.25" spans="1:7">
       <c r="A1" s="53" t="s">
-        <v>314</v>
+        <v>323</v>
       </c>
       <c r="B1" s="54" t="s">
-        <v>315</v>
+        <v>324</v>
       </c>
       <c r="C1" s="55" t="s">
-        <v>316</v>
+        <v>325</v>
       </c>
       <c r="D1" s="56"/>
       <c r="E1" s="57"/>
@@ -4262,16 +4255,16 @@
       <c r="A2" s="59"/>
       <c r="B2" s="60"/>
       <c r="C2" s="61" t="s">
-        <v>317</v>
+        <v>326</v>
       </c>
       <c r="D2" s="61" t="s">
-        <v>318</v>
+        <v>327</v>
       </c>
       <c r="E2" s="62" t="s">
-        <v>319</v>
+        <v>328</v>
       </c>
       <c r="F2" s="62" t="s">
-        <v>318</v>
+        <v>327</v>
       </c>
       <c r="G2" s="63"/>
     </row>
@@ -4280,23 +4273,23 @@
         <v>4000</v>
       </c>
       <c r="B3" s="65" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="C3" s="66" t="s">
-        <v>321</v>
+        <v>330</v>
       </c>
       <c r="D3" s="66"/>
       <c r="E3" s="67"/>
       <c r="F3" s="64"/>
       <c r="G3" s="67" t="s">
-        <v>322</v>
+        <v>331</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4" s="64"/>
       <c r="B4" s="68"/>
       <c r="C4" s="66" t="s">
-        <v>323</v>
+        <v>332</v>
       </c>
       <c r="D4" s="66"/>
       <c r="E4" s="67"/>
@@ -4308,16 +4301,16 @@
         <v>4001</v>
       </c>
       <c r="B5" s="67" t="s">
-        <v>324</v>
+        <v>333</v>
       </c>
       <c r="C5" s="66" t="s">
-        <v>325</v>
+        <v>334</v>
       </c>
       <c r="D5" s="66"/>
       <c r="E5" s="67"/>
       <c r="F5" s="64"/>
       <c r="G5" s="67" t="s">
-        <v>324</v>
+        <v>333</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -4325,23 +4318,23 @@
         <v>4002</v>
       </c>
       <c r="B6" s="70" t="s">
-        <v>326</v>
+        <v>335</v>
       </c>
       <c r="C6" s="66" t="s">
-        <v>327</v>
+        <v>336</v>
       </c>
       <c r="D6" s="66"/>
       <c r="E6" s="67"/>
       <c r="F6" s="64"/>
       <c r="G6" s="69" t="s">
-        <v>326</v>
+        <v>335</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7" s="71"/>
       <c r="B7" s="68"/>
       <c r="C7" s="66" t="s">
-        <v>328</v>
+        <v>337</v>
       </c>
       <c r="D7" s="66"/>
       <c r="E7" s="67"/>
@@ -4352,10 +4345,10 @@
       <c r="A8" s="71"/>
       <c r="B8" s="68"/>
       <c r="C8" s="66" t="s">
-        <v>329</v>
+        <v>338</v>
       </c>
       <c r="D8" s="66" t="s">
-        <v>330</v>
+        <v>339</v>
       </c>
       <c r="E8" s="67"/>
       <c r="F8" s="64"/>
@@ -4365,7 +4358,7 @@
       <c r="A9" s="72"/>
       <c r="B9" s="73"/>
       <c r="C9" s="66" t="s">
-        <v>331</v>
+        <v>340</v>
       </c>
       <c r="D9" s="66"/>
       <c r="E9" s="66"/>
@@ -4377,13 +4370,13 @@
         <v>4003</v>
       </c>
       <c r="B10" s="70" t="s">
-        <v>332</v>
+        <v>341</v>
       </c>
       <c r="C10" s="66" t="s">
-        <v>333</v>
+        <v>342</v>
       </c>
       <c r="D10" s="66" t="s">
-        <v>334</v>
+        <v>343</v>
       </c>
       <c r="E10" s="66"/>
       <c r="F10" s="66"/>
@@ -4393,10 +4386,10 @@
       <c r="A11" s="72"/>
       <c r="B11" s="73"/>
       <c r="C11" s="66" t="s">
-        <v>335</v>
+        <v>344</v>
       </c>
       <c r="D11" s="66" t="s">
-        <v>336</v>
+        <v>345</v>
       </c>
       <c r="E11" s="66"/>
       <c r="F11" s="66"/>
@@ -4407,10 +4400,10 @@
         <v>4004</v>
       </c>
       <c r="B12" s="70" t="s">
-        <v>337</v>
+        <v>346</v>
       </c>
       <c r="C12" s="66" t="s">
-        <v>338</v>
+        <v>347</v>
       </c>
       <c r="D12" s="66"/>
       <c r="E12" s="66"/>
@@ -4421,7 +4414,7 @@
       <c r="A13" s="72"/>
       <c r="B13" s="73"/>
       <c r="C13" s="66" t="s">
-        <v>339</v>
+        <v>348</v>
       </c>
       <c r="D13" s="66"/>
       <c r="E13" s="66"/>
@@ -4433,10 +4426,10 @@
         <v>4005</v>
       </c>
       <c r="B14" s="70" t="s">
-        <v>340</v>
+        <v>349</v>
       </c>
       <c r="C14" s="66" t="s">
-        <v>323</v>
+        <v>332</v>
       </c>
       <c r="D14" s="66"/>
       <c r="E14" s="66"/>
@@ -4447,7 +4440,7 @@
       <c r="A15" s="72"/>
       <c r="B15" s="73"/>
       <c r="C15" s="66" t="s">
-        <v>341</v>
+        <v>350</v>
       </c>
       <c r="D15" s="66"/>
       <c r="E15" s="66"/>
@@ -4459,10 +4452,10 @@
         <v>4006</v>
       </c>
       <c r="B16" s="70" t="s">
-        <v>342</v>
+        <v>351</v>
       </c>
       <c r="C16" s="66" t="s">
-        <v>343</v>
+        <v>352</v>
       </c>
       <c r="D16" s="66"/>
       <c r="E16" s="66"/>
@@ -4473,7 +4466,7 @@
       <c r="A17" s="72"/>
       <c r="B17" s="73"/>
       <c r="C17" s="66" t="s">
-        <v>339</v>
+        <v>348</v>
       </c>
       <c r="D17" s="66"/>
       <c r="E17" s="66"/>
@@ -4485,10 +4478,10 @@
         <v>4007</v>
       </c>
       <c r="B18" s="70" t="s">
-        <v>344</v>
+        <v>353</v>
       </c>
       <c r="C18" s="66" t="s">
-        <v>343</v>
+        <v>352</v>
       </c>
       <c r="D18" s="66"/>
       <c r="E18" s="66"/>
@@ -4499,7 +4492,7 @@
       <c r="A19" s="72"/>
       <c r="B19" s="73"/>
       <c r="C19" s="66" t="s">
-        <v>339</v>
+        <v>348</v>
       </c>
       <c r="D19" s="66"/>
       <c r="E19" s="66"/>
@@ -4511,10 +4504,10 @@
         <v>4008</v>
       </c>
       <c r="B20" s="70" t="s">
-        <v>345</v>
+        <v>354</v>
       </c>
       <c r="C20" s="66" t="s">
-        <v>343</v>
+        <v>352</v>
       </c>
       <c r="D20" s="66"/>
       <c r="E20" s="67"/>
@@ -4525,7 +4518,7 @@
       <c r="A21" s="72"/>
       <c r="B21" s="73"/>
       <c r="C21" s="66" t="s">
-        <v>346</v>
+        <v>355</v>
       </c>
       <c r="D21" s="66"/>
       <c r="E21" s="67"/>
@@ -4585,27 +4578,27 @@
   <sheetData>
     <row r="1" ht="21.75" spans="4:13">
       <c r="D1" s="2" t="s">
-        <v>347</v>
+        <v>356</v>
       </c>
     </row>
     <row r="2" ht="16.5" spans="4:13">
       <c r="D2" s="3" t="s">
-        <v>348</v>
+        <v>357</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>284</v>
+        <v>293</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>349</v>
+        <v>358</v>
       </c>
       <c r="G2" s="5" t="s">
-        <v>283</v>
+        <v>292</v>
       </c>
       <c r="H2" s="6" t="s">
-        <v>350</v>
+        <v>359</v>
       </c>
       <c r="I2" s="4" t="s">
-        <v>284</v>
+        <v>293</v>
       </c>
     </row>
     <row r="3" ht="16.5" spans="4:13">
@@ -4613,7 +4606,7 @@
         <v>1</v>
       </c>
       <c r="E3" s="7" t="s">
-        <v>351</v>
+        <v>360</v>
       </c>
       <c r="F3" s="7">
         <v>1</v>
@@ -4622,10 +4615,10 @@
         <v>1</v>
       </c>
       <c r="H3" s="8" t="s">
-        <v>352</v>
+        <v>361</v>
       </c>
       <c r="I3" s="9" t="s">
-        <v>288</v>
+        <v>297</v>
       </c>
     </row>
     <row r="4" ht="16.5" spans="4:13">
@@ -4634,7 +4627,7 @@
       <c r="F4" s="10"/>
       <c r="G4" s="10"/>
       <c r="H4" s="8" t="s">
-        <v>353</v>
+        <v>362</v>
       </c>
       <c r="I4" s="11"/>
     </row>
@@ -4644,7 +4637,7 @@
       <c r="F5" s="10"/>
       <c r="G5" s="10"/>
       <c r="H5" s="8" t="s">
-        <v>354</v>
+        <v>363</v>
       </c>
       <c r="I5" s="11"/>
     </row>
@@ -4654,7 +4647,7 @@
       <c r="F6" s="10"/>
       <c r="G6" s="10"/>
       <c r="H6" s="8" t="s">
-        <v>355</v>
+        <v>364</v>
       </c>
       <c r="I6" s="11"/>
     </row>
@@ -4664,7 +4657,7 @@
       <c r="F7" s="12"/>
       <c r="G7" s="12"/>
       <c r="H7" s="8" t="s">
-        <v>356</v>
+        <v>365</v>
       </c>
       <c r="I7" s="13"/>
     </row>
@@ -4673,7 +4666,7 @@
         <v>2</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>357</v>
+        <v>366</v>
       </c>
       <c r="F8" s="7">
         <v>2</v>
@@ -4682,16 +4675,16 @@
         <v>2</v>
       </c>
       <c r="H8" s="8" t="s">
-        <v>352</v>
+        <v>361</v>
       </c>
       <c r="I8" s="9" t="s">
-        <v>286</v>
+        <v>295</v>
       </c>
       <c r="K8" s="14" t="s">
-        <v>358</v>
+        <v>367</v>
       </c>
       <c r="L8" s="4" t="s">
-        <v>284</v>
+        <v>293</v>
       </c>
       <c r="M8" s="15"/>
     </row>
@@ -4701,17 +4694,17 @@
       <c r="F9" s="10"/>
       <c r="G9" s="10"/>
       <c r="H9" s="8" t="s">
-        <v>359</v>
+        <v>368</v>
       </c>
       <c r="I9" s="11"/>
       <c r="K9" s="16">
         <v>1</v>
       </c>
       <c r="L9" s="16" t="s">
-        <v>288</v>
+        <v>297</v>
       </c>
       <c r="M9" s="17" t="s">
-        <v>352</v>
+        <v>361</v>
       </c>
     </row>
     <row r="10" ht="16.5" spans="4:13">
@@ -4720,13 +4713,13 @@
       <c r="F10" s="10"/>
       <c r="G10" s="10"/>
       <c r="H10" s="8" t="s">
-        <v>360</v>
+        <v>369</v>
       </c>
       <c r="I10" s="11"/>
       <c r="K10" s="18"/>
       <c r="L10" s="18"/>
       <c r="M10" s="17" t="s">
-        <v>353</v>
+        <v>362</v>
       </c>
     </row>
     <row r="11" ht="16.5" spans="4:13">
@@ -4735,13 +4728,13 @@
       <c r="F11" s="12"/>
       <c r="G11" s="12"/>
       <c r="H11" s="8" t="s">
-        <v>361</v>
+        <v>370</v>
       </c>
       <c r="I11" s="13"/>
       <c r="K11" s="18"/>
       <c r="L11" s="18"/>
       <c r="M11" s="17" t="s">
-        <v>354</v>
+        <v>363</v>
       </c>
     </row>
     <row r="12" ht="16.5" spans="4:13">
@@ -4749,7 +4742,7 @@
         <v>3</v>
       </c>
       <c r="E12" s="20" t="s">
-        <v>362</v>
+        <v>371</v>
       </c>
       <c r="F12" s="20">
         <v>3</v>
@@ -4758,15 +4751,15 @@
         <v>3</v>
       </c>
       <c r="H12" s="21" t="s">
-        <v>363</v>
+        <v>372</v>
       </c>
       <c r="I12" s="21" t="s">
-        <v>364</v>
+        <v>373</v>
       </c>
       <c r="K12" s="18"/>
       <c r="L12" s="18"/>
       <c r="M12" s="17" t="s">
-        <v>355</v>
+        <v>364</v>
       </c>
     </row>
     <row r="13" ht="16.5" spans="4:13">
@@ -4774,7 +4767,7 @@
         <v>4</v>
       </c>
       <c r="E13" s="22" t="s">
-        <v>365</v>
+        <v>374</v>
       </c>
       <c r="F13" s="22">
         <v>4</v>
@@ -4783,15 +4776,15 @@
         <v>4</v>
       </c>
       <c r="H13" s="24" t="s">
-        <v>366</v>
+        <v>375</v>
       </c>
       <c r="I13" s="24" t="s">
-        <v>367</v>
+        <v>376</v>
       </c>
       <c r="K13" s="19"/>
       <c r="L13" s="19"/>
       <c r="M13" s="25" t="s">
-        <v>356</v>
+        <v>365</v>
       </c>
     </row>
     <row r="14" ht="16.5" spans="4:13">
@@ -4802,19 +4795,19 @@
         <v>5</v>
       </c>
       <c r="H14" s="24" t="s">
-        <v>366</v>
+        <v>375</v>
       </c>
       <c r="I14" s="24" t="s">
-        <v>368</v>
+        <v>377</v>
       </c>
       <c r="K14" s="16">
         <v>2</v>
       </c>
       <c r="L14" s="16" t="s">
-        <v>286</v>
+        <v>295</v>
       </c>
       <c r="M14" s="17" t="s">
-        <v>352</v>
+        <v>361</v>
       </c>
     </row>
     <row r="15" ht="16.5" spans="4:13">
@@ -4822,7 +4815,7 @@
         <v>5</v>
       </c>
       <c r="E15" s="22" t="s">
-        <v>369</v>
+        <v>378</v>
       </c>
       <c r="F15" s="22">
         <v>5</v>
@@ -4831,15 +4824,15 @@
         <v>4</v>
       </c>
       <c r="H15" s="24" t="s">
-        <v>366</v>
+        <v>375</v>
       </c>
       <c r="I15" s="24" t="s">
-        <v>367</v>
+        <v>376</v>
       </c>
       <c r="K15" s="18"/>
       <c r="L15" s="18"/>
       <c r="M15" s="17" t="s">
-        <v>359</v>
+        <v>368</v>
       </c>
     </row>
     <row r="16" ht="16.5" spans="4:13">
@@ -4850,15 +4843,15 @@
         <v>5</v>
       </c>
       <c r="H16" s="24" t="s">
-        <v>366</v>
+        <v>375</v>
       </c>
       <c r="I16" s="24" t="s">
-        <v>368</v>
+        <v>377</v>
       </c>
       <c r="K16" s="18"/>
       <c r="L16" s="18"/>
       <c r="M16" s="17" t="s">
-        <v>360</v>
+        <v>369</v>
       </c>
     </row>
     <row r="17" ht="16.5" spans="4:14">
@@ -4869,15 +4862,15 @@
         <v>6</v>
       </c>
       <c r="H17" s="24" t="s">
-        <v>370</v>
+        <v>379</v>
       </c>
       <c r="I17" s="24" t="s">
-        <v>371</v>
+        <v>380</v>
       </c>
       <c r="K17" s="19"/>
       <c r="L17" s="19"/>
       <c r="M17" s="25" t="s">
-        <v>361</v>
+        <v>370</v>
       </c>
     </row>
     <row r="18" ht="16.5" spans="4:14">
@@ -4885,7 +4878,7 @@
         <v>6</v>
       </c>
       <c r="E18" s="23" t="s">
-        <v>372</v>
+        <v>381</v>
       </c>
       <c r="F18" s="22">
         <v>6</v>
@@ -4894,19 +4887,19 @@
         <v>4</v>
       </c>
       <c r="H18" s="28" t="s">
-        <v>366</v>
+        <v>375</v>
       </c>
       <c r="I18" s="28" t="s">
-        <v>367</v>
+        <v>376</v>
       </c>
       <c r="K18" s="19">
         <v>3</v>
       </c>
       <c r="L18" s="20" t="s">
-        <v>373</v>
+        <v>382</v>
       </c>
       <c r="M18" s="25" t="s">
-        <v>366</v>
+        <v>375</v>
       </c>
     </row>
     <row r="19" ht="16.5" spans="4:14">
@@ -4914,7 +4907,7 @@
         <v>7</v>
       </c>
       <c r="E19" s="23" t="s">
-        <v>374</v>
+        <v>383</v>
       </c>
       <c r="F19" s="26"/>
       <c r="G19" s="26"/>
@@ -4924,10 +4917,10 @@
         <v>4</v>
       </c>
       <c r="L19" s="20" t="s">
-        <v>364</v>
+        <v>373</v>
       </c>
       <c r="M19" s="25" t="s">
-        <v>366</v>
+        <v>375</v>
       </c>
     </row>
     <row r="20" ht="16.5" spans="4:14">
@@ -4935,7 +4928,7 @@
         <v>8</v>
       </c>
       <c r="E20" s="23" t="s">
-        <v>375</v>
+        <v>384</v>
       </c>
       <c r="F20" s="22">
         <v>8</v>
@@ -4944,10 +4937,10 @@
         <v>8</v>
       </c>
       <c r="H20" s="28" t="s">
-        <v>376</v>
+        <v>385</v>
       </c>
       <c r="I20" s="28" t="s">
-        <v>377</v>
+        <v>386</v>
       </c>
     </row>
     <row r="21" ht="16.5" spans="4:14">
@@ -4955,7 +4948,7 @@
         <v>9</v>
       </c>
       <c r="E21" s="23" t="s">
-        <v>378</v>
+        <v>387</v>
       </c>
       <c r="F21" s="26"/>
       <c r="G21" s="26"/>
@@ -4967,7 +4960,7 @@
         <v>10</v>
       </c>
       <c r="E22" s="23" t="s">
-        <v>379</v>
+        <v>388</v>
       </c>
       <c r="F22" s="23">
         <v>10</v>
@@ -4976,10 +4969,10 @@
         <v>10</v>
       </c>
       <c r="H22" s="24" t="s">
-        <v>366</v>
+        <v>375</v>
       </c>
       <c r="I22" s="24" t="s">
-        <v>380</v>
+        <v>389</v>
       </c>
     </row>
     <row r="23" ht="16.5" spans="4:14">
@@ -5006,16 +4999,16 @@
       <c r="H25" s="23"/>
       <c r="I25" s="23"/>
       <c r="K25" s="30" t="s">
-        <v>381</v>
+        <v>390</v>
       </c>
       <c r="L25" s="31" t="s">
-        <v>284</v>
+        <v>293</v>
       </c>
       <c r="M25" s="31" t="s">
-        <v>382</v>
+        <v>391</v>
       </c>
       <c r="N25" s="31" t="s">
-        <v>383</v>
+        <v>392</v>
       </c>
     </row>
     <row r="26" ht="32.25" spans="4:14">
@@ -5026,40 +5019,40 @@
       <c r="H26" s="23"/>
       <c r="I26" s="23"/>
       <c r="K26" s="32" t="s">
-        <v>348</v>
+        <v>357</v>
       </c>
       <c r="L26" s="33" t="s">
-        <v>384</v>
+        <v>393</v>
       </c>
       <c r="M26" s="33"/>
       <c r="N26" s="33" t="s">
-        <v>385</v>
+        <v>394</v>
       </c>
     </row>
     <row r="27" ht="16.5" spans="4:14">
       <c r="D27" s="19"/>
       <c r="E27" s="23" t="s">
-        <v>386</v>
+        <v>395</v>
       </c>
       <c r="F27" s="23"/>
       <c r="G27" s="23"/>
       <c r="H27" s="23"/>
       <c r="I27" s="23"/>
       <c r="K27" s="32" t="s">
-        <v>283</v>
+        <v>292</v>
       </c>
       <c r="L27" s="33" t="s">
-        <v>387</v>
+        <v>396</v>
       </c>
       <c r="M27" s="33"/>
       <c r="N27" s="33" t="s">
-        <v>385</v>
+        <v>394</v>
       </c>
     </row>
     <row r="28" ht="16.5" spans="4:14">
       <c r="D28" s="34"/>
       <c r="E28" s="23" t="s">
-        <v>386</v>
+        <v>395</v>
       </c>
       <c r="F28" s="23"/>
       <c r="G28" s="23"/>
@@ -5069,45 +5062,45 @@
     <row r="37" ht="14.25"/>
     <row r="38" ht="16.5" spans="4:10">
       <c r="D38" s="35" t="s">
-        <v>388</v>
+        <v>397</v>
       </c>
       <c r="E38" s="36" t="s">
-        <v>389</v>
+        <v>398</v>
       </c>
       <c r="F38" s="36" t="s">
-        <v>390</v>
+        <v>399</v>
       </c>
       <c r="G38" s="36" t="s">
-        <v>391</v>
+        <v>400</v>
       </c>
       <c r="H38" s="37" t="s">
-        <v>392</v>
+        <v>401</v>
       </c>
       <c r="I38" s="38" t="s">
-        <v>389</v>
+        <v>398</v>
       </c>
       <c r="J38" s="39" t="s">
-        <v>393</v>
+        <v>402</v>
       </c>
     </row>
     <row r="39" ht="16.5" spans="4:10">
       <c r="D39" s="40" t="s">
-        <v>393</v>
+        <v>402</v>
       </c>
       <c r="E39" s="41" t="s">
-        <v>394</v>
+        <v>403</v>
       </c>
       <c r="F39" s="42" t="s">
-        <v>395</v>
+        <v>404</v>
       </c>
       <c r="G39" s="41" t="s">
-        <v>396</v>
+        <v>405</v>
       </c>
       <c r="H39" s="19">
         <v>1</v>
       </c>
       <c r="I39" s="20" t="s">
-        <v>397</v>
+        <v>406</v>
       </c>
       <c r="J39" s="20">
         <v>2</v>
@@ -5117,14 +5110,14 @@
       <c r="D40" s="43"/>
       <c r="E40" s="44"/>
       <c r="F40" s="42" t="s">
-        <v>398</v>
+        <v>407</v>
       </c>
       <c r="G40" s="44"/>
       <c r="H40" s="19">
         <v>2</v>
       </c>
       <c r="I40" s="20" t="s">
-        <v>399</v>
+        <v>408</v>
       </c>
       <c r="J40" s="20">
         <v>2</v>
@@ -5134,7 +5127,7 @@
       <c r="D41" s="43"/>
       <c r="E41" s="44"/>
       <c r="F41" s="45" t="s">
-        <v>400</v>
+        <v>409</v>
       </c>
       <c r="G41" s="44"/>
     </row>
@@ -5142,7 +5135,7 @@
       <c r="D42" s="43"/>
       <c r="E42" s="44"/>
       <c r="F42" s="46" t="s">
-        <v>401</v>
+        <v>410</v>
       </c>
       <c r="G42" s="44"/>
     </row>
@@ -5150,7 +5143,7 @@
       <c r="D43" s="43"/>
       <c r="E43" s="44"/>
       <c r="F43" s="46" t="s">
-        <v>402</v>
+        <v>411</v>
       </c>
       <c r="G43" s="44"/>
     </row>
@@ -5158,7 +5151,7 @@
       <c r="D44" s="43"/>
       <c r="E44" s="44"/>
       <c r="F44" s="46" t="s">
-        <v>403</v>
+        <v>412</v>
       </c>
       <c r="G44" s="44"/>
     </row>
@@ -5166,7 +5159,7 @@
       <c r="D45" s="43"/>
       <c r="E45" s="44"/>
       <c r="F45" s="46" t="s">
-        <v>404</v>
+        <v>413</v>
       </c>
       <c r="G45" s="44"/>
     </row>
@@ -5174,7 +5167,7 @@
       <c r="D46" s="43"/>
       <c r="E46" s="44"/>
       <c r="F46" s="46" t="s">
-        <v>405</v>
+        <v>414</v>
       </c>
       <c r="G46" s="44"/>
     </row>
@@ -5182,7 +5175,7 @@
       <c r="D47" s="43"/>
       <c r="E47" s="44"/>
       <c r="F47" s="46" t="s">
-        <v>406</v>
+        <v>415</v>
       </c>
       <c r="G47" s="44"/>
     </row>
@@ -5190,7 +5183,7 @@
       <c r="D48" s="43"/>
       <c r="E48" s="44"/>
       <c r="F48" s="46" t="s">
-        <v>407</v>
+        <v>416</v>
       </c>
       <c r="G48" s="44"/>
     </row>
@@ -5198,7 +5191,7 @@
       <c r="D49" s="43"/>
       <c r="E49" s="44"/>
       <c r="F49" s="46" t="s">
-        <v>408</v>
+        <v>417</v>
       </c>
       <c r="G49" s="44"/>
     </row>
@@ -5206,7 +5199,7 @@
       <c r="D50" s="43"/>
       <c r="E50" s="44"/>
       <c r="F50" s="46" t="s">
-        <v>409</v>
+        <v>418</v>
       </c>
       <c r="G50" s="44"/>
     </row>
@@ -5214,7 +5207,7 @@
       <c r="D51" s="43"/>
       <c r="E51" s="44"/>
       <c r="F51" s="46" t="s">
-        <v>410</v>
+        <v>419</v>
       </c>
       <c r="G51" s="44"/>
     </row>
@@ -5222,23 +5215,23 @@
       <c r="D52" s="47"/>
       <c r="E52" s="48"/>
       <c r="F52" s="49" t="s">
-        <v>411</v>
+        <v>420</v>
       </c>
       <c r="G52" s="48"/>
     </row>
     <row r="53" ht="21" spans="4:7">
       <c r="D53" s="50" t="s">
-        <v>412</v>
+        <v>421</v>
       </c>
     </row>
     <row r="54" ht="15.75" spans="4:7">
       <c r="D54" s="51" t="s">
-        <v>395</v>
+        <v>404</v>
       </c>
     </row>
     <row r="55" ht="15.75" spans="4:7">
       <c r="D55" s="52" t="s">
-        <v>413</v>
+        <v>422</v>
       </c>
     </row>
   </sheetData>
@@ -5283,356 +5276,201 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:I13"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <dimension ref="A1:H7"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="6" outlineLevelCol="7"/>
   <cols>
     <col min="1" max="1" width="6.66666666666667" style="81" customWidth="1"/>
     <col min="2" max="2" width="43.775" style="81" customWidth="1"/>
     <col min="3" max="3" width="43.5" style="81" customWidth="1"/>
-    <col min="4" max="4" width="10.775" style="81" customWidth="1"/>
-    <col min="5" max="5" width="13.1083333333333" style="81" customWidth="1"/>
+    <col min="4" max="4" width="12.9666666666667" style="81" customWidth="1"/>
+    <col min="5" max="5" width="22.5" style="81" customWidth="1"/>
     <col min="6" max="6" width="34" style="81" customWidth="1"/>
     <col min="7" max="7" width="16" style="81" customWidth="1"/>
     <col min="8" max="8" width="51.9416666666667" style="81" customWidth="1"/>
-    <col min="9" max="9" width="48.4666666666667" style="81" customWidth="1"/>
-    <col min="10" max="16384" width="9" style="81"/>
+    <col min="9" max="16384" width="9" style="81"/>
   </cols>
   <sheetData>
-    <row r="1" ht="33" customHeight="1" spans="1:9">
-      <c r="A1" s="106" t="s">
+    <row r="1" ht="33" customHeight="1" spans="1:8">
+      <c r="A1" s="107" t="s">
         <v>98</v>
       </c>
-      <c r="B1" s="106" t="s">
+      <c r="B1" s="107" t="s">
         <v>99</v>
       </c>
-      <c r="C1" s="106" t="s">
+      <c r="C1" s="107" t="s">
         <v>100</v>
       </c>
-      <c r="D1" s="106" t="s">
+      <c r="D1" s="107" t="s">
         <v>101</v>
       </c>
-      <c r="E1" s="106" t="s">
+      <c r="E1" s="107" t="s">
         <v>102</v>
       </c>
-      <c r="F1" s="106" t="s">
+      <c r="F1" s="107" t="s">
         <v>103</v>
       </c>
-      <c r="G1" s="106" t="s">
+      <c r="G1" s="107" t="s">
         <v>104</v>
       </c>
-      <c r="H1" s="106" t="s">
+      <c r="H1" s="107" t="s">
         <v>105</v>
       </c>
-      <c r="I1" s="107" t="s">
+    </row>
+    <row r="2" s="106" customFormat="1" ht="75" spans="1:8">
+      <c r="A2" s="108">
+        <v>5001</v>
+      </c>
+      <c r="B2" s="108" t="s">
         <v>106</v>
       </c>
-    </row>
-    <row r="2" s="105" customFormat="1" ht="141.75" spans="1:9">
-      <c r="A2" s="102">
-        <v>1001</v>
-      </c>
-      <c r="B2" s="102" t="s">
+      <c r="C2" s="109" t="s">
         <v>107</v>
       </c>
-      <c r="C2" s="108" t="s">
+      <c r="D2" s="108">
+        <v>1</v>
+      </c>
+      <c r="E2" s="101">
+        <v>501</v>
+      </c>
+      <c r="F2" s="101" t="s">
         <v>108</v>
       </c>
-      <c r="D2" s="102">
-        <v>1</v>
-      </c>
-      <c r="E2" s="102">
-        <v>1002</v>
-      </c>
-      <c r="F2" s="102" t="s">
+      <c r="G2" s="101" t="s">
         <v>109</v>
       </c>
-      <c r="G2" s="102" t="s">
+      <c r="H2" s="102" t="s">
         <v>110</v>
       </c>
-      <c r="H2" s="102" t="s">
+    </row>
+    <row r="3" s="106" customFormat="1" ht="75" spans="1:8">
+      <c r="A3" s="108">
+        <v>5002</v>
+      </c>
+      <c r="B3" s="108" t="s">
         <v>111</v>
       </c>
-      <c r="I2" s="108" t="s">
+      <c r="C3" s="109" t="s">
         <v>112</v>
       </c>
-    </row>
-    <row r="3" s="105" customFormat="1" ht="81" spans="1:9">
-      <c r="A3" s="109">
-        <v>1002</v>
-      </c>
-      <c r="B3" s="109" t="s">
+      <c r="D3" s="108">
+        <v>2</v>
+      </c>
+      <c r="E3" s="101">
+        <v>501</v>
+      </c>
+      <c r="F3" s="101" t="s">
+        <v>108</v>
+      </c>
+      <c r="G3" s="101" t="s">
+        <v>109</v>
+      </c>
+      <c r="H3" s="102" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="4" s="106" customFormat="1" ht="75" spans="1:8">
+      <c r="A4" s="108">
+        <v>5003</v>
+      </c>
+      <c r="B4" s="108" t="s">
         <v>113</v>
       </c>
-      <c r="C3" s="110" t="s">
+      <c r="C4" s="109" t="s">
         <v>114</v>
       </c>
-      <c r="D3" s="109">
-        <v>2</v>
-      </c>
-      <c r="E3" s="102">
+      <c r="D4" s="108">
+        <v>3</v>
+      </c>
+      <c r="E4" s="101">
+        <v>501</v>
+      </c>
+      <c r="F4" s="101" t="s">
+        <v>108</v>
+      </c>
+      <c r="G4" s="101" t="s">
+        <v>109</v>
+      </c>
+      <c r="H4" s="102" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="5" s="106" customFormat="1" ht="75" spans="1:8">
+      <c r="A5" s="108">
+        <v>5004</v>
+      </c>
+      <c r="B5" s="108" t="s">
+        <v>115</v>
+      </c>
+      <c r="C5" s="109" t="s">
+        <v>116</v>
+      </c>
+      <c r="D5" s="108">
+        <v>4</v>
+      </c>
+      <c r="E5" s="101">
+        <v>501</v>
+      </c>
+      <c r="F5" s="101" t="s">
+        <v>108</v>
+      </c>
+      <c r="G5" s="101" t="s">
+        <v>109</v>
+      </c>
+      <c r="H5" s="102" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="6" s="106" customFormat="1" ht="56.25" spans="1:8">
+      <c r="A6" s="108">
+        <v>5005</v>
+      </c>
+      <c r="B6" s="108" t="s">
+        <v>117</v>
+      </c>
+      <c r="C6" s="109" t="s">
+        <v>118</v>
+      </c>
+      <c r="D6" s="108">
+        <v>5</v>
+      </c>
+      <c r="E6" s="108">
         <v>502</v>
       </c>
-      <c r="F3" s="102" t="s">
-        <v>115</v>
-      </c>
-      <c r="G3" s="102" t="s">
-        <v>110</v>
-      </c>
-      <c r="H3" s="102" t="s">
-        <v>116</v>
-      </c>
-      <c r="I3" s="108" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="4" s="105" customFormat="1" ht="20.25" spans="1:9">
-      <c r="A4" s="111"/>
-      <c r="B4" s="111"/>
-      <c r="C4" s="112"/>
-      <c r="D4" s="111"/>
-      <c r="E4" s="102">
-        <v>515</v>
-      </c>
-      <c r="F4" s="102" t="s">
-        <v>118</v>
-      </c>
-      <c r="G4" s="102" t="s">
-        <v>110</v>
-      </c>
-      <c r="H4" s="108" t="s">
+      <c r="F6" s="108" t="s">
         <v>119</v>
       </c>
-      <c r="I4" s="108"/>
-    </row>
-    <row r="5" s="105" customFormat="1" ht="141.75" spans="1:9">
-      <c r="A5" s="102">
-        <v>1003</v>
-      </c>
-      <c r="B5" s="102" t="s">
+      <c r="G6" s="108" t="s">
+        <v>109</v>
+      </c>
+      <c r="H6" s="102" t="s">
         <v>120</v>
       </c>
-      <c r="C5" s="108" t="s">
+    </row>
+    <row r="7" s="106" customFormat="1" ht="20.25" spans="1:8">
+      <c r="A7" s="108"/>
+      <c r="B7" s="108"/>
+      <c r="C7" s="109"/>
+      <c r="D7" s="108"/>
+      <c r="E7" s="101">
+        <v>503</v>
+      </c>
+      <c r="F7" s="101" t="s">
         <v>121</v>
       </c>
-      <c r="D5" s="102">
-        <v>3</v>
-      </c>
-      <c r="E5" s="102">
-        <v>1002</v>
-      </c>
-      <c r="F5" s="102" t="s">
+      <c r="G7" s="101" t="s">
         <v>109</v>
       </c>
-      <c r="G5" s="102" t="s">
-        <v>110</v>
-      </c>
-      <c r="H5" s="102" t="s">
-        <v>111</v>
-      </c>
-      <c r="I5" s="108" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="6" s="105" customFormat="1" ht="141.75" spans="1:9">
-      <c r="A6" s="102">
-        <v>1004</v>
-      </c>
-      <c r="B6" s="102" t="s">
+      <c r="H7" s="109" t="s">
         <v>122</v>
       </c>
-      <c r="C6" s="108" t="s">
-        <v>123</v>
-      </c>
-      <c r="D6" s="102">
-        <v>4</v>
-      </c>
-      <c r="E6" s="102">
-        <v>1002</v>
-      </c>
-      <c r="F6" s="102" t="s">
-        <v>109</v>
-      </c>
-      <c r="G6" s="102" t="s">
-        <v>110</v>
-      </c>
-      <c r="H6" s="102" t="s">
-        <v>111</v>
-      </c>
-      <c r="I6" s="108" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="7" s="105" customFormat="1" ht="141.75" spans="1:9">
-      <c r="A7" s="102">
-        <v>1005</v>
-      </c>
-      <c r="B7" s="102" t="s">
-        <v>124</v>
-      </c>
-      <c r="C7" s="108" t="s">
-        <v>125</v>
-      </c>
-      <c r="D7" s="102">
-        <v>5</v>
-      </c>
-      <c r="E7" s="102">
-        <v>1002</v>
-      </c>
-      <c r="F7" s="102" t="s">
-        <v>109</v>
-      </c>
-      <c r="G7" s="102" t="s">
-        <v>110</v>
-      </c>
-      <c r="H7" s="102" t="s">
-        <v>111</v>
-      </c>
-      <c r="I7" s="108" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="8" s="105" customFormat="1" ht="20.25" spans="1:9">
-      <c r="A8" s="102">
-        <v>2001</v>
-      </c>
-      <c r="B8" s="102" t="s">
-        <v>126</v>
-      </c>
-      <c r="C8" s="108" t="s">
-        <v>127</v>
-      </c>
-      <c r="D8" s="102">
-        <v>21</v>
-      </c>
-      <c r="E8" s="103">
-        <v>503</v>
-      </c>
-      <c r="F8" s="103" t="s">
-        <v>128</v>
-      </c>
-      <c r="G8" s="103" t="s">
-        <v>129</v>
-      </c>
-      <c r="H8" s="103" t="s">
-        <v>130</v>
-      </c>
-      <c r="I8" s="113"/>
-    </row>
-    <row r="9" s="105" customFormat="1" ht="45" customHeight="1" spans="1:9">
-      <c r="A9" s="109">
-        <v>2002</v>
-      </c>
-      <c r="B9" s="109" t="s">
-        <v>131</v>
-      </c>
-      <c r="C9" s="110" t="s">
-        <v>132</v>
-      </c>
-      <c r="D9" s="109">
-        <v>22</v>
-      </c>
-      <c r="E9" s="95">
-        <v>518</v>
-      </c>
-      <c r="F9" s="102" t="s">
-        <v>133</v>
-      </c>
-      <c r="G9" s="103" t="s">
-        <v>110</v>
-      </c>
-      <c r="H9" s="102" t="s">
-        <v>134</v>
-      </c>
-      <c r="I9" s="96"/>
-    </row>
-    <row r="10" s="105" customFormat="1" ht="45" customHeight="1" spans="1:9">
-      <c r="A10" s="114"/>
-      <c r="B10" s="114"/>
-      <c r="C10" s="115"/>
-      <c r="D10" s="114"/>
-      <c r="E10" s="95">
-        <v>519</v>
-      </c>
-      <c r="F10" s="102" t="s">
-        <v>135</v>
-      </c>
-      <c r="G10" s="102" t="s">
-        <v>129</v>
-      </c>
-      <c r="H10" s="102" t="s">
-        <v>136</v>
-      </c>
-      <c r="I10" s="96"/>
-    </row>
-    <row r="11" s="105" customFormat="1" ht="45" customHeight="1" spans="1:9">
-      <c r="A11" s="109">
-        <v>2003</v>
-      </c>
-      <c r="B11" s="109" t="s">
-        <v>137</v>
-      </c>
-      <c r="C11" s="110" t="s">
-        <v>138</v>
-      </c>
-      <c r="D11" s="109">
-        <v>23</v>
-      </c>
-      <c r="E11" s="95">
-        <v>518</v>
-      </c>
-      <c r="F11" s="102" t="s">
-        <v>133</v>
-      </c>
-      <c r="G11" s="103" t="s">
-        <v>110</v>
-      </c>
-      <c r="H11" s="102" t="s">
-        <v>134</v>
-      </c>
-      <c r="I11" s="96"/>
-    </row>
-    <row r="12" s="105" customFormat="1" ht="45" customHeight="1" spans="1:9">
-      <c r="A12" s="114"/>
-      <c r="B12" s="114"/>
-      <c r="C12" s="115"/>
-      <c r="D12" s="114"/>
-      <c r="E12" s="95">
-        <v>519</v>
-      </c>
-      <c r="F12" s="102" t="s">
-        <v>135</v>
-      </c>
-      <c r="G12" s="102" t="s">
-        <v>129</v>
-      </c>
-      <c r="H12" s="102" t="s">
-        <v>136</v>
-      </c>
-      <c r="I12" s="96"/>
-    </row>
-    <row r="13" spans="1:9">
-      <c r="F13" s="116"/>
     </row>
   </sheetData>
-  <mergeCells count="12">
-    <mergeCell ref="A3:A4"/>
-    <mergeCell ref="A9:A10"/>
-    <mergeCell ref="A11:A12"/>
-    <mergeCell ref="B3:B4"/>
-    <mergeCell ref="B9:B10"/>
-    <mergeCell ref="B11:B12"/>
-    <mergeCell ref="C3:C4"/>
-    <mergeCell ref="C9:C10"/>
-    <mergeCell ref="C11:C12"/>
-    <mergeCell ref="D3:D4"/>
-    <mergeCell ref="D9:D10"/>
-    <mergeCell ref="D11:D12"/>
+  <mergeCells count="4">
+    <mergeCell ref="A6:A7"/>
+    <mergeCell ref="B6:B7"/>
+    <mergeCell ref="C6:C7"/>
+    <mergeCell ref="D6:D7"/>
   </mergeCells>
-  <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I4">
-      <formula1>"x, "</formula1>
-    </dataValidation>
-  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>
@@ -5643,355 +5481,356 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F21"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18.75" outlineLevelCol="5"/>
+  <dimension ref="A1:G20"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18.75" outlineLevelCol="6"/>
   <cols>
     <col min="1" max="1" width="6.66666666666667" style="100" customWidth="1"/>
     <col min="2" max="2" width="29.8833333333333" style="100" customWidth="1"/>
     <col min="3" max="3" width="16" style="100" customWidth="1"/>
-    <col min="4" max="4" width="48.25" style="100" customWidth="1"/>
-    <col min="5" max="5" width="50.5" style="100" customWidth="1"/>
-    <col min="6" max="6" width="36.375" style="100" customWidth="1"/>
-    <col min="7" max="16384" width="9" style="100"/>
+    <col min="4" max="5" width="25.125" style="100" customWidth="1"/>
+    <col min="6" max="6" width="57.5" style="100" customWidth="1"/>
+    <col min="7" max="7" width="36.375" style="100" customWidth="1"/>
+    <col min="8" max="16384" width="9" style="100"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
-      <c r="A1" s="93" t="s">
+    <row r="1" spans="1:7">
+      <c r="A1" s="91" t="s">
+        <v>123</v>
+      </c>
+      <c r="B1" s="91" t="s">
+        <v>124</v>
+      </c>
+      <c r="C1" s="91" t="s">
+        <v>104</v>
+      </c>
+      <c r="D1" s="91" t="s">
+        <v>125</v>
+      </c>
+      <c r="E1" s="91" t="s">
+        <v>126</v>
+      </c>
+      <c r="F1" s="91" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="2" s="99" customFormat="1" ht="75" spans="1:7">
+      <c r="A2" s="101">
+        <v>501</v>
+      </c>
+      <c r="B2" s="101" t="s">
+        <v>108</v>
+      </c>
+      <c r="C2" s="101" t="s">
+        <v>109</v>
+      </c>
+      <c r="D2" s="101"/>
+      <c r="E2" s="101"/>
+      <c r="F2" s="102" t="s">
+        <v>110</v>
+      </c>
+      <c r="G2" s="100"/>
+    </row>
+    <row r="3" s="100" customFormat="1" ht="56.25" spans="1:7">
+      <c r="A3" s="101">
+        <v>502</v>
+      </c>
+      <c r="B3" s="101" t="s">
+        <v>119</v>
+      </c>
+      <c r="C3" s="101" t="s">
+        <v>109</v>
+      </c>
+      <c r="D3" s="101"/>
+      <c r="E3" s="101"/>
+      <c r="F3" s="102" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="4" s="100" customFormat="1" spans="1:7">
+      <c r="A4" s="101">
+        <v>503</v>
+      </c>
+      <c r="B4" s="101" t="s">
+        <v>121</v>
+      </c>
+      <c r="C4" s="101" t="s">
+        <v>109</v>
+      </c>
+      <c r="D4" s="101"/>
+      <c r="E4" s="101"/>
+      <c r="F4" s="101" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="5" s="100" customFormat="1" spans="1:7">
+      <c r="A5" s="101">
+        <v>504</v>
+      </c>
+      <c r="B5" s="101" t="s">
+        <v>128</v>
+      </c>
+      <c r="C5" s="101" t="s">
+        <v>129</v>
+      </c>
+      <c r="D5" s="101"/>
+      <c r="E5" s="101"/>
+      <c r="F5" s="101" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="6" s="100" customFormat="1" spans="1:7">
+      <c r="A6" s="101">
+        <v>505</v>
+      </c>
+      <c r="B6" s="101" t="s">
+        <v>131</v>
+      </c>
+      <c r="C6" s="101" t="s">
+        <v>129</v>
+      </c>
+      <c r="D6" s="101"/>
+      <c r="E6" s="102" t="s">
+        <v>132</v>
+      </c>
+      <c r="F6" s="101" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="7" s="100" customFormat="1" spans="1:7">
+      <c r="A7" s="101">
+        <v>506</v>
+      </c>
+      <c r="B7" s="101" t="s">
+        <v>134</v>
+      </c>
+      <c r="C7" s="101" t="s">
+        <v>129</v>
+      </c>
+      <c r="D7" s="101"/>
+      <c r="E7" s="102"/>
+      <c r="F7" s="101" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="8" s="100" customFormat="1" spans="1:7">
+      <c r="A8" s="101">
+        <v>511</v>
+      </c>
+      <c r="B8" s="101" t="s">
+        <v>136</v>
+      </c>
+      <c r="C8" s="101" t="s">
+        <v>129</v>
+      </c>
+      <c r="D8" s="101"/>
+      <c r="E8" s="102"/>
+      <c r="F8" s="101" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="9" s="100" customFormat="1" spans="1:7">
+      <c r="A9" s="101">
+        <v>512</v>
+      </c>
+      <c r="B9" s="101" t="s">
+        <v>138</v>
+      </c>
+      <c r="C9" s="101" t="s">
+        <v>109</v>
+      </c>
+      <c r="D9" s="101"/>
+      <c r="E9" s="102"/>
+      <c r="F9" s="101" t="s">
         <v>139</v>
       </c>
-      <c r="B1" s="93" t="s">
+    </row>
+    <row r="10" s="100" customFormat="1" spans="1:7">
+      <c r="A10" s="101">
+        <v>513</v>
+      </c>
+      <c r="B10" s="101" t="s">
         <v>140</v>
       </c>
-      <c r="C1" s="93" t="s">
+      <c r="C10" s="101" t="s">
+        <v>109</v>
+      </c>
+      <c r="D10" s="101"/>
+      <c r="E10" s="102"/>
+      <c r="F10" s="101" t="s">
         <v>141</v>
       </c>
-      <c r="D1" s="93" t="s">
+    </row>
+    <row r="11" s="100" customFormat="1" spans="1:7">
+      <c r="A11" s="101">
+        <v>514</v>
+      </c>
+      <c r="B11" s="101" t="s">
         <v>142</v>
       </c>
-      <c r="E1" s="93" t="s">
+      <c r="C11" s="101" t="s">
+        <v>109</v>
+      </c>
+      <c r="D11" s="101"/>
+      <c r="E11" s="102">
+        <v>1</v>
+      </c>
+      <c r="F11" s="101" t="s">
         <v>143</v>
       </c>
     </row>
-    <row r="2" s="99" customFormat="1" ht="75" spans="1:6">
-      <c r="A2" s="95">
-        <v>502</v>
-      </c>
-      <c r="B2" s="95" t="s">
-        <v>115</v>
-      </c>
-      <c r="C2" s="95" t="s">
-        <v>110</v>
-      </c>
-      <c r="D2" s="95" t="s">
-        <v>116</v>
-      </c>
-      <c r="E2" s="101" t="s">
+    <row r="12" s="100" customFormat="1" spans="1:7">
+      <c r="A12" s="101">
+        <v>515</v>
+      </c>
+      <c r="B12" s="101" t="s">
         <v>144</v>
       </c>
-      <c r="F2" s="100"/>
-    </row>
-    <row r="3" s="100" customFormat="1" spans="1:6">
-      <c r="A3" s="95">
-        <v>503</v>
-      </c>
-      <c r="B3" s="95" t="s">
-        <v>128</v>
-      </c>
-      <c r="C3" s="95" t="s">
+      <c r="C12" s="101" t="s">
+        <v>109</v>
+      </c>
+      <c r="D12" s="101"/>
+      <c r="E12" s="102">
+        <v>2</v>
+      </c>
+      <c r="F12" s="101" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="13" s="99" customFormat="1" spans="1:7">
+      <c r="A13" s="101">
+        <v>516</v>
+      </c>
+      <c r="B13" s="101" t="s">
+        <v>146</v>
+      </c>
+      <c r="C13" s="101" t="s">
+        <v>109</v>
+      </c>
+      <c r="D13" s="101"/>
+      <c r="E13" s="102">
+        <v>3</v>
+      </c>
+      <c r="F13" s="101" t="s">
+        <v>147</v>
+      </c>
+      <c r="G13" s="100"/>
+    </row>
+    <row r="14" s="100" customFormat="1" spans="1:7">
+      <c r="A14" s="101">
+        <v>521</v>
+      </c>
+      <c r="B14" s="101" t="s">
+        <v>148</v>
+      </c>
+      <c r="C14" s="101" t="s">
+        <v>109</v>
+      </c>
+      <c r="D14" s="101"/>
+      <c r="E14" s="102"/>
+      <c r="F14" s="102" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="15" s="100" customFormat="1" spans="1:7">
+      <c r="A15" s="101">
+        <v>522</v>
+      </c>
+      <c r="B15" s="101" t="s">
+        <v>150</v>
+      </c>
+      <c r="C15" s="101" t="s">
         <v>129</v>
       </c>
-      <c r="D3" s="95" t="s">
-        <v>130</v>
-      </c>
-      <c r="E3" s="96"/>
-    </row>
-    <row r="4" s="100" customFormat="1" spans="1:6">
-      <c r="A4" s="95">
-        <v>504</v>
-      </c>
-      <c r="B4" s="95" t="s">
-        <v>145</v>
-      </c>
-      <c r="C4" s="95" t="s">
-        <v>110</v>
-      </c>
-      <c r="D4" s="95" t="s">
-        <v>146</v>
-      </c>
-      <c r="E4" s="96"/>
-    </row>
-    <row r="5" s="100" customFormat="1" spans="1:6">
-      <c r="A5" s="95">
-        <v>505</v>
-      </c>
-      <c r="B5" s="95" t="s">
-        <v>147</v>
-      </c>
-      <c r="C5" s="95" t="s">
+      <c r="D15" s="101"/>
+      <c r="E15" s="102"/>
+      <c r="F15" s="102" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="16" s="100" customFormat="1" spans="1:7">
+      <c r="A16" s="101">
+        <v>523</v>
+      </c>
+      <c r="B16" s="101" t="s">
+        <v>152</v>
+      </c>
+      <c r="C16" s="101" t="s">
+        <v>109</v>
+      </c>
+      <c r="D16" s="101"/>
+      <c r="E16" s="102"/>
+      <c r="F16" s="102" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="17" s="100" customFormat="1" spans="1:7">
+      <c r="A17" s="101">
+        <v>524</v>
+      </c>
+      <c r="B17" s="101" t="s">
+        <v>154</v>
+      </c>
+      <c r="C17" s="101" t="s">
         <v>129</v>
       </c>
-      <c r="D5" s="95" t="s">
-        <v>148</v>
-      </c>
-      <c r="E5" s="96"/>
-    </row>
-    <row r="6" s="100" customFormat="1" spans="1:6">
-      <c r="A6" s="95">
-        <v>506</v>
-      </c>
-      <c r="B6" s="95" t="s">
-        <v>149</v>
-      </c>
-      <c r="C6" s="95" t="s">
-        <v>110</v>
-      </c>
-      <c r="D6" s="95" t="s">
-        <v>150</v>
-      </c>
-      <c r="E6" s="96"/>
-    </row>
-    <row r="7" s="100" customFormat="1" spans="1:6">
-      <c r="A7" s="95">
-        <v>507</v>
-      </c>
-      <c r="B7" s="95" t="s">
-        <v>151</v>
-      </c>
-      <c r="C7" s="95" t="s">
-        <v>110</v>
-      </c>
-      <c r="D7" s="95" t="s">
-        <v>152</v>
-      </c>
-      <c r="E7" s="96"/>
-    </row>
-    <row r="8" s="100" customFormat="1" spans="1:6">
-      <c r="A8" s="95">
-        <v>508</v>
-      </c>
-      <c r="B8" s="95" t="s">
-        <v>153</v>
-      </c>
-      <c r="C8" s="95" t="s">
-        <v>129</v>
-      </c>
-      <c r="D8" s="95" t="s">
-        <v>154</v>
-      </c>
-      <c r="E8" s="96"/>
-    </row>
-    <row r="9" s="100" customFormat="1" spans="1:6">
-      <c r="A9" s="95">
-        <v>509</v>
-      </c>
-      <c r="B9" s="95" t="s">
+      <c r="D17" s="101"/>
+      <c r="E17" s="102"/>
+      <c r="F17" s="102" t="s">
         <v>155</v>
       </c>
-      <c r="C9" s="95" t="s">
-        <v>110</v>
-      </c>
-      <c r="D9" s="95" t="s">
+    </row>
+    <row r="18" s="100" customFormat="1" spans="1:7">
+      <c r="A18" s="101">
+        <v>525</v>
+      </c>
+      <c r="B18" s="101" t="s">
         <v>156</v>
       </c>
-      <c r="E9" s="96"/>
-    </row>
-    <row r="10" s="100" customFormat="1" ht="37.5" spans="1:6">
-      <c r="A10" s="95">
-        <v>510</v>
-      </c>
-      <c r="B10" s="95" t="s">
+      <c r="C18" s="101" t="s">
+        <v>109</v>
+      </c>
+      <c r="D18" s="101"/>
+      <c r="E18" s="102">
+        <v>2</v>
+      </c>
+      <c r="F18" s="102" t="s">
         <v>157</v>
       </c>
-      <c r="C10" s="95" t="s">
-        <v>110</v>
-      </c>
-      <c r="D10" s="95" t="s">
+    </row>
+    <row r="19" s="100" customFormat="1" spans="1:7">
+      <c r="A19" s="101">
+        <v>526</v>
+      </c>
+      <c r="B19" s="101" t="s">
         <v>158</v>
       </c>
-      <c r="E10" s="96" t="s">
+      <c r="C19" s="101" t="s">
+        <v>109</v>
+      </c>
+      <c r="D19" s="101"/>
+      <c r="E19" s="103">
+        <v>0</v>
+      </c>
+      <c r="F19" s="101" t="s">
         <v>159</v>
       </c>
-    </row>
-    <row r="11" s="100" customFormat="1" spans="1:6">
-      <c r="A11" s="95">
-        <v>511</v>
-      </c>
-      <c r="B11" s="95" t="s">
+      <c r="G19" s="104"/>
+    </row>
+    <row r="20" spans="1:7">
+      <c r="A20" s="105">
+        <v>527</v>
+      </c>
+      <c r="B20" s="105" t="s">
         <v>160</v>
       </c>
-      <c r="C11" s="95" t="s">
-        <v>110</v>
-      </c>
-      <c r="D11" s="95" t="s">
+      <c r="C20" s="105" t="s">
+        <v>109</v>
+      </c>
+      <c r="D20" s="105"/>
+      <c r="E20" s="105"/>
+      <c r="F20" s="105" t="s">
         <v>161</v>
       </c>
-      <c r="E11" s="96">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="12" s="100" customFormat="1" spans="1:6">
-      <c r="A12" s="95">
-        <v>512</v>
-      </c>
-      <c r="B12" s="95" t="s">
-        <v>162</v>
-      </c>
-      <c r="C12" s="95" t="s">
-        <v>110</v>
-      </c>
-      <c r="D12" s="95" t="s">
-        <v>163</v>
-      </c>
-      <c r="E12" s="96">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" s="99" customFormat="1" spans="1:6">
-      <c r="A13" s="95">
-        <v>513</v>
-      </c>
-      <c r="B13" s="95" t="s">
-        <v>164</v>
-      </c>
-      <c r="C13" s="95" t="s">
-        <v>129</v>
-      </c>
-      <c r="D13" s="95" t="s">
-        <v>165</v>
-      </c>
-      <c r="E13" s="96" t="s">
-        <v>166</v>
-      </c>
-      <c r="F13" s="100"/>
-    </row>
-    <row r="14" s="100" customFormat="1" spans="1:6">
-      <c r="A14" s="95">
-        <v>514</v>
-      </c>
-      <c r="B14" s="95" t="s">
-        <v>167</v>
-      </c>
-      <c r="C14" s="95" t="s">
-        <v>129</v>
-      </c>
-      <c r="D14" s="96" t="s">
-        <v>168</v>
-      </c>
-      <c r="E14" s="96" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="15" s="100" customFormat="1" spans="1:6">
-      <c r="A15" s="95">
-        <v>515</v>
-      </c>
-      <c r="B15" s="95" t="s">
-        <v>118</v>
-      </c>
-      <c r="C15" s="95" t="s">
-        <v>110</v>
-      </c>
-      <c r="D15" s="96" t="s">
-        <v>119</v>
-      </c>
-      <c r="E15" s="96"/>
-    </row>
-    <row r="16" s="100" customFormat="1" spans="1:6">
-      <c r="A16" s="95">
-        <v>516</v>
-      </c>
-      <c r="B16" s="95" t="s">
-        <v>170</v>
-      </c>
-      <c r="C16" s="95" t="s">
-        <v>110</v>
-      </c>
-      <c r="D16" s="96" t="s">
-        <v>171</v>
-      </c>
-      <c r="E16" s="96">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17" s="100" customFormat="1" spans="1:6">
-      <c r="A17" s="95">
-        <v>517</v>
-      </c>
-      <c r="B17" s="95" t="s">
-        <v>172</v>
-      </c>
-      <c r="C17" s="95" t="s">
-        <v>110</v>
-      </c>
-      <c r="D17" s="96" t="s">
-        <v>173</v>
-      </c>
-      <c r="E17" s="96">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="18" s="100" customFormat="1" ht="20.25" spans="1:6">
-      <c r="A18" s="95">
-        <v>518</v>
-      </c>
-      <c r="B18" s="102" t="s">
-        <v>133</v>
-      </c>
-      <c r="C18" s="103" t="s">
-        <v>110</v>
-      </c>
-      <c r="D18" s="102" t="s">
-        <v>134</v>
-      </c>
-      <c r="E18" s="96"/>
-    </row>
-    <row r="19" s="100" customFormat="1" ht="20.25" spans="1:6">
-      <c r="A19" s="95">
-        <v>519</v>
-      </c>
-      <c r="B19" s="102" t="s">
-        <v>135</v>
-      </c>
-      <c r="C19" s="102" t="s">
-        <v>129</v>
-      </c>
-      <c r="D19" s="102" t="s">
-        <v>136</v>
-      </c>
-      <c r="E19" s="96"/>
-    </row>
-    <row r="20" s="100" customFormat="1" spans="1:6">
-      <c r="A20" s="95">
-        <v>1001</v>
-      </c>
-      <c r="B20" s="95" t="s">
-        <v>174</v>
-      </c>
-      <c r="C20" s="95" t="s">
-        <v>129</v>
-      </c>
-      <c r="D20" s="96" t="s">
-        <v>20</v>
-      </c>
-      <c r="E20" s="96"/>
-    </row>
-    <row r="21" s="100" customFormat="1" ht="131.25" spans="1:6">
-      <c r="A21" s="95">
-        <v>1002</v>
-      </c>
-      <c r="B21" s="95" t="s">
-        <v>109</v>
-      </c>
-      <c r="C21" s="95" t="s">
-        <v>110</v>
-      </c>
-      <c r="D21" s="95" t="s">
-        <v>111</v>
-      </c>
-      <c r="E21" s="101" t="s">
-        <v>112</v>
-      </c>
-      <c r="F21" s="104"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -6003,235 +5842,252 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E30"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
+  <dimension ref="A1:F14"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="11.3333333333333" customWidth="1"/>
-    <col min="2" max="2" width="46.4416666666667" customWidth="1"/>
-    <col min="3" max="3" width="12.3333333333333" customWidth="1"/>
-    <col min="4" max="4" width="80.375" customWidth="1"/>
-    <col min="5" max="5" width="50.25" style="92" customWidth="1"/>
+    <col min="1" max="1" width="8.84166666666667" style="97" customWidth="1"/>
+    <col min="2" max="2" width="30.8666666666667" style="97" customWidth="1"/>
+    <col min="3" max="3" width="12.3333333333333" style="97" customWidth="1"/>
+    <col min="4" max="5" width="18.625" style="97" customWidth="1"/>
+    <col min="6" max="6" width="36.925" style="97" customWidth="1"/>
+    <col min="7" max="16384" width="9" style="97"/>
   </cols>
   <sheetData>
-    <row r="1" ht="19" customHeight="1" spans="1:5">
-      <c r="A1" s="93" t="s">
+    <row r="1" ht="19" customHeight="1" spans="1:6">
+      <c r="A1" s="91" t="s">
+        <v>162</v>
+      </c>
+      <c r="B1" s="91" t="s">
+        <v>163</v>
+      </c>
+      <c r="C1" s="91" t="s">
+        <v>104</v>
+      </c>
+      <c r="D1" s="91" t="s">
+        <v>125</v>
+      </c>
+      <c r="E1" s="91" t="s">
+        <v>126</v>
+      </c>
+      <c r="F1" s="91" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
+      <c r="A2" s="98">
+        <v>601</v>
+      </c>
+      <c r="B2" s="98" t="s">
+        <v>164</v>
+      </c>
+      <c r="C2" s="98" t="s">
+        <v>129</v>
+      </c>
+      <c r="D2" s="98"/>
+      <c r="E2" s="98"/>
+      <c r="F2" s="98" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="98">
+        <v>602</v>
+      </c>
+      <c r="B3" s="98" t="s">
+        <v>166</v>
+      </c>
+      <c r="C3" s="98" t="s">
+        <v>167</v>
+      </c>
+      <c r="D3" s="98" t="s">
+        <v>129</v>
+      </c>
+      <c r="E3" s="98"/>
+      <c r="F3" s="98" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" s="98">
+        <v>603</v>
+      </c>
+      <c r="B4" s="98" t="s">
+        <v>169</v>
+      </c>
+      <c r="C4" s="98" t="s">
+        <v>167</v>
+      </c>
+      <c r="D4" s="98" t="s">
+        <v>109</v>
+      </c>
+      <c r="E4" s="98"/>
+      <c r="F4" s="98" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" s="98">
+        <v>604</v>
+      </c>
+      <c r="B5" s="98" t="s">
+        <v>171</v>
+      </c>
+      <c r="C5" s="98" t="s">
+        <v>109</v>
+      </c>
+      <c r="D5" s="98"/>
+      <c r="E5" s="98"/>
+      <c r="F5" s="98" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" s="98">
+        <v>605</v>
+      </c>
+      <c r="B6" s="98" t="s">
+        <v>173</v>
+      </c>
+      <c r="C6" s="98" t="s">
+        <v>174</v>
+      </c>
+      <c r="D6" s="98"/>
+      <c r="E6" s="98"/>
+      <c r="F6" s="98" t="s">
         <v>175</v>
       </c>
-      <c r="B1" s="93" t="s">
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="98">
+        <v>611</v>
+      </c>
+      <c r="B7" s="98" t="s">
         <v>176</v>
       </c>
-      <c r="C1" s="93" t="s">
-        <v>104</v>
-      </c>
-      <c r="D1" s="93" t="s">
-        <v>105</v>
-      </c>
-      <c r="E1" s="94" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5">
-      <c r="A2" s="97"/>
-      <c r="B2" s="97"/>
-      <c r="C2" s="97"/>
-      <c r="D2" s="97"/>
-      <c r="E2" s="98"/>
-    </row>
-    <row r="3" spans="1:5">
-      <c r="A3" s="97"/>
-      <c r="B3" s="97"/>
-      <c r="C3" s="97"/>
-      <c r="D3" s="97"/>
-      <c r="E3" s="98"/>
-    </row>
-    <row r="4" spans="1:5">
-      <c r="A4" s="97"/>
-      <c r="B4" s="97"/>
-      <c r="C4" s="97"/>
-      <c r="D4" s="97"/>
-      <c r="E4" s="98"/>
-    </row>
-    <row r="5" spans="1:5">
-      <c r="A5" s="97"/>
-      <c r="B5" s="97"/>
-      <c r="C5" s="97"/>
-      <c r="D5" s="97"/>
-      <c r="E5" s="98"/>
-    </row>
-    <row r="6" spans="1:5">
-      <c r="A6" s="97"/>
-      <c r="B6" s="97"/>
-      <c r="C6" s="97"/>
-      <c r="D6" s="97"/>
-      <c r="E6" s="98"/>
-    </row>
-    <row r="7" spans="1:5">
-      <c r="A7" s="97"/>
-      <c r="B7" s="97"/>
-      <c r="C7" s="97"/>
-      <c r="D7" s="97"/>
+      <c r="C7" s="98" t="s">
+        <v>129</v>
+      </c>
+      <c r="D7" s="98"/>
       <c r="E7" s="98"/>
-    </row>
-    <row r="8" spans="1:5">
-      <c r="A8" s="97"/>
-      <c r="B8" s="97"/>
-      <c r="C8" s="97"/>
-      <c r="D8" s="97"/>
+      <c r="F7" s="98" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="98">
+        <v>612</v>
+      </c>
+      <c r="B8" s="98" t="s">
+        <v>178</v>
+      </c>
+      <c r="C8" s="98" t="s">
+        <v>167</v>
+      </c>
+      <c r="D8" s="98" t="s">
+        <v>129</v>
+      </c>
       <c r="E8" s="98"/>
-    </row>
-    <row r="9" spans="1:5">
-      <c r="A9" s="97"/>
-      <c r="B9" s="97"/>
-      <c r="C9" s="97"/>
-      <c r="D9" s="97"/>
+      <c r="F8" s="98" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="98">
+        <v>613</v>
+      </c>
+      <c r="B9" s="98" t="s">
+        <v>180</v>
+      </c>
+      <c r="C9" s="98" t="s">
+        <v>167</v>
+      </c>
+      <c r="D9" s="98" t="s">
+        <v>109</v>
+      </c>
       <c r="E9" s="98"/>
-    </row>
-    <row r="10" spans="1:5">
-      <c r="A10" s="97"/>
-      <c r="B10" s="97"/>
-      <c r="C10" s="97"/>
-      <c r="D10" s="97"/>
+      <c r="F9" s="98" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="98">
+        <v>614</v>
+      </c>
+      <c r="B10" s="98" t="s">
+        <v>182</v>
+      </c>
+      <c r="C10" s="98" t="s">
+        <v>109</v>
+      </c>
+      <c r="D10" s="98"/>
       <c r="E10" s="98"/>
-    </row>
-    <row r="11" spans="1:5">
-      <c r="A11" s="97"/>
-      <c r="B11" s="97"/>
-      <c r="C11" s="97"/>
-      <c r="D11" s="97"/>
+      <c r="F10" s="98" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="98">
+        <v>615</v>
+      </c>
+      <c r="B11" s="98" t="s">
+        <v>184</v>
+      </c>
+      <c r="C11" s="98" t="s">
+        <v>174</v>
+      </c>
+      <c r="D11" s="98"/>
       <c r="E11" s="98"/>
-    </row>
-    <row r="12" spans="1:5">
-      <c r="A12" s="97"/>
-      <c r="B12" s="97"/>
-      <c r="C12" s="97"/>
-      <c r="D12" s="97"/>
+      <c r="F11" s="98" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="98">
+        <v>621</v>
+      </c>
+      <c r="B12" s="98" t="s">
+        <v>186</v>
+      </c>
+      <c r="C12" s="98" t="s">
+        <v>129</v>
+      </c>
+      <c r="D12" s="98"/>
       <c r="E12" s="98"/>
-    </row>
-    <row r="13" spans="1:5">
-      <c r="A13" s="97"/>
-      <c r="B13" s="97"/>
-      <c r="C13" s="97"/>
-      <c r="D13" s="97"/>
+      <c r="F12" s="98" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="98">
+        <v>624</v>
+      </c>
+      <c r="B13" s="98" t="s">
+        <v>188</v>
+      </c>
+      <c r="C13" s="98" t="s">
+        <v>109</v>
+      </c>
+      <c r="D13" s="98"/>
       <c r="E13" s="98"/>
-    </row>
-    <row r="14" spans="1:5">
-      <c r="A14" s="97"/>
-      <c r="B14" s="97"/>
-      <c r="C14" s="97"/>
-      <c r="D14" s="97"/>
+      <c r="F13" s="98" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="98">
+        <v>625</v>
+      </c>
+      <c r="B14" s="98" t="s">
+        <v>190</v>
+      </c>
+      <c r="C14" s="98" t="s">
+        <v>174</v>
+      </c>
+      <c r="D14" s="98"/>
       <c r="E14" s="98"/>
-    </row>
-    <row r="15" spans="1:5">
-      <c r="A15" s="97"/>
-      <c r="B15" s="97"/>
-      <c r="C15" s="97"/>
-      <c r="D15" s="97"/>
-      <c r="E15" s="98"/>
-    </row>
-    <row r="16" spans="1:5">
-      <c r="A16" s="97"/>
-      <c r="B16" s="97"/>
-      <c r="C16" s="97"/>
-      <c r="D16" s="97"/>
-      <c r="E16" s="98"/>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="97"/>
-      <c r="B17" s="97"/>
-      <c r="C17" s="97"/>
-      <c r="D17" s="97"/>
-      <c r="E17" s="98"/>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="97"/>
-      <c r="B18" s="97"/>
-      <c r="C18" s="97"/>
-      <c r="D18" s="97"/>
-      <c r="E18" s="98"/>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="97"/>
-      <c r="B19" s="97"/>
-      <c r="C19" s="97"/>
-      <c r="D19" s="97"/>
-      <c r="E19" s="98"/>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="97"/>
-      <c r="B20" s="97"/>
-      <c r="C20" s="97"/>
-      <c r="D20" s="97"/>
-      <c r="E20" s="98"/>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="97"/>
-      <c r="B21" s="97"/>
-      <c r="C21" s="97"/>
-      <c r="D21" s="97"/>
-      <c r="E21" s="98"/>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="97"/>
-      <c r="B22" s="97"/>
-      <c r="C22" s="97"/>
-      <c r="D22" s="97"/>
-      <c r="E22" s="98"/>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="97"/>
-      <c r="B23" s="97"/>
-      <c r="C23" s="97"/>
-      <c r="D23" s="97"/>
-      <c r="E23" s="98"/>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="97"/>
-      <c r="B24" s="97"/>
-      <c r="C24" s="97"/>
-      <c r="D24" s="97"/>
-      <c r="E24" s="98"/>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="97"/>
-      <c r="B25" s="97"/>
-      <c r="C25" s="97"/>
-      <c r="D25" s="97"/>
-      <c r="E25" s="98"/>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="97"/>
-      <c r="B26" s="97"/>
-      <c r="C26" s="97"/>
-      <c r="D26" s="97"/>
-      <c r="E26" s="98"/>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="97"/>
-      <c r="B27" s="97"/>
-      <c r="C27" s="97"/>
-      <c r="D27" s="97"/>
-      <c r="E27" s="98"/>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="97"/>
-      <c r="B28" s="97"/>
-      <c r="C28" s="97"/>
-      <c r="D28" s="97"/>
-      <c r="E28" s="98"/>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="97"/>
-      <c r="B29" s="97"/>
-      <c r="C29" s="97"/>
-      <c r="D29" s="97"/>
-      <c r="E29" s="98"/>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="97"/>
-      <c r="B30" s="97"/>
-      <c r="C30" s="97"/>
-      <c r="D30" s="97"/>
-      <c r="E30" s="98"/>
+      <c r="F14" s="98" t="s">
+        <v>191</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6242,387 +6098,384 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E22"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
+  <dimension ref="A1:F21"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="8.775" customWidth="1"/>
     <col min="2" max="2" width="34" customWidth="1"/>
     <col min="3" max="3" width="12.3333333333333" customWidth="1"/>
-    <col min="4" max="4" width="47.5" customWidth="1"/>
-    <col min="5" max="5" width="36.6666666666667" style="92" customWidth="1"/>
+    <col min="4" max="4" width="18.625" customWidth="1"/>
+    <col min="5" max="5" width="20.7583333333333" customWidth="1"/>
+    <col min="6" max="6" width="69.9916666666667" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="18.75" spans="1:5">
-      <c r="A1" s="93" t="s">
-        <v>177</v>
-      </c>
-      <c r="B1" s="93" t="s">
-        <v>176</v>
-      </c>
-      <c r="C1" s="93" t="s">
+    <row r="1" ht="18.75" spans="1:6">
+      <c r="A1" s="91" t="s">
+        <v>192</v>
+      </c>
+      <c r="B1" s="91" t="s">
+        <v>193</v>
+      </c>
+      <c r="C1" s="91" t="s">
         <v>104</v>
       </c>
-      <c r="D1" s="93" t="s">
+      <c r="D1" s="91" t="s">
+        <v>125</v>
+      </c>
+      <c r="E1" s="91" t="s">
+        <v>126</v>
+      </c>
+      <c r="F1" s="91" t="s">
         <v>105</v>
       </c>
-      <c r="E1" s="94" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="2" ht="18.75" spans="1:5">
-      <c r="A2" s="95">
+    </row>
+    <row r="2" ht="18.75" spans="1:6">
+      <c r="A2" s="92">
         <v>701</v>
       </c>
-      <c r="B2" s="95" t="s">
-        <v>179</v>
-      </c>
-      <c r="C2" s="95" t="s">
-        <v>110</v>
-      </c>
-      <c r="D2" s="95" t="s">
-        <v>180</v>
-      </c>
-      <c r="E2" s="96">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="3" ht="18.75" spans="1:5">
-      <c r="A3" s="95">
+      <c r="B2" s="92" t="s">
+        <v>194</v>
+      </c>
+      <c r="C2" s="92" t="s">
+        <v>129</v>
+      </c>
+      <c r="D2" s="92"/>
+      <c r="E2" s="93" t="s">
+        <v>195</v>
+      </c>
+      <c r="F2" s="92" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="3" ht="18.75" spans="1:6">
+      <c r="A3" s="92">
         <v>702</v>
       </c>
-      <c r="B3" s="95" t="s">
-        <v>181</v>
-      </c>
-      <c r="C3" s="95" t="s">
-        <v>110</v>
-      </c>
-      <c r="D3" s="95" t="s">
-        <v>182</v>
-      </c>
-      <c r="E3" s="96">
+      <c r="B3" s="92" t="s">
+        <v>197</v>
+      </c>
+      <c r="C3" s="92" t="s">
+        <v>109</v>
+      </c>
+      <c r="D3" s="92"/>
+      <c r="E3" s="93">
+        <v>5000</v>
+      </c>
+      <c r="F3" s="92" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="4" ht="18.75" spans="1:6">
+      <c r="A4" s="92">
+        <v>703</v>
+      </c>
+      <c r="B4" s="92" t="s">
+        <v>199</v>
+      </c>
+      <c r="C4" s="92" t="s">
+        <v>109</v>
+      </c>
+      <c r="D4" s="92"/>
+      <c r="E4" s="93">
+        <v>30</v>
+      </c>
+      <c r="F4" s="92" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="5" ht="18.75" spans="1:6">
+      <c r="A5" s="92">
+        <v>704</v>
+      </c>
+      <c r="B5" s="92" t="s">
+        <v>201</v>
+      </c>
+      <c r="C5" s="92" t="s">
+        <v>109</v>
+      </c>
+      <c r="D5" s="92"/>
+      <c r="E5" s="93">
+        <v>100</v>
+      </c>
+      <c r="F5" s="92" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="6" ht="18.75" spans="1:6">
+      <c r="A6" s="92">
+        <v>705</v>
+      </c>
+      <c r="B6" s="92" t="s">
+        <v>203</v>
+      </c>
+      <c r="C6" s="92" t="s">
+        <v>174</v>
+      </c>
+      <c r="D6" s="92"/>
+      <c r="E6" s="93" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" ht="18.75" spans="1:5">
-      <c r="A4" s="95">
-        <v>703</v>
-      </c>
-      <c r="B4" s="95" t="s">
-        <v>183</v>
-      </c>
-      <c r="C4" s="95" t="s">
-        <v>110</v>
-      </c>
-      <c r="D4" s="95" t="s">
-        <v>184</v>
-      </c>
-      <c r="E4" s="96">
+      <c r="F6" s="92" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="7" ht="37.5" spans="1:6">
+      <c r="A7" s="92">
+        <v>706</v>
+      </c>
+      <c r="B7" s="92" t="s">
+        <v>205</v>
+      </c>
+      <c r="C7" s="92" t="s">
+        <v>129</v>
+      </c>
+      <c r="D7" s="92"/>
+      <c r="E7" s="93" t="s">
+        <v>206</v>
+      </c>
+      <c r="F7" s="93" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="8" ht="18.75" spans="1:6">
+      <c r="A8" s="92">
+        <v>707</v>
+      </c>
+      <c r="B8" s="92" t="s">
+        <v>208</v>
+      </c>
+      <c r="C8" s="92" t="s">
+        <v>129</v>
+      </c>
+      <c r="D8" s="92"/>
+      <c r="E8" s="93" t="s">
+        <v>209</v>
+      </c>
+      <c r="F8" s="92" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="9" ht="18.75" spans="1:6">
+      <c r="A9" s="92">
+        <v>708</v>
+      </c>
+      <c r="B9" s="92" t="s">
+        <v>211</v>
+      </c>
+      <c r="C9" s="92" t="s">
+        <v>109</v>
+      </c>
+      <c r="D9" s="92"/>
+      <c r="E9" s="93">
+        <v>502</v>
+      </c>
+      <c r="F9" s="92" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="10" ht="18.75" spans="1:6">
+      <c r="A10" s="92">
+        <v>709</v>
+      </c>
+      <c r="B10" s="92" t="s">
+        <v>213</v>
+      </c>
+      <c r="C10" s="92" t="s">
+        <v>109</v>
+      </c>
+      <c r="D10" s="92"/>
+      <c r="E10" s="93">
+        <v>1998</v>
+      </c>
+      <c r="F10" s="92" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="11" ht="18.75" spans="1:6">
+      <c r="A11" s="92">
+        <v>710</v>
+      </c>
+      <c r="B11" s="92" t="s">
+        <v>215</v>
+      </c>
+      <c r="C11" s="92" t="s">
+        <v>109</v>
+      </c>
+      <c r="D11" s="92"/>
+      <c r="E11" s="93">
         <v>2</v>
       </c>
-    </row>
-    <row r="5" ht="18.75" spans="1:5">
-      <c r="A5" s="95">
-        <v>704</v>
-      </c>
-      <c r="B5" s="95" t="s">
-        <v>185</v>
-      </c>
-      <c r="C5" s="95" t="s">
-        <v>110</v>
-      </c>
-      <c r="D5" s="95" t="s">
-        <v>186</v>
-      </c>
-      <c r="E5" s="96">
+      <c r="F11" s="92" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="12" ht="18.75" spans="1:6">
+      <c r="A12" s="92">
+        <v>711</v>
+      </c>
+      <c r="B12" s="92" t="s">
+        <v>217</v>
+      </c>
+      <c r="C12" s="92" t="s">
+        <v>109</v>
+      </c>
+      <c r="D12" s="92"/>
+      <c r="E12" s="93">
         <v>4</v>
       </c>
-    </row>
-    <row r="6" ht="18.75" spans="1:5">
-      <c r="A6" s="95">
-        <v>705</v>
-      </c>
-      <c r="B6" s="95" t="s">
-        <v>187</v>
-      </c>
-      <c r="C6" s="95" t="s">
+      <c r="F12" s="92" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="13" ht="18.75" spans="1:6">
+      <c r="A13" s="92">
+        <v>712</v>
+      </c>
+      <c r="B13" s="92" t="s">
+        <v>219</v>
+      </c>
+      <c r="C13" s="92" t="s">
         <v>129</v>
       </c>
-      <c r="D6" s="95" t="s">
-        <v>188</v>
-      </c>
-      <c r="E6" s="96" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="7" ht="18.75" spans="1:5">
-      <c r="A7" s="95">
-        <v>706</v>
-      </c>
-      <c r="B7" s="95" t="s">
-        <v>190</v>
-      </c>
-      <c r="C7" s="95" t="s">
+      <c r="D13" s="92"/>
+      <c r="E13" s="93" t="s">
+        <v>220</v>
+      </c>
+      <c r="F13" s="92" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="14" ht="18.75" spans="1:6">
+      <c r="A14" s="92">
+        <v>713</v>
+      </c>
+      <c r="B14" s="92" t="s">
+        <v>222</v>
+      </c>
+      <c r="C14" s="92" t="s">
         <v>129</v>
       </c>
-      <c r="D7" s="95" t="s">
-        <v>191</v>
-      </c>
-      <c r="E7" s="96" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="8" ht="18.75" spans="1:5">
-      <c r="A8" s="95">
-        <v>707</v>
-      </c>
-      <c r="B8" s="95" t="s">
-        <v>193</v>
-      </c>
-      <c r="C8" s="95" t="s">
+      <c r="D14" s="92"/>
+      <c r="E14" s="93" t="s">
+        <v>223</v>
+      </c>
+      <c r="F14" s="92" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="15" ht="18.75" spans="1:6">
+      <c r="A15" s="92">
+        <v>714</v>
+      </c>
+      <c r="B15" s="92" t="s">
+        <v>225</v>
+      </c>
+      <c r="C15" s="92" t="s">
         <v>129</v>
       </c>
-      <c r="D8" s="95" t="s">
-        <v>194</v>
-      </c>
-      <c r="E8" s="96" t="s">
+      <c r="D15" s="92"/>
+      <c r="E15" s="93" t="s">
         <v>195</v>
       </c>
-    </row>
-    <row r="9" ht="18.75" spans="1:5">
-      <c r="A9" s="95">
-        <v>708</v>
-      </c>
-      <c r="B9" s="95" t="s">
-        <v>196</v>
-      </c>
-      <c r="C9" s="95" t="s">
+      <c r="F15" s="92" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="16" ht="18.75" spans="1:6">
+      <c r="A16" s="92">
+        <v>715</v>
+      </c>
+      <c r="B16" s="92" t="s">
+        <v>227</v>
+      </c>
+      <c r="C16" s="92" t="s">
         <v>129</v>
       </c>
-      <c r="D9" s="95" t="s">
-        <v>197</v>
-      </c>
-      <c r="E9" s="96" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="10" ht="18.75" spans="1:5">
-      <c r="A10" s="95">
-        <v>709</v>
-      </c>
-      <c r="B10" s="95" t="s">
-        <v>199</v>
-      </c>
-      <c r="C10" s="95" t="s">
-        <v>110</v>
-      </c>
-      <c r="D10" s="95" t="s">
-        <v>200</v>
-      </c>
-      <c r="E10" s="96">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="11" ht="18.75" spans="1:5">
-      <c r="A11" s="95">
-        <v>710</v>
-      </c>
-      <c r="B11" s="95" t="s">
-        <v>201</v>
-      </c>
-      <c r="C11" s="95" t="s">
+      <c r="D16" s="92"/>
+      <c r="E16" s="93"/>
+      <c r="F16" s="92" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="17" ht="18.75" spans="1:6">
+      <c r="A17" s="92">
+        <v>716</v>
+      </c>
+      <c r="B17" s="92" t="s">
+        <v>229</v>
+      </c>
+      <c r="C17" s="92" t="s">
         <v>129</v>
       </c>
-      <c r="D11" s="95" t="s">
-        <v>202</v>
-      </c>
-      <c r="E11" s="96" t="s">
+      <c r="D17" s="92"/>
+      <c r="E17" s="93" t="s">
         <v>195</v>
       </c>
-    </row>
-    <row r="12" ht="18.75" spans="1:5">
-      <c r="A12" s="95">
-        <v>711</v>
-      </c>
-      <c r="B12" s="95" t="s">
-        <v>203</v>
-      </c>
-      <c r="C12" s="95" t="s">
-        <v>110</v>
-      </c>
-      <c r="D12" s="95" t="s">
-        <v>204</v>
-      </c>
-      <c r="E12" s="96">
-        <v>5000</v>
-      </c>
-    </row>
-    <row r="13" ht="18.75" spans="1:5">
-      <c r="A13" s="95">
-        <v>712</v>
-      </c>
-      <c r="B13" s="95" t="s">
-        <v>205</v>
-      </c>
-      <c r="C13" s="95" t="s">
-        <v>206</v>
-      </c>
-      <c r="D13" s="95" t="s">
-        <v>207</v>
-      </c>
-      <c r="E13" s="96" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" ht="18.75" spans="1:5">
-      <c r="A14" s="95">
-        <v>713</v>
-      </c>
-      <c r="B14" s="95" t="s">
-        <v>208</v>
-      </c>
-      <c r="C14" s="95" t="s">
+      <c r="F17" s="92" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="18" ht="18.75" spans="1:6">
+      <c r="A18" s="94">
+        <v>717</v>
+      </c>
+      <c r="B18" s="94" t="s">
+        <v>231</v>
+      </c>
+      <c r="C18" s="94" t="s">
+        <v>109</v>
+      </c>
+      <c r="D18" s="94"/>
+      <c r="E18" s="95">
+        <v>1830</v>
+      </c>
+      <c r="F18" s="95" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="19" ht="18.75" spans="1:6">
+      <c r="A19" s="94">
+        <v>718</v>
+      </c>
+      <c r="B19" s="94" t="s">
+        <v>233</v>
+      </c>
+      <c r="C19" s="94" t="s">
+        <v>109</v>
+      </c>
+      <c r="D19" s="94"/>
+      <c r="E19" s="95">
+        <v>1831</v>
+      </c>
+      <c r="F19" s="94" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="20" ht="18.75" spans="1:6">
+      <c r="A20" s="94">
+        <v>719</v>
+      </c>
+      <c r="B20" s="94" t="s">
+        <v>235</v>
+      </c>
+      <c r="C20" s="94" t="s">
+        <v>167</v>
+      </c>
+      <c r="D20" s="94" t="s">
         <v>129</v>
       </c>
-      <c r="D14" s="95" t="s">
-        <v>209</v>
-      </c>
-      <c r="E14" s="96" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="15" ht="18.75" spans="1:5">
-      <c r="A15" s="95">
-        <v>714</v>
-      </c>
-      <c r="B15" s="95" t="s">
-        <v>211</v>
-      </c>
-      <c r="C15" s="95" t="s">
-        <v>110</v>
-      </c>
-      <c r="D15" s="95" t="s">
-        <v>212</v>
-      </c>
-      <c r="E15" s="96">
-        <v>502</v>
-      </c>
-    </row>
-    <row r="16" ht="18.75" spans="1:5">
-      <c r="A16" s="95">
-        <v>715</v>
-      </c>
-      <c r="B16" s="95" t="s">
-        <v>213</v>
-      </c>
-      <c r="C16" s="95" t="s">
-        <v>110</v>
-      </c>
-      <c r="D16" s="95" t="s">
-        <v>214</v>
-      </c>
-      <c r="E16" s="96">
-        <v>1998</v>
-      </c>
-    </row>
-    <row r="17" ht="18.75" spans="1:5">
-      <c r="A17" s="95">
-        <v>716</v>
-      </c>
-      <c r="B17" s="95" t="s">
-        <v>215</v>
-      </c>
-      <c r="C17" s="95" t="s">
-        <v>129</v>
-      </c>
-      <c r="D17" s="95" t="s">
-        <v>216</v>
-      </c>
-      <c r="E17" s="96" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="18" ht="18.75" spans="1:5">
-      <c r="A18" s="95">
-        <v>717</v>
-      </c>
-      <c r="B18" s="95" t="s">
-        <v>218</v>
-      </c>
-      <c r="C18" s="95" t="s">
-        <v>129</v>
-      </c>
-      <c r="D18" s="96" t="s">
-        <v>219</v>
-      </c>
-      <c r="E18" s="96" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="19" ht="18.75" spans="1:5">
-      <c r="A19" s="95">
-        <v>718</v>
-      </c>
-      <c r="B19" s="95" t="s">
-        <v>220</v>
-      </c>
-      <c r="C19" s="95" t="s">
-        <v>110</v>
-      </c>
-      <c r="D19" s="95" t="s">
-        <v>221</v>
-      </c>
-      <c r="E19" s="96">
-        <v>1830</v>
-      </c>
-    </row>
-    <row r="20" ht="18.75" spans="1:5">
-      <c r="A20" s="95">
-        <v>719</v>
-      </c>
-      <c r="B20" s="95" t="s">
-        <v>222</v>
-      </c>
-      <c r="C20" s="95" t="s">
-        <v>223</v>
-      </c>
-      <c r="D20" s="96" t="s">
-        <v>224</v>
-      </c>
-      <c r="E20" s="96"/>
-    </row>
-    <row r="21" ht="18.75" spans="1:5">
-      <c r="A21" s="95">
-        <v>720</v>
-      </c>
-      <c r="B21" s="95" t="s">
-        <v>225</v>
-      </c>
-      <c r="C21" s="95" t="s">
-        <v>110</v>
-      </c>
-      <c r="D21" s="95" t="s">
-        <v>226</v>
-      </c>
-      <c r="E21" s="96">
-        <v>1831</v>
-      </c>
-    </row>
-    <row r="22" ht="18.75" spans="1:5">
-      <c r="A22" s="95">
-        <v>721</v>
-      </c>
-      <c r="B22" s="95" t="s">
-        <v>227</v>
-      </c>
-      <c r="C22" s="95" t="s">
-        <v>110</v>
-      </c>
-      <c r="D22" s="95" t="s">
-        <v>228</v>
-      </c>
-      <c r="E22" s="96">
-        <v>30</v>
-      </c>
+      <c r="E20" s="95"/>
+      <c r="F20" s="95" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6">
+      <c r="A21" s="96"/>
+      <c r="B21" s="96"/>
+      <c r="C21" s="96"/>
+      <c r="D21" s="96"/>
+      <c r="E21" s="96"/>
+      <c r="F21" s="96"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6633,8 +6486,8 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E8"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="7" outlineLevelCol="4"/>
+  <dimension ref="A1:E4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="3" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="19.3083333333333" style="81" customWidth="1"/>
     <col min="2" max="2" width="27.325" style="81" customWidth="1"/>
@@ -6647,95 +6500,67 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="89" t="s">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="B1" s="89" t="s">
-        <v>230</v>
+        <v>238</v>
       </c>
       <c r="C1" s="89" t="s">
-        <v>231</v>
+        <v>239</v>
       </c>
       <c r="D1" s="89" t="s">
-        <v>232</v>
+        <v>240</v>
       </c>
       <c r="E1" s="89" t="s">
-        <v>233</v>
+        <v>241</v>
       </c>
     </row>
     <row r="2" s="81" customFormat="1" spans="1:5">
-      <c r="A2" s="84" t="s">
-        <v>234</v>
-      </c>
-      <c r="B2" s="84" t="s">
-        <v>235</v>
+      <c r="A2" s="86" t="s">
+        <v>242</v>
+      </c>
+      <c r="B2" s="86" t="s">
+        <v>243</v>
       </c>
       <c r="C2" s="90" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="D2" s="90" t="s">
         <v>129</v>
       </c>
       <c r="E2" s="90" t="s">
-        <v>236</v>
+        <v>244</v>
       </c>
     </row>
     <row r="3" s="81" customFormat="1" spans="1:5">
-      <c r="A3" s="84" t="s">
-        <v>237</v>
-      </c>
-      <c r="B3" s="84" t="s">
-        <v>238</v>
+      <c r="A3" s="86" t="s">
+        <v>245</v>
+      </c>
+      <c r="B3" s="86" t="s">
+        <v>246</v>
       </c>
       <c r="C3" s="90" t="s">
-        <v>128</v>
+        <v>136</v>
       </c>
       <c r="D3" s="90" t="s">
         <v>129</v>
       </c>
       <c r="E3" s="90" t="s">
-        <v>239</v>
+        <v>247</v>
       </c>
     </row>
     <row r="4" s="81" customFormat="1" spans="1:5">
-      <c r="A4" s="84"/>
-      <c r="B4" s="84"/>
+      <c r="A4" s="86"/>
+      <c r="B4" s="86"/>
       <c r="C4" s="90" t="s">
-        <v>145</v>
+        <v>138</v>
       </c>
       <c r="D4" s="90" t="s">
-        <v>240</v>
+        <v>248</v>
       </c>
       <c r="E4" s="90" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5">
-      <c r="A5" s="91"/>
-      <c r="B5" s="91"/>
-      <c r="C5" s="90"/>
-      <c r="D5" s="90"/>
-      <c r="E5" s="90"/>
-    </row>
-    <row r="6" spans="1:5">
-      <c r="A6" s="91"/>
-      <c r="B6" s="91"/>
-      <c r="C6" s="90"/>
-      <c r="D6" s="90"/>
-      <c r="E6" s="90"/>
-    </row>
-    <row r="7" spans="1:5">
-      <c r="A7" s="91"/>
-      <c r="B7" s="91"/>
-      <c r="C7" s="90"/>
-      <c r="D7" s="90"/>
-      <c r="E7" s="90"/>
-    </row>
-    <row r="8" spans="1:5">
-      <c r="A8" s="84"/>
-      <c r="B8" s="84"/>
-      <c r="C8" s="90"/>
-      <c r="D8" s="90"/>
-      <c r="E8" s="90"/>
+        <v>139</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -6763,89 +6588,89 @@
   <sheetData>
     <row r="1" s="81" customFormat="1" spans="1:3">
       <c r="A1" s="88" t="s">
-        <v>134</v>
+        <v>249</v>
       </c>
       <c r="B1" s="88" t="s">
-        <v>241</v>
+        <v>250</v>
       </c>
       <c r="C1" s="88" t="s">
-        <v>242</v>
+        <v>251</v>
       </c>
     </row>
     <row r="2" s="81" customFormat="1" spans="1:3">
-      <c r="A2" s="84"/>
-      <c r="B2" s="84"/>
-      <c r="C2" s="84"/>
+      <c r="A2" s="86"/>
+      <c r="B2" s="86"/>
+      <c r="C2" s="86"/>
     </row>
     <row r="3" s="81" customFormat="1" spans="1:3">
-      <c r="A3" s="84"/>
-      <c r="B3" s="84"/>
-      <c r="C3" s="84"/>
+      <c r="A3" s="86"/>
+      <c r="B3" s="86"/>
+      <c r="C3" s="86"/>
     </row>
     <row r="4" s="81" customFormat="1" spans="1:3">
-      <c r="A4" s="84"/>
-      <c r="B4" s="84"/>
-      <c r="C4" s="84"/>
+      <c r="A4" s="86"/>
+      <c r="B4" s="86"/>
+      <c r="C4" s="86"/>
     </row>
     <row r="5" s="81" customFormat="1" spans="1:3">
-      <c r="A5" s="84"/>
-      <c r="B5" s="84"/>
-      <c r="C5" s="84"/>
+      <c r="A5" s="86"/>
+      <c r="B5" s="86"/>
+      <c r="C5" s="86"/>
     </row>
     <row r="6" s="81" customFormat="1" spans="1:3">
-      <c r="A6" s="84"/>
-      <c r="B6" s="84"/>
-      <c r="C6" s="84"/>
+      <c r="A6" s="86"/>
+      <c r="B6" s="86"/>
+      <c r="C6" s="86"/>
     </row>
     <row r="7" s="81" customFormat="1" spans="1:3">
-      <c r="A7" s="84"/>
-      <c r="B7" s="84"/>
-      <c r="C7" s="84"/>
+      <c r="A7" s="86"/>
+      <c r="B7" s="86"/>
+      <c r="C7" s="86"/>
     </row>
     <row r="8" s="81" customFormat="1" spans="1:3">
-      <c r="A8" s="84"/>
-      <c r="B8" s="84"/>
-      <c r="C8" s="84"/>
+      <c r="A8" s="86"/>
+      <c r="B8" s="86"/>
+      <c r="C8" s="86"/>
     </row>
     <row r="9" spans="1:3">
-      <c r="A9" s="84"/>
-      <c r="B9" s="84"/>
-      <c r="C9" s="84"/>
+      <c r="A9" s="86"/>
+      <c r="B9" s="86"/>
+      <c r="C9" s="86"/>
     </row>
     <row r="10" spans="1:3">
-      <c r="A10" s="84"/>
-      <c r="B10" s="84"/>
-      <c r="C10" s="84"/>
+      <c r="A10" s="86"/>
+      <c r="B10" s="86"/>
+      <c r="C10" s="86"/>
     </row>
     <row r="11" spans="1:3">
-      <c r="A11" s="84"/>
-      <c r="B11" s="84"/>
-      <c r="C11" s="84"/>
+      <c r="A11" s="86"/>
+      <c r="B11" s="86"/>
+      <c r="C11" s="86"/>
     </row>
     <row r="12" spans="1:3">
-      <c r="A12" s="84"/>
-      <c r="B12" s="84"/>
-      <c r="C12" s="84"/>
+      <c r="A12" s="86"/>
+      <c r="B12" s="86"/>
+      <c r="C12" s="86"/>
     </row>
     <row r="13" spans="1:3">
-      <c r="A13" s="84"/>
-      <c r="B13" s="84"/>
-      <c r="C13" s="84"/>
+      <c r="A13" s="86"/>
+      <c r="B13" s="86"/>
+      <c r="C13" s="86"/>
     </row>
     <row r="14" spans="1:3">
-      <c r="A14" s="84"/>
-      <c r="B14" s="84"/>
-      <c r="C14" s="84"/>
+      <c r="A14" s="86"/>
+      <c r="B14" s="86"/>
+      <c r="C14" s="86"/>
     </row>
     <row r="15" spans="1:3">
-      <c r="A15" s="84"/>
-      <c r="B15" s="84"/>
-      <c r="C15" s="84"/>
+      <c r="A15" s="86"/>
+      <c r="B15" s="86"/>
+      <c r="C15" s="86"/>
     </row>
     <row r="16" spans="1:3">
-      <c r="A16" s="84"/>
-      <c r="B16" s="84"/>
-      <c r="C16" s="84"/>
+      <c r="A16" s="86"/>
+      <c r="B16" s="86"/>
+      <c r="C16" s="86"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6867,16 +6692,16 @@
   <sheetData>
     <row r="1" s="81" customFormat="1" spans="1:5">
       <c r="A1" s="82" t="s">
-        <v>243</v>
+        <v>252</v>
       </c>
       <c r="B1" s="82" t="s">
-        <v>244</v>
+        <v>253</v>
       </c>
       <c r="C1" s="82" t="s">
-        <v>245</v>
+        <v>254</v>
       </c>
       <c r="D1" s="82" t="s">
-        <v>246</v>
+        <v>255</v>
       </c>
       <c r="E1" s="82" t="s">
         <v>2</v>
@@ -6884,283 +6709,283 @@
     </row>
     <row r="2" s="81" customFormat="1" spans="1:5">
       <c r="A2" s="83" t="s">
-        <v>247</v>
-      </c>
-      <c r="B2" s="83" t="s">
-        <v>248</v>
+        <v>256</v>
+      </c>
+      <c r="B2" s="84" t="s">
+        <v>257</v>
       </c>
       <c r="C2" s="84">
         <v>1</v>
       </c>
       <c r="D2" s="84" t="s">
-        <v>249</v>
+        <v>258</v>
       </c>
       <c r="E2" s="84" t="s">
-        <v>250</v>
+        <v>259</v>
       </c>
     </row>
     <row r="3" s="81" customFormat="1" spans="1:5">
-      <c r="A3" s="83" t="s">
-        <v>251</v>
-      </c>
-      <c r="B3" s="84" t="s">
-        <v>252</v>
-      </c>
-      <c r="C3" s="84">
+      <c r="A3" s="85" t="s">
+        <v>260</v>
+      </c>
+      <c r="B3" s="85" t="s">
+        <v>261</v>
+      </c>
+      <c r="C3" s="86">
+        <v>1</v>
+      </c>
+      <c r="D3" s="86" t="s">
+        <v>262</v>
+      </c>
+      <c r="E3" s="86" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="4" s="81" customFormat="1" spans="1:5">
+      <c r="A4" s="85" t="s">
+        <v>264</v>
+      </c>
+      <c r="B4" s="86" t="s">
+        <v>265</v>
+      </c>
+      <c r="C4" s="86">
         <v>2</v>
       </c>
-      <c r="D3" s="84" t="s">
-        <v>249</v>
-      </c>
-      <c r="E3" s="84" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="4" s="81" customFormat="1" spans="1:5">
-      <c r="A4" s="83" t="s">
-        <v>254</v>
-      </c>
-      <c r="B4" s="84" t="s">
-        <v>255</v>
-      </c>
-      <c r="C4" s="84">
-        <v>20</v>
-      </c>
-      <c r="D4" s="84" t="s">
-        <v>249</v>
-      </c>
-      <c r="E4" s="84" t="s">
-        <v>256</v>
+      <c r="D4" s="86" t="s">
+        <v>262</v>
+      </c>
+      <c r="E4" s="86" t="s">
+        <v>266</v>
       </c>
     </row>
     <row r="5" s="81" customFormat="1" spans="1:5">
       <c r="A5" s="85" t="s">
-        <v>257</v>
+        <v>267</v>
       </c>
       <c r="B5" s="86" t="s">
+        <v>268</v>
+      </c>
+      <c r="C5" s="86">
+        <v>20</v>
+      </c>
+      <c r="D5" s="86" t="s">
+        <v>262</v>
+      </c>
+      <c r="E5" s="86" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="6" s="81" customFormat="1" spans="1:5">
+      <c r="A6" s="83" t="s">
+        <v>270</v>
+      </c>
+      <c r="B6" s="84" t="s">
+        <v>265</v>
+      </c>
+      <c r="C6" s="84">
+        <v>1</v>
+      </c>
+      <c r="D6" s="84" t="s">
         <v>258</v>
       </c>
-      <c r="C5" s="86">
-        <v>1</v>
-      </c>
-      <c r="D5" s="86" t="s">
-        <v>259</v>
-      </c>
-      <c r="E5" s="86" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="6" s="81" customFormat="1" spans="1:5">
-      <c r="A6" s="85" t="s">
-        <v>261</v>
-      </c>
-      <c r="B6" s="84" t="s">
-        <v>252</v>
-      </c>
-      <c r="C6" s="84">
+      <c r="E6" s="84" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="7" s="81" customFormat="1" spans="1:5">
+      <c r="A7" s="83" t="s">
+        <v>272</v>
+      </c>
+      <c r="B7" s="84" t="s">
+        <v>268</v>
+      </c>
+      <c r="C7" s="84">
+        <v>80</v>
+      </c>
+      <c r="D7" s="84" t="s">
+        <v>258</v>
+      </c>
+      <c r="E7" s="84" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="8" s="81" customFormat="1" spans="1:5">
+      <c r="A8" s="83" t="s">
+        <v>274</v>
+      </c>
+      <c r="B8" s="84" t="s">
+        <v>268</v>
+      </c>
+      <c r="C8" s="84">
+        <v>80</v>
+      </c>
+      <c r="D8" s="84" t="s">
+        <v>258</v>
+      </c>
+      <c r="E8" s="84" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="9" s="81" customFormat="1" spans="1:5">
+      <c r="A9" s="83" t="s">
+        <v>275</v>
+      </c>
+      <c r="B9" s="84" t="s">
+        <v>276</v>
+      </c>
+      <c r="C9" s="84">
+        <v>4</v>
+      </c>
+      <c r="D9" s="84" t="s">
+        <v>258</v>
+      </c>
+      <c r="E9" s="84" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="10" s="81" customFormat="1" spans="1:5">
+      <c r="A10" s="83" t="s">
+        <v>278</v>
+      </c>
+      <c r="B10" s="86" t="s">
+        <v>265</v>
+      </c>
+      <c r="C10" s="86">
         <v>2</v>
       </c>
-      <c r="D6" s="84" t="s">
-        <v>249</v>
-      </c>
-      <c r="E6" s="84" t="s">
+      <c r="D10" s="86" t="s">
         <v>262</v>
       </c>
-    </row>
-    <row r="7" s="81" customFormat="1" spans="1:5">
-      <c r="A7" s="85" t="s">
-        <v>263</v>
-      </c>
-      <c r="B7" s="86" t="s">
-        <v>252</v>
-      </c>
-      <c r="C7" s="86">
-        <v>1</v>
-      </c>
-      <c r="D7" s="86" t="s">
-        <v>259</v>
-      </c>
-      <c r="E7" s="86" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="8" s="81" customFormat="1" spans="1:5">
-      <c r="A8" s="85" t="s">
+      <c r="E10" s="86" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="11" s="81" customFormat="1" spans="1:5">
+      <c r="A11" s="83" t="s">
+        <v>280</v>
+      </c>
+      <c r="B11" s="84" t="s">
         <v>265</v>
       </c>
-      <c r="B8" s="86" t="s">
-        <v>255</v>
-      </c>
-      <c r="C8" s="86">
+      <c r="C11" s="84">
+        <v>2</v>
+      </c>
+      <c r="D11" s="84" t="s">
+        <v>258</v>
+      </c>
+      <c r="E11" s="84" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="12" s="81" customFormat="1" spans="1:5">
+      <c r="A12" s="83" t="s">
+        <v>280</v>
+      </c>
+      <c r="B12" s="84" t="s">
+        <v>268</v>
+      </c>
+      <c r="C12" s="84">
         <v>80</v>
       </c>
-      <c r="D8" s="86" t="s">
-        <v>259</v>
-      </c>
-      <c r="E8" s="86" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="9" s="81" customFormat="1" spans="1:5">
-      <c r="A9" s="85" t="s">
-        <v>267</v>
-      </c>
-      <c r="B9" s="86" t="s">
-        <v>255</v>
-      </c>
-      <c r="C9" s="86">
-        <v>80</v>
-      </c>
-      <c r="D9" s="86" t="s">
-        <v>259</v>
-      </c>
-      <c r="E9" s="86" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="10" s="81" customFormat="1" spans="1:5">
-      <c r="A10" s="85" t="s">
-        <v>268</v>
-      </c>
-      <c r="B10" s="86" t="s">
-        <v>269</v>
-      </c>
-      <c r="C10" s="86">
-        <v>4</v>
-      </c>
-      <c r="D10" s="86" t="s">
-        <v>259</v>
-      </c>
-      <c r="E10" s="86" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="11" s="81" customFormat="1" spans="1:5">
-      <c r="A11" s="85" t="s">
-        <v>271</v>
-      </c>
-      <c r="B11" s="86" t="s">
-        <v>252</v>
-      </c>
-      <c r="C11" s="86">
+      <c r="D12" s="84" t="s">
+        <v>258</v>
+      </c>
+      <c r="E12" s="84" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="13" s="81" customFormat="1" spans="1:5">
+      <c r="A13" s="83" t="s">
+        <v>280</v>
+      </c>
+      <c r="B13" s="84" t="s">
+        <v>265</v>
+      </c>
+      <c r="C13" s="84">
         <v>2</v>
       </c>
-      <c r="D11" s="86" t="s">
-        <v>259</v>
-      </c>
-      <c r="E11" s="86" t="s">
-        <v>272</v>
-      </c>
-    </row>
-    <row r="12" s="81" customFormat="1" spans="1:5">
-      <c r="A12" s="85" t="s">
-        <v>271</v>
-      </c>
-      <c r="B12" s="86" t="s">
-        <v>255</v>
-      </c>
-      <c r="C12" s="86">
-        <v>80</v>
-      </c>
-      <c r="D12" s="86" t="s">
-        <v>259</v>
-      </c>
-      <c r="E12" s="86" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="13" s="81" customFormat="1" spans="1:5">
-      <c r="A13" s="85" t="s">
-        <v>271</v>
-      </c>
-      <c r="B13" s="86" t="s">
-        <v>252</v>
-      </c>
-      <c r="C13" s="86">
-        <v>2</v>
-      </c>
-      <c r="D13" s="86" t="s">
-        <v>259</v>
-      </c>
-      <c r="E13" s="86" t="s">
-        <v>274</v>
+      <c r="D13" s="84" t="s">
+        <v>258</v>
+      </c>
+      <c r="E13" s="84" t="s">
+        <v>283</v>
       </c>
     </row>
     <row r="14" s="81" customFormat="1" spans="1:5">
       <c r="A14" s="87" t="s">
-        <v>275</v>
-      </c>
-      <c r="B14" s="84"/>
-      <c r="C14" s="84"/>
-      <c r="D14" s="84"/>
-      <c r="E14" s="84"/>
+        <v>284</v>
+      </c>
+      <c r="B14" s="86"/>
+      <c r="C14" s="86"/>
+      <c r="D14" s="86"/>
+      <c r="E14" s="86"/>
     </row>
     <row r="15" s="81" customFormat="1" spans="1:5">
-      <c r="A15" s="83" t="s">
-        <v>276</v>
-      </c>
-      <c r="B15" s="84" t="s">
-        <v>252</v>
-      </c>
-      <c r="C15" s="84">
+      <c r="A15" s="85" t="s">
+        <v>285</v>
+      </c>
+      <c r="B15" s="86" t="s">
+        <v>265</v>
+      </c>
+      <c r="C15" s="86">
         <v>2</v>
       </c>
-      <c r="D15" s="84" t="s">
-        <v>249</v>
-      </c>
-      <c r="E15" s="84" t="s">
-        <v>277</v>
+      <c r="D15" s="86" t="s">
+        <v>262</v>
+      </c>
+      <c r="E15" s="86" t="s">
+        <v>286</v>
       </c>
     </row>
     <row r="16" s="81" customFormat="1" spans="1:5">
-      <c r="A16" s="83" t="s">
-        <v>278</v>
-      </c>
-      <c r="B16" s="84" t="s">
-        <v>255</v>
-      </c>
-      <c r="C16" s="84">
+      <c r="A16" s="85" t="s">
+        <v>287</v>
+      </c>
+      <c r="B16" s="86" t="s">
+        <v>268</v>
+      </c>
+      <c r="C16" s="86">
         <v>80</v>
       </c>
-      <c r="D16" s="84" t="s">
-        <v>249</v>
-      </c>
-      <c r="E16" s="84" t="s">
-        <v>279</v>
+      <c r="D16" s="86" t="s">
+        <v>262</v>
+      </c>
+      <c r="E16" s="86" t="s">
+        <v>288</v>
       </c>
     </row>
     <row r="17" s="81" customFormat="1" ht="12" customHeight="1" spans="1:5">
-      <c r="A17" s="85" t="s">
-        <v>280</v>
-      </c>
-      <c r="B17" s="86" t="s">
-        <v>252</v>
-      </c>
-      <c r="C17" s="86">
+      <c r="A17" s="83" t="s">
+        <v>289</v>
+      </c>
+      <c r="B17" s="84" t="s">
+        <v>265</v>
+      </c>
+      <c r="C17" s="84">
         <v>2</v>
       </c>
-      <c r="D17" s="86" t="s">
-        <v>259</v>
-      </c>
-      <c r="E17" s="86" t="s">
-        <v>281</v>
+      <c r="D17" s="84" t="s">
+        <v>258</v>
+      </c>
+      <c r="E17" s="84" t="s">
+        <v>290</v>
       </c>
     </row>
     <row r="18" s="81" customFormat="1" spans="1:5">
-      <c r="A18" s="83" t="s">
-        <v>276</v>
-      </c>
-      <c r="B18" s="86" t="s">
-        <v>252</v>
-      </c>
-      <c r="C18" s="86">
+      <c r="A18" s="85" t="s">
+        <v>285</v>
+      </c>
+      <c r="B18" s="84" t="s">
+        <v>265</v>
+      </c>
+      <c r="C18" s="84">
         <v>2</v>
       </c>
-      <c r="D18" s="86" t="s">
-        <v>259</v>
-      </c>
-      <c r="E18" s="86" t="s">
-        <v>282</v>
+      <c r="D18" s="84" t="s">
+        <v>258</v>
+      </c>
+      <c r="E18" s="84" t="s">
+        <v>291</v>
       </c>
     </row>
   </sheetData>
@@ -7184,13 +7009,13 @@
   <sheetData>
     <row r="1" ht="16.5" spans="1:4">
       <c r="A1" s="5" t="s">
-        <v>283</v>
+        <v>292</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>284</v>
+        <v>293</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>285</v>
+        <v>294</v>
       </c>
     </row>
     <row r="2" ht="16.5" spans="1:4">
@@ -7198,10 +7023,10 @@
         <v>0</v>
       </c>
       <c r="B2" s="78" t="s">
-        <v>286</v>
+        <v>295</v>
       </c>
       <c r="C2" s="26" t="s">
-        <v>287</v>
+        <v>296</v>
       </c>
     </row>
     <row r="3" ht="16.5" spans="1:4">
@@ -7209,13 +7034,13 @@
         <v>1</v>
       </c>
       <c r="B3" s="78" t="s">
-        <v>288</v>
+        <v>297</v>
       </c>
       <c r="C3" s="79" t="s">
-        <v>287</v>
+        <v>296</v>
       </c>
       <c r="D3" s="80" t="s">
-        <v>289</v>
+        <v>298</v>
       </c>
     </row>
     <row r="4" ht="16.5" spans="1:4">
@@ -7223,10 +7048,10 @@
         <v>10</v>
       </c>
       <c r="B4" s="78" t="s">
-        <v>290</v>
+        <v>299</v>
       </c>
       <c r="C4" s="26" t="s">
-        <v>291</v>
+        <v>300</v>
       </c>
       <c r="D4" s="80"/>
     </row>
@@ -7235,10 +7060,10 @@
         <v>100</v>
       </c>
       <c r="B5" s="24" t="s">
-        <v>292</v>
+        <v>301</v>
       </c>
       <c r="C5" s="26" t="s">
-        <v>291</v>
+        <v>300</v>
       </c>
       <c r="D5" s="80"/>
     </row>
@@ -7247,10 +7072,10 @@
         <v>200</v>
       </c>
       <c r="B6" s="24" t="s">
-        <v>293</v>
+        <v>302</v>
       </c>
       <c r="C6" s="26" t="s">
-        <v>291</v>
+        <v>300</v>
       </c>
       <c r="D6" s="80"/>
     </row>

--- a/equipment_sequence/manual.xlsx
+++ b/equipment_sequence/manual.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375" tabRatio="485" firstSheet="1" activeTab="7"/>
+    <workbookView windowWidth="27945" windowHeight="12375" tabRatio="485" firstSheet="1" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="secs指令" sheetId="14" r:id="rId1"/>
@@ -308,7 +308,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="653" uniqueCount="423">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="657" uniqueCount="426">
   <si>
     <t>direction</t>
   </si>
@@ -1090,6 +1090,15 @@
   </si>
   <si>
     <t>Host 服务监控设备端的服务ip和端口列表</t>
+  </si>
+  <si>
+    <t>equipment_type</t>
+  </si>
+  <si>
+    <t>plc</t>
+  </si>
+  <si>
+    <t>控制设备运行的类型, plc: plc 控制运动, socket:板卡控制运动(通过 socket 和 mes 通讯)</t>
   </si>
   <si>
     <t>remote_command</t>
@@ -2824,7 +2833,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="110">
+  <cellXfs count="104">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -3105,21 +3114,6 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -3130,9 +3124,6 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -4061,41 +4052,41 @@
   <sheetData>
     <row r="1" ht="21" spans="1:6">
       <c r="A1" s="74" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="B1" s="74" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="C1" s="74" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="D1" s="74" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="E1" s="74" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
     </row>
     <row r="2" ht="21" spans="1:6">
       <c r="A2" s="74" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="B2" s="16" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="C2" s="16" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="D2" s="16" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="E2" s="75" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
     </row>
     <row r="3" ht="21" spans="1:6">
       <c r="A3" s="74" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="B3" s="16">
         <v>5</v>
@@ -4112,44 +4103,44 @@
     </row>
     <row r="4" ht="21" spans="1:6">
       <c r="A4" s="74" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="B4" s="16" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="C4" s="16" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="D4" s="16" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="E4" s="75" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="F4" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
     </row>
     <row r="5" ht="21" spans="1:6">
       <c r="A5" s="74" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="B5" s="16" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="C5" s="16" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="D5" s="16" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="E5" s="75" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
     </row>
     <row r="6" ht="21" spans="1:6">
       <c r="A6" s="74" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="B6" s="16">
         <v>1</v>
@@ -4166,22 +4157,22 @@
     </row>
     <row r="7" ht="21" spans="1:6">
       <c r="A7" s="74" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="B7" s="16" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="C7" s="16" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="D7" s="16"/>
       <c r="E7" s="75" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
     </row>
     <row r="8" ht="21" spans="1:6">
       <c r="A8" s="74" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="B8" s="75">
         <v>0</v>
@@ -4198,7 +4189,7 @@
     </row>
     <row r="9" ht="21" spans="1:6">
       <c r="A9" s="74" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="B9" s="75">
         <v>0</v>
@@ -4236,13 +4227,13 @@
   <sheetData>
     <row r="1" ht="14.25" spans="1:7">
       <c r="A1" s="53" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="B1" s="54" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="C1" s="55" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="D1" s="56"/>
       <c r="E1" s="57"/>
@@ -4255,16 +4246,16 @@
       <c r="A2" s="59"/>
       <c r="B2" s="60"/>
       <c r="C2" s="61" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="D2" s="61" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="E2" s="62" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="F2" s="62" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="G2" s="63"/>
     </row>
@@ -4273,23 +4264,23 @@
         <v>4000</v>
       </c>
       <c r="B3" s="65" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="C3" s="66" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="D3" s="66"/>
       <c r="E3" s="67"/>
       <c r="F3" s="64"/>
       <c r="G3" s="67" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4" s="64"/>
       <c r="B4" s="68"/>
       <c r="C4" s="66" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="D4" s="66"/>
       <c r="E4" s="67"/>
@@ -4301,16 +4292,16 @@
         <v>4001</v>
       </c>
       <c r="B5" s="67" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="C5" s="66" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="D5" s="66"/>
       <c r="E5" s="67"/>
       <c r="F5" s="64"/>
       <c r="G5" s="67" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -4318,23 +4309,23 @@
         <v>4002</v>
       </c>
       <c r="B6" s="70" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="C6" s="66" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="D6" s="66"/>
       <c r="E6" s="67"/>
       <c r="F6" s="64"/>
       <c r="G6" s="69" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7" s="71"/>
       <c r="B7" s="68"/>
       <c r="C7" s="66" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="D7" s="66"/>
       <c r="E7" s="67"/>
@@ -4345,10 +4336,10 @@
       <c r="A8" s="71"/>
       <c r="B8" s="68"/>
       <c r="C8" s="66" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="D8" s="66" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="E8" s="67"/>
       <c r="F8" s="64"/>
@@ -4358,7 +4349,7 @@
       <c r="A9" s="72"/>
       <c r="B9" s="73"/>
       <c r="C9" s="66" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="D9" s="66"/>
       <c r="E9" s="66"/>
@@ -4370,13 +4361,13 @@
         <v>4003</v>
       </c>
       <c r="B10" s="70" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="C10" s="66" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="D10" s="66" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="E10" s="66"/>
       <c r="F10" s="66"/>
@@ -4386,10 +4377,10 @@
       <c r="A11" s="72"/>
       <c r="B11" s="73"/>
       <c r="C11" s="66" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="D11" s="66" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="E11" s="66"/>
       <c r="F11" s="66"/>
@@ -4400,10 +4391,10 @@
         <v>4004</v>
       </c>
       <c r="B12" s="70" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="C12" s="66" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="D12" s="66"/>
       <c r="E12" s="66"/>
@@ -4414,7 +4405,7 @@
       <c r="A13" s="72"/>
       <c r="B13" s="73"/>
       <c r="C13" s="66" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="D13" s="66"/>
       <c r="E13" s="66"/>
@@ -4426,10 +4417,10 @@
         <v>4005</v>
       </c>
       <c r="B14" s="70" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="C14" s="66" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="D14" s="66"/>
       <c r="E14" s="66"/>
@@ -4440,7 +4431,7 @@
       <c r="A15" s="72"/>
       <c r="B15" s="73"/>
       <c r="C15" s="66" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="D15" s="66"/>
       <c r="E15" s="66"/>
@@ -4452,10 +4443,10 @@
         <v>4006</v>
       </c>
       <c r="B16" s="70" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="C16" s="66" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="D16" s="66"/>
       <c r="E16" s="66"/>
@@ -4466,7 +4457,7 @@
       <c r="A17" s="72"/>
       <c r="B17" s="73"/>
       <c r="C17" s="66" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="D17" s="66"/>
       <c r="E17" s="66"/>
@@ -4478,10 +4469,10 @@
         <v>4007</v>
       </c>
       <c r="B18" s="70" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="C18" s="66" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="D18" s="66"/>
       <c r="E18" s="66"/>
@@ -4492,7 +4483,7 @@
       <c r="A19" s="72"/>
       <c r="B19" s="73"/>
       <c r="C19" s="66" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="D19" s="66"/>
       <c r="E19" s="66"/>
@@ -4504,10 +4495,10 @@
         <v>4008</v>
       </c>
       <c r="B20" s="70" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="C20" s="66" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="D20" s="66"/>
       <c r="E20" s="67"/>
@@ -4518,7 +4509,7 @@
       <c r="A21" s="72"/>
       <c r="B21" s="73"/>
       <c r="C21" s="66" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="D21" s="66"/>
       <c r="E21" s="67"/>
@@ -4578,27 +4569,27 @@
   <sheetData>
     <row r="1" ht="21.75" spans="4:13">
       <c r="D1" s="2" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
     </row>
     <row r="2" ht="16.5" spans="4:13">
       <c r="D2" s="3" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="G2" s="5" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="H2" s="6" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="I2" s="4" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
     </row>
     <row r="3" ht="16.5" spans="4:13">
@@ -4606,7 +4597,7 @@
         <v>1</v>
       </c>
       <c r="E3" s="7" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="F3" s="7">
         <v>1</v>
@@ -4615,10 +4606,10 @@
         <v>1</v>
       </c>
       <c r="H3" s="8" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="I3" s="9" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
     </row>
     <row r="4" ht="16.5" spans="4:13">
@@ -4627,7 +4618,7 @@
       <c r="F4" s="10"/>
       <c r="G4" s="10"/>
       <c r="H4" s="8" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="I4" s="11"/>
     </row>
@@ -4637,7 +4628,7 @@
       <c r="F5" s="10"/>
       <c r="G5" s="10"/>
       <c r="H5" s="8" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="I5" s="11"/>
     </row>
@@ -4647,7 +4638,7 @@
       <c r="F6" s="10"/>
       <c r="G6" s="10"/>
       <c r="H6" s="8" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="I6" s="11"/>
     </row>
@@ -4657,7 +4648,7 @@
       <c r="F7" s="12"/>
       <c r="G7" s="12"/>
       <c r="H7" s="8" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="I7" s="13"/>
     </row>
@@ -4666,7 +4657,7 @@
         <v>2</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="F8" s="7">
         <v>2</v>
@@ -4675,16 +4666,16 @@
         <v>2</v>
       </c>
       <c r="H8" s="8" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="I8" s="9" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="K8" s="14" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="L8" s="4" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="M8" s="15"/>
     </row>
@@ -4694,17 +4685,17 @@
       <c r="F9" s="10"/>
       <c r="G9" s="10"/>
       <c r="H9" s="8" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="I9" s="11"/>
       <c r="K9" s="16">
         <v>1</v>
       </c>
       <c r="L9" s="16" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="M9" s="17" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
     </row>
     <row r="10" ht="16.5" spans="4:13">
@@ -4713,13 +4704,13 @@
       <c r="F10" s="10"/>
       <c r="G10" s="10"/>
       <c r="H10" s="8" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="I10" s="11"/>
       <c r="K10" s="18"/>
       <c r="L10" s="18"/>
       <c r="M10" s="17" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
     </row>
     <row r="11" ht="16.5" spans="4:13">
@@ -4728,13 +4719,13 @@
       <c r="F11" s="12"/>
       <c r="G11" s="12"/>
       <c r="H11" s="8" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="I11" s="13"/>
       <c r="K11" s="18"/>
       <c r="L11" s="18"/>
       <c r="M11" s="17" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
     </row>
     <row r="12" ht="16.5" spans="4:13">
@@ -4742,7 +4733,7 @@
         <v>3</v>
       </c>
       <c r="E12" s="20" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="F12" s="20">
         <v>3</v>
@@ -4751,15 +4742,15 @@
         <v>3</v>
       </c>
       <c r="H12" s="21" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="I12" s="21" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="K12" s="18"/>
       <c r="L12" s="18"/>
       <c r="M12" s="17" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
     </row>
     <row r="13" ht="16.5" spans="4:13">
@@ -4767,7 +4758,7 @@
         <v>4</v>
       </c>
       <c r="E13" s="22" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="F13" s="22">
         <v>4</v>
@@ -4776,15 +4767,15 @@
         <v>4</v>
       </c>
       <c r="H13" s="24" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="I13" s="24" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="K13" s="19"/>
       <c r="L13" s="19"/>
       <c r="M13" s="25" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
     </row>
     <row r="14" ht="16.5" spans="4:13">
@@ -4795,19 +4786,19 @@
         <v>5</v>
       </c>
       <c r="H14" s="24" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="I14" s="24" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="K14" s="16">
         <v>2</v>
       </c>
       <c r="L14" s="16" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="M14" s="17" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
     </row>
     <row r="15" ht="16.5" spans="4:13">
@@ -4815,7 +4806,7 @@
         <v>5</v>
       </c>
       <c r="E15" s="22" t="s">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="F15" s="22">
         <v>5</v>
@@ -4824,15 +4815,15 @@
         <v>4</v>
       </c>
       <c r="H15" s="24" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="I15" s="24" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="K15" s="18"/>
       <c r="L15" s="18"/>
       <c r="M15" s="17" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
     </row>
     <row r="16" ht="16.5" spans="4:13">
@@ -4843,15 +4834,15 @@
         <v>5</v>
       </c>
       <c r="H16" s="24" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="I16" s="24" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="K16" s="18"/>
       <c r="L16" s="18"/>
       <c r="M16" s="17" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
     </row>
     <row r="17" ht="16.5" spans="4:14">
@@ -4862,15 +4853,15 @@
         <v>6</v>
       </c>
       <c r="H17" s="24" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="I17" s="24" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="K17" s="19"/>
       <c r="L17" s="19"/>
       <c r="M17" s="25" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
     </row>
     <row r="18" ht="16.5" spans="4:14">
@@ -4878,7 +4869,7 @@
         <v>6</v>
       </c>
       <c r="E18" s="23" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="F18" s="22">
         <v>6</v>
@@ -4887,19 +4878,19 @@
         <v>4</v>
       </c>
       <c r="H18" s="28" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="I18" s="28" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="K18" s="19">
         <v>3</v>
       </c>
       <c r="L18" s="20" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="M18" s="25" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
     </row>
     <row r="19" ht="16.5" spans="4:14">
@@ -4907,7 +4898,7 @@
         <v>7</v>
       </c>
       <c r="E19" s="23" t="s">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="F19" s="26"/>
       <c r="G19" s="26"/>
@@ -4917,10 +4908,10 @@
         <v>4</v>
       </c>
       <c r="L19" s="20" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="M19" s="25" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
     </row>
     <row r="20" ht="16.5" spans="4:14">
@@ -4928,7 +4919,7 @@
         <v>8</v>
       </c>
       <c r="E20" s="23" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="F20" s="22">
         <v>8</v>
@@ -4937,10 +4928,10 @@
         <v>8</v>
       </c>
       <c r="H20" s="28" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="I20" s="28" t="s">
-        <v>386</v>
+        <v>389</v>
       </c>
     </row>
     <row r="21" ht="16.5" spans="4:14">
@@ -4948,7 +4939,7 @@
         <v>9</v>
       </c>
       <c r="E21" s="23" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="F21" s="26"/>
       <c r="G21" s="26"/>
@@ -4960,7 +4951,7 @@
         <v>10</v>
       </c>
       <c r="E22" s="23" t="s">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="F22" s="23">
         <v>10</v>
@@ -4969,10 +4960,10 @@
         <v>10</v>
       </c>
       <c r="H22" s="24" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="I22" s="24" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
     </row>
     <row r="23" ht="16.5" spans="4:14">
@@ -4999,16 +4990,16 @@
       <c r="H25" s="23"/>
       <c r="I25" s="23"/>
       <c r="K25" s="30" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="L25" s="31" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="M25" s="31" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="N25" s="31" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
     </row>
     <row r="26" ht="32.25" spans="4:14">
@@ -5019,40 +5010,40 @@
       <c r="H26" s="23"/>
       <c r="I26" s="23"/>
       <c r="K26" s="32" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="L26" s="33" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="M26" s="33"/>
       <c r="N26" s="33" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
     </row>
     <row r="27" ht="16.5" spans="4:14">
       <c r="D27" s="19"/>
       <c r="E27" s="23" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="F27" s="23"/>
       <c r="G27" s="23"/>
       <c r="H27" s="23"/>
       <c r="I27" s="23"/>
       <c r="K27" s="32" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="L27" s="33" t="s">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="M27" s="33"/>
       <c r="N27" s="33" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
     </row>
     <row r="28" ht="16.5" spans="4:14">
       <c r="D28" s="34"/>
       <c r="E28" s="23" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="F28" s="23"/>
       <c r="G28" s="23"/>
@@ -5062,45 +5053,45 @@
     <row r="37" ht="14.25"/>
     <row r="38" ht="16.5" spans="4:10">
       <c r="D38" s="35" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="E38" s="36" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="F38" s="36" t="s">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="G38" s="36" t="s">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="H38" s="37" t="s">
+        <v>404</v>
+      </c>
+      <c r="I38" s="38" t="s">
         <v>401</v>
       </c>
-      <c r="I38" s="38" t="s">
-        <v>398</v>
-      </c>
       <c r="J38" s="39" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
     </row>
     <row r="39" ht="16.5" spans="4:10">
       <c r="D39" s="40" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="E39" s="41" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c r="F39" s="42" t="s">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="G39" s="41" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="H39" s="19">
         <v>1</v>
       </c>
       <c r="I39" s="20" t="s">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="J39" s="20">
         <v>2</v>
@@ -5110,14 +5101,14 @@
       <c r="D40" s="43"/>
       <c r="E40" s="44"/>
       <c r="F40" s="42" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="G40" s="44"/>
       <c r="H40" s="19">
         <v>2</v>
       </c>
       <c r="I40" s="20" t="s">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c r="J40" s="20">
         <v>2</v>
@@ -5127,7 +5118,7 @@
       <c r="D41" s="43"/>
       <c r="E41" s="44"/>
       <c r="F41" s="45" t="s">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="G41" s="44"/>
     </row>
@@ -5135,7 +5126,7 @@
       <c r="D42" s="43"/>
       <c r="E42" s="44"/>
       <c r="F42" s="46" t="s">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c r="G42" s="44"/>
     </row>
@@ -5143,7 +5134,7 @@
       <c r="D43" s="43"/>
       <c r="E43" s="44"/>
       <c r="F43" s="46" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="G43" s="44"/>
     </row>
@@ -5151,7 +5142,7 @@
       <c r="D44" s="43"/>
       <c r="E44" s="44"/>
       <c r="F44" s="46" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="G44" s="44"/>
     </row>
@@ -5159,7 +5150,7 @@
       <c r="D45" s="43"/>
       <c r="E45" s="44"/>
       <c r="F45" s="46" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="G45" s="44"/>
     </row>
@@ -5167,7 +5158,7 @@
       <c r="D46" s="43"/>
       <c r="E46" s="44"/>
       <c r="F46" s="46" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="G46" s="44"/>
     </row>
@@ -5175,7 +5166,7 @@
       <c r="D47" s="43"/>
       <c r="E47" s="44"/>
       <c r="F47" s="46" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="G47" s="44"/>
     </row>
@@ -5183,7 +5174,7 @@
       <c r="D48" s="43"/>
       <c r="E48" s="44"/>
       <c r="F48" s="46" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="G48" s="44"/>
     </row>
@@ -5191,7 +5182,7 @@
       <c r="D49" s="43"/>
       <c r="E49" s="44"/>
       <c r="F49" s="46" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="G49" s="44"/>
     </row>
@@ -5199,7 +5190,7 @@
       <c r="D50" s="43"/>
       <c r="E50" s="44"/>
       <c r="F50" s="46" t="s">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="G50" s="44"/>
     </row>
@@ -5207,7 +5198,7 @@
       <c r="D51" s="43"/>
       <c r="E51" s="44"/>
       <c r="F51" s="46" t="s">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="G51" s="44"/>
     </row>
@@ -5215,23 +5206,23 @@
       <c r="D52" s="47"/>
       <c r="E52" s="48"/>
       <c r="F52" s="49" t="s">
-        <v>420</v>
+        <v>423</v>
       </c>
       <c r="G52" s="48"/>
     </row>
     <row r="53" ht="21" spans="4:7">
       <c r="D53" s="50" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
     </row>
     <row r="54" ht="15.75" spans="4:7">
       <c r="D54" s="51" t="s">
-        <v>404</v>
+        <v>407</v>
       </c>
     </row>
     <row r="55" ht="15.75" spans="4:7">
       <c r="D55" s="52" t="s">
-        <v>422</v>
+        <v>425</v>
       </c>
     </row>
   </sheetData>
@@ -5291,176 +5282,176 @@
   </cols>
   <sheetData>
     <row r="1" ht="33" customHeight="1" spans="1:8">
-      <c r="A1" s="107" t="s">
+      <c r="A1" s="101" t="s">
         <v>98</v>
       </c>
-      <c r="B1" s="107" t="s">
+      <c r="B1" s="101" t="s">
         <v>99</v>
       </c>
-      <c r="C1" s="107" t="s">
+      <c r="C1" s="101" t="s">
         <v>100</v>
       </c>
-      <c r="D1" s="107" t="s">
+      <c r="D1" s="101" t="s">
         <v>101</v>
       </c>
-      <c r="E1" s="107" t="s">
+      <c r="E1" s="101" t="s">
         <v>102</v>
       </c>
-      <c r="F1" s="107" t="s">
+      <c r="F1" s="101" t="s">
         <v>103</v>
       </c>
-      <c r="G1" s="107" t="s">
+      <c r="G1" s="101" t="s">
         <v>104</v>
       </c>
-      <c r="H1" s="107" t="s">
+      <c r="H1" s="101" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="2" s="106" customFormat="1" ht="75" spans="1:8">
-      <c r="A2" s="108">
+    <row r="2" s="100" customFormat="1" ht="75" spans="1:8">
+      <c r="A2" s="102">
         <v>5001</v>
       </c>
-      <c r="B2" s="108" t="s">
+      <c r="B2" s="102" t="s">
         <v>106</v>
       </c>
-      <c r="C2" s="109" t="s">
+      <c r="C2" s="103" t="s">
         <v>107</v>
       </c>
-      <c r="D2" s="108">
+      <c r="D2" s="102">
         <v>1</v>
       </c>
-      <c r="E2" s="101">
+      <c r="E2" s="96">
         <v>501</v>
       </c>
-      <c r="F2" s="101" t="s">
+      <c r="F2" s="96" t="s">
         <v>108</v>
       </c>
-      <c r="G2" s="101" t="s">
+      <c r="G2" s="96" t="s">
         <v>109</v>
       </c>
-      <c r="H2" s="102" t="s">
+      <c r="H2" s="97" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="3" s="106" customFormat="1" ht="75" spans="1:8">
-      <c r="A3" s="108">
+    <row r="3" s="100" customFormat="1" ht="75" spans="1:8">
+      <c r="A3" s="102">
         <v>5002</v>
       </c>
-      <c r="B3" s="108" t="s">
+      <c r="B3" s="102" t="s">
         <v>111</v>
       </c>
-      <c r="C3" s="109" t="s">
+      <c r="C3" s="103" t="s">
         <v>112</v>
       </c>
-      <c r="D3" s="108">
+      <c r="D3" s="102">
         <v>2</v>
       </c>
-      <c r="E3" s="101">
+      <c r="E3" s="96">
         <v>501</v>
       </c>
-      <c r="F3" s="101" t="s">
+      <c r="F3" s="96" t="s">
         <v>108</v>
       </c>
-      <c r="G3" s="101" t="s">
+      <c r="G3" s="96" t="s">
         <v>109</v>
       </c>
-      <c r="H3" s="102" t="s">
+      <c r="H3" s="97" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="4" s="106" customFormat="1" ht="75" spans="1:8">
-      <c r="A4" s="108">
+    <row r="4" s="100" customFormat="1" ht="75" spans="1:8">
+      <c r="A4" s="102">
         <v>5003</v>
       </c>
-      <c r="B4" s="108" t="s">
+      <c r="B4" s="102" t="s">
         <v>113</v>
       </c>
-      <c r="C4" s="109" t="s">
+      <c r="C4" s="103" t="s">
         <v>114</v>
       </c>
-      <c r="D4" s="108">
+      <c r="D4" s="102">
         <v>3</v>
       </c>
-      <c r="E4" s="101">
+      <c r="E4" s="96">
         <v>501</v>
       </c>
-      <c r="F4" s="101" t="s">
+      <c r="F4" s="96" t="s">
         <v>108</v>
       </c>
-      <c r="G4" s="101" t="s">
+      <c r="G4" s="96" t="s">
         <v>109</v>
       </c>
-      <c r="H4" s="102" t="s">
+      <c r="H4" s="97" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="5" s="106" customFormat="1" ht="75" spans="1:8">
-      <c r="A5" s="108">
+    <row r="5" s="100" customFormat="1" ht="75" spans="1:8">
+      <c r="A5" s="102">
         <v>5004</v>
       </c>
-      <c r="B5" s="108" t="s">
+      <c r="B5" s="102" t="s">
         <v>115</v>
       </c>
-      <c r="C5" s="109" t="s">
+      <c r="C5" s="103" t="s">
         <v>116</v>
       </c>
-      <c r="D5" s="108">
+      <c r="D5" s="102">
         <v>4</v>
       </c>
-      <c r="E5" s="101">
+      <c r="E5" s="96">
         <v>501</v>
       </c>
-      <c r="F5" s="101" t="s">
+      <c r="F5" s="96" t="s">
         <v>108</v>
       </c>
-      <c r="G5" s="101" t="s">
+      <c r="G5" s="96" t="s">
         <v>109</v>
       </c>
-      <c r="H5" s="102" t="s">
+      <c r="H5" s="97" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="6" s="106" customFormat="1" ht="56.25" spans="1:8">
-      <c r="A6" s="108">
+    <row r="6" s="100" customFormat="1" ht="56.25" spans="1:8">
+      <c r="A6" s="102">
         <v>5005</v>
       </c>
-      <c r="B6" s="108" t="s">
+      <c r="B6" s="102" t="s">
         <v>117</v>
       </c>
-      <c r="C6" s="109" t="s">
+      <c r="C6" s="103" t="s">
         <v>118</v>
       </c>
-      <c r="D6" s="108">
+      <c r="D6" s="102">
         <v>5</v>
       </c>
-      <c r="E6" s="108">
+      <c r="E6" s="102">
         <v>502</v>
       </c>
-      <c r="F6" s="108" t="s">
+      <c r="F6" s="102" t="s">
         <v>119</v>
       </c>
-      <c r="G6" s="108" t="s">
+      <c r="G6" s="102" t="s">
         <v>109</v>
       </c>
-      <c r="H6" s="102" t="s">
+      <c r="H6" s="97" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="7" s="106" customFormat="1" ht="20.25" spans="1:8">
-      <c r="A7" s="108"/>
-      <c r="B7" s="108"/>
-      <c r="C7" s="109"/>
-      <c r="D7" s="108"/>
-      <c r="E7" s="101">
+    <row r="7" s="100" customFormat="1" ht="20.25" spans="1:8">
+      <c r="A7" s="102"/>
+      <c r="B7" s="102"/>
+      <c r="C7" s="103"/>
+      <c r="D7" s="102"/>
+      <c r="E7" s="96">
         <v>503</v>
       </c>
-      <c r="F7" s="101" t="s">
+      <c r="F7" s="96" t="s">
         <v>121</v>
       </c>
-      <c r="G7" s="101" t="s">
+      <c r="G7" s="96" t="s">
         <v>109</v>
       </c>
-      <c r="H7" s="109" t="s">
+      <c r="H7" s="103" t="s">
         <v>122</v>
       </c>
     </row>
@@ -5484,13 +5475,13 @@
   <dimension ref="A1:G20"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18.75" outlineLevelCol="6"/>
   <cols>
-    <col min="1" max="1" width="6.66666666666667" style="100" customWidth="1"/>
-    <col min="2" max="2" width="29.8833333333333" style="100" customWidth="1"/>
-    <col min="3" max="3" width="16" style="100" customWidth="1"/>
-    <col min="4" max="5" width="25.125" style="100" customWidth="1"/>
-    <col min="6" max="6" width="57.5" style="100" customWidth="1"/>
-    <col min="7" max="7" width="36.375" style="100" customWidth="1"/>
-    <col min="8" max="16384" width="9" style="100"/>
+    <col min="1" max="1" width="6.66666666666667" style="95" customWidth="1"/>
+    <col min="2" max="2" width="29.8833333333333" style="95" customWidth="1"/>
+    <col min="3" max="3" width="16" style="95" customWidth="1"/>
+    <col min="4" max="5" width="25.125" style="95" customWidth="1"/>
+    <col min="6" max="6" width="57.5" style="95" customWidth="1"/>
+    <col min="7" max="7" width="36.375" style="95" customWidth="1"/>
+    <col min="8" max="16384" width="9" style="95"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
@@ -5513,322 +5504,322 @@
         <v>127</v>
       </c>
     </row>
-    <row r="2" s="99" customFormat="1" ht="75" spans="1:7">
-      <c r="A2" s="101">
+    <row r="2" s="94" customFormat="1" ht="75" spans="1:7">
+      <c r="A2" s="96">
         <v>501</v>
       </c>
-      <c r="B2" s="101" t="s">
+      <c r="B2" s="96" t="s">
         <v>108</v>
       </c>
-      <c r="C2" s="101" t="s">
+      <c r="C2" s="96" t="s">
         <v>109</v>
       </c>
-      <c r="D2" s="101"/>
-      <c r="E2" s="101"/>
-      <c r="F2" s="102" t="s">
+      <c r="D2" s="96"/>
+      <c r="E2" s="96"/>
+      <c r="F2" s="97" t="s">
         <v>110</v>
       </c>
-      <c r="G2" s="100"/>
-    </row>
-    <row r="3" s="100" customFormat="1" ht="56.25" spans="1:7">
-      <c r="A3" s="101">
+      <c r="G2" s="95"/>
+    </row>
+    <row r="3" s="95" customFormat="1" ht="56.25" spans="1:7">
+      <c r="A3" s="96">
         <v>502</v>
       </c>
-      <c r="B3" s="101" t="s">
+      <c r="B3" s="96" t="s">
         <v>119</v>
       </c>
-      <c r="C3" s="101" t="s">
+      <c r="C3" s="96" t="s">
         <v>109</v>
       </c>
-      <c r="D3" s="101"/>
-      <c r="E3" s="101"/>
-      <c r="F3" s="102" t="s">
+      <c r="D3" s="96"/>
+      <c r="E3" s="96"/>
+      <c r="F3" s="97" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="4" s="100" customFormat="1" spans="1:7">
-      <c r="A4" s="101">
+    <row r="4" s="95" customFormat="1" spans="1:7">
+      <c r="A4" s="96">
         <v>503</v>
       </c>
-      <c r="B4" s="101" t="s">
+      <c r="B4" s="96" t="s">
         <v>121</v>
       </c>
-      <c r="C4" s="101" t="s">
+      <c r="C4" s="96" t="s">
         <v>109</v>
       </c>
-      <c r="D4" s="101"/>
-      <c r="E4" s="101"/>
-      <c r="F4" s="101" t="s">
+      <c r="D4" s="96"/>
+      <c r="E4" s="96"/>
+      <c r="F4" s="96" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="5" s="100" customFormat="1" spans="1:7">
-      <c r="A5" s="101">
+    <row r="5" s="95" customFormat="1" spans="1:7">
+      <c r="A5" s="96">
         <v>504</v>
       </c>
-      <c r="B5" s="101" t="s">
+      <c r="B5" s="96" t="s">
         <v>128</v>
       </c>
-      <c r="C5" s="101" t="s">
+      <c r="C5" s="96" t="s">
         <v>129</v>
       </c>
-      <c r="D5" s="101"/>
-      <c r="E5" s="101"/>
-      <c r="F5" s="101" t="s">
+      <c r="D5" s="96"/>
+      <c r="E5" s="96"/>
+      <c r="F5" s="96" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="6" s="100" customFormat="1" spans="1:7">
-      <c r="A6" s="101">
+    <row r="6" s="95" customFormat="1" spans="1:7">
+      <c r="A6" s="96">
         <v>505</v>
       </c>
-      <c r="B6" s="101" t="s">
+      <c r="B6" s="96" t="s">
         <v>131</v>
       </c>
-      <c r="C6" s="101" t="s">
+      <c r="C6" s="96" t="s">
         <v>129</v>
       </c>
-      <c r="D6" s="101"/>
-      <c r="E6" s="102" t="s">
+      <c r="D6" s="96"/>
+      <c r="E6" s="97" t="s">
         <v>132</v>
       </c>
-      <c r="F6" s="101" t="s">
+      <c r="F6" s="96" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="7" s="100" customFormat="1" spans="1:7">
-      <c r="A7" s="101">
+    <row r="7" s="95" customFormat="1" spans="1:7">
+      <c r="A7" s="96">
         <v>506</v>
       </c>
-      <c r="B7" s="101" t="s">
+      <c r="B7" s="96" t="s">
         <v>134</v>
       </c>
-      <c r="C7" s="101" t="s">
+      <c r="C7" s="96" t="s">
         <v>129</v>
       </c>
-      <c r="D7" s="101"/>
-      <c r="E7" s="102"/>
-      <c r="F7" s="101" t="s">
+      <c r="D7" s="96"/>
+      <c r="E7" s="97"/>
+      <c r="F7" s="96" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="8" s="100" customFormat="1" spans="1:7">
-      <c r="A8" s="101">
+    <row r="8" s="95" customFormat="1" spans="1:7">
+      <c r="A8" s="96">
         <v>511</v>
       </c>
-      <c r="B8" s="101" t="s">
+      <c r="B8" s="96" t="s">
         <v>136</v>
       </c>
-      <c r="C8" s="101" t="s">
+      <c r="C8" s="96" t="s">
         <v>129</v>
       </c>
-      <c r="D8" s="101"/>
-      <c r="E8" s="102"/>
-      <c r="F8" s="101" t="s">
+      <c r="D8" s="96"/>
+      <c r="E8" s="97"/>
+      <c r="F8" s="96" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="9" s="100" customFormat="1" spans="1:7">
-      <c r="A9" s="101">
+    <row r="9" s="95" customFormat="1" spans="1:7">
+      <c r="A9" s="96">
         <v>512</v>
       </c>
-      <c r="B9" s="101" t="s">
+      <c r="B9" s="96" t="s">
         <v>138</v>
       </c>
-      <c r="C9" s="101" t="s">
+      <c r="C9" s="96" t="s">
         <v>109</v>
       </c>
-      <c r="D9" s="101"/>
-      <c r="E9" s="102"/>
-      <c r="F9" s="101" t="s">
+      <c r="D9" s="96"/>
+      <c r="E9" s="97"/>
+      <c r="F9" s="96" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="10" s="100" customFormat="1" spans="1:7">
-      <c r="A10" s="101">
+    <row r="10" s="95" customFormat="1" spans="1:7">
+      <c r="A10" s="96">
         <v>513</v>
       </c>
-      <c r="B10" s="101" t="s">
+      <c r="B10" s="96" t="s">
         <v>140</v>
       </c>
-      <c r="C10" s="101" t="s">
+      <c r="C10" s="96" t="s">
         <v>109</v>
       </c>
-      <c r="D10" s="101"/>
-      <c r="E10" s="102"/>
-      <c r="F10" s="101" t="s">
+      <c r="D10" s="96"/>
+      <c r="E10" s="97"/>
+      <c r="F10" s="96" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="11" s="100" customFormat="1" spans="1:7">
-      <c r="A11" s="101">
+    <row r="11" s="95" customFormat="1" spans="1:7">
+      <c r="A11" s="96">
         <v>514</v>
       </c>
-      <c r="B11" s="101" t="s">
+      <c r="B11" s="96" t="s">
         <v>142</v>
       </c>
-      <c r="C11" s="101" t="s">
+      <c r="C11" s="96" t="s">
         <v>109</v>
       </c>
-      <c r="D11" s="101"/>
-      <c r="E11" s="102">
+      <c r="D11" s="96"/>
+      <c r="E11" s="97">
         <v>1</v>
       </c>
-      <c r="F11" s="101" t="s">
+      <c r="F11" s="96" t="s">
         <v>143</v>
       </c>
     </row>
-    <row r="12" s="100" customFormat="1" spans="1:7">
-      <c r="A12" s="101">
+    <row r="12" s="95" customFormat="1" spans="1:7">
+      <c r="A12" s="96">
         <v>515</v>
       </c>
-      <c r="B12" s="101" t="s">
+      <c r="B12" s="96" t="s">
         <v>144</v>
       </c>
-      <c r="C12" s="101" t="s">
+      <c r="C12" s="96" t="s">
         <v>109</v>
       </c>
-      <c r="D12" s="101"/>
-      <c r="E12" s="102">
+      <c r="D12" s="96"/>
+      <c r="E12" s="97">
         <v>2</v>
       </c>
-      <c r="F12" s="101" t="s">
+      <c r="F12" s="96" t="s">
         <v>145</v>
       </c>
     </row>
-    <row r="13" s="99" customFormat="1" spans="1:7">
-      <c r="A13" s="101">
+    <row r="13" s="94" customFormat="1" spans="1:7">
+      <c r="A13" s="96">
         <v>516</v>
       </c>
-      <c r="B13" s="101" t="s">
+      <c r="B13" s="96" t="s">
         <v>146</v>
       </c>
-      <c r="C13" s="101" t="s">
+      <c r="C13" s="96" t="s">
         <v>109</v>
       </c>
-      <c r="D13" s="101"/>
-      <c r="E13" s="102">
+      <c r="D13" s="96"/>
+      <c r="E13" s="97">
         <v>3</v>
       </c>
-      <c r="F13" s="101" t="s">
+      <c r="F13" s="96" t="s">
         <v>147</v>
       </c>
-      <c r="G13" s="100"/>
-    </row>
-    <row r="14" s="100" customFormat="1" spans="1:7">
-      <c r="A14" s="101">
+      <c r="G13" s="95"/>
+    </row>
+    <row r="14" s="95" customFormat="1" spans="1:7">
+      <c r="A14" s="96">
         <v>521</v>
       </c>
-      <c r="B14" s="101" t="s">
+      <c r="B14" s="96" t="s">
         <v>148</v>
       </c>
-      <c r="C14" s="101" t="s">
+      <c r="C14" s="96" t="s">
         <v>109</v>
       </c>
-      <c r="D14" s="101"/>
-      <c r="E14" s="102"/>
-      <c r="F14" s="102" t="s">
+      <c r="D14" s="96"/>
+      <c r="E14" s="97"/>
+      <c r="F14" s="97" t="s">
         <v>149</v>
       </c>
     </row>
-    <row r="15" s="100" customFormat="1" spans="1:7">
-      <c r="A15" s="101">
+    <row r="15" s="95" customFormat="1" spans="1:7">
+      <c r="A15" s="96">
         <v>522</v>
       </c>
-      <c r="B15" s="101" t="s">
+      <c r="B15" s="96" t="s">
         <v>150</v>
       </c>
-      <c r="C15" s="101" t="s">
+      <c r="C15" s="96" t="s">
         <v>129</v>
       </c>
-      <c r="D15" s="101"/>
-      <c r="E15" s="102"/>
-      <c r="F15" s="102" t="s">
+      <c r="D15" s="96"/>
+      <c r="E15" s="97"/>
+      <c r="F15" s="97" t="s">
         <v>151</v>
       </c>
     </row>
-    <row r="16" s="100" customFormat="1" spans="1:7">
-      <c r="A16" s="101">
+    <row r="16" s="95" customFormat="1" spans="1:7">
+      <c r="A16" s="96">
         <v>523</v>
       </c>
-      <c r="B16" s="101" t="s">
+      <c r="B16" s="96" t="s">
         <v>152</v>
       </c>
-      <c r="C16" s="101" t="s">
+      <c r="C16" s="96" t="s">
         <v>109</v>
       </c>
-      <c r="D16" s="101"/>
-      <c r="E16" s="102"/>
-      <c r="F16" s="102" t="s">
+      <c r="D16" s="96"/>
+      <c r="E16" s="97"/>
+      <c r="F16" s="97" t="s">
         <v>153</v>
       </c>
     </row>
-    <row r="17" s="100" customFormat="1" spans="1:7">
-      <c r="A17" s="101">
+    <row r="17" s="95" customFormat="1" spans="1:7">
+      <c r="A17" s="96">
         <v>524</v>
       </c>
-      <c r="B17" s="101" t="s">
+      <c r="B17" s="96" t="s">
         <v>154</v>
       </c>
-      <c r="C17" s="101" t="s">
+      <c r="C17" s="96" t="s">
         <v>129</v>
       </c>
-      <c r="D17" s="101"/>
-      <c r="E17" s="102"/>
-      <c r="F17" s="102" t="s">
+      <c r="D17" s="96"/>
+      <c r="E17" s="97"/>
+      <c r="F17" s="97" t="s">
         <v>155</v>
       </c>
     </row>
-    <row r="18" s="100" customFormat="1" spans="1:7">
-      <c r="A18" s="101">
+    <row r="18" s="95" customFormat="1" spans="1:7">
+      <c r="A18" s="96">
         <v>525</v>
       </c>
-      <c r="B18" s="101" t="s">
+      <c r="B18" s="96" t="s">
         <v>156</v>
       </c>
-      <c r="C18" s="101" t="s">
+      <c r="C18" s="96" t="s">
         <v>109</v>
       </c>
-      <c r="D18" s="101"/>
-      <c r="E18" s="102">
+      <c r="D18" s="96"/>
+      <c r="E18" s="97">
         <v>2</v>
       </c>
-      <c r="F18" s="102" t="s">
+      <c r="F18" s="97" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="19" s="100" customFormat="1" spans="1:7">
-      <c r="A19" s="101">
+    <row r="19" s="95" customFormat="1" spans="1:7">
+      <c r="A19" s="96">
         <v>526</v>
       </c>
-      <c r="B19" s="101" t="s">
+      <c r="B19" s="96" t="s">
         <v>158</v>
       </c>
-      <c r="C19" s="101" t="s">
+      <c r="C19" s="96" t="s">
         <v>109</v>
       </c>
-      <c r="D19" s="101"/>
-      <c r="E19" s="103">
+      <c r="D19" s="96"/>
+      <c r="E19" s="93">
         <v>0</v>
       </c>
-      <c r="F19" s="101" t="s">
+      <c r="F19" s="96" t="s">
         <v>159</v>
       </c>
-      <c r="G19" s="104"/>
+      <c r="G19" s="98"/>
     </row>
     <row r="20" spans="1:7">
-      <c r="A20" s="105">
+      <c r="A20" s="99">
         <v>527</v>
       </c>
-      <c r="B20" s="105" t="s">
+      <c r="B20" s="99" t="s">
         <v>160</v>
       </c>
-      <c r="C20" s="105" t="s">
+      <c r="C20" s="99" t="s">
         <v>109</v>
       </c>
-      <c r="D20" s="105"/>
-      <c r="E20" s="105"/>
-      <c r="F20" s="105" t="s">
+      <c r="D20" s="99"/>
+      <c r="E20" s="99"/>
+      <c r="F20" s="99" t="s">
         <v>161</v>
       </c>
     </row>
@@ -5845,12 +5836,12 @@
   <dimension ref="A1:F14"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="8.84166666666667" style="97" customWidth="1"/>
-    <col min="2" max="2" width="30.8666666666667" style="97" customWidth="1"/>
-    <col min="3" max="3" width="12.3333333333333" style="97" customWidth="1"/>
-    <col min="4" max="5" width="18.625" style="97" customWidth="1"/>
-    <col min="6" max="6" width="36.925" style="97" customWidth="1"/>
-    <col min="7" max="16384" width="9" style="97"/>
+    <col min="1" max="1" width="8.84166666666667" style="81" customWidth="1"/>
+    <col min="2" max="2" width="30.8666666666667" style="81" customWidth="1"/>
+    <col min="3" max="3" width="12.3333333333333" style="81" customWidth="1"/>
+    <col min="4" max="5" width="18.625" style="81" customWidth="1"/>
+    <col min="6" max="6" width="36.925" style="81" customWidth="1"/>
+    <col min="7" max="16384" width="9" style="81"/>
   </cols>
   <sheetData>
     <row r="1" ht="19" customHeight="1" spans="1:6">
@@ -5874,218 +5865,218 @@
       </c>
     </row>
     <row r="2" spans="1:6">
-      <c r="A2" s="98">
+      <c r="A2" s="86">
         <v>601</v>
       </c>
-      <c r="B2" s="98" t="s">
+      <c r="B2" s="86" t="s">
         <v>164</v>
       </c>
-      <c r="C2" s="98" t="s">
+      <c r="C2" s="86" t="s">
         <v>129</v>
       </c>
-      <c r="D2" s="98"/>
-      <c r="E2" s="98"/>
-      <c r="F2" s="98" t="s">
+      <c r="D2" s="86"/>
+      <c r="E2" s="86"/>
+      <c r="F2" s="86" t="s">
         <v>165</v>
       </c>
     </row>
     <row r="3" spans="1:6">
-      <c r="A3" s="98">
+      <c r="A3" s="86">
         <v>602</v>
       </c>
-      <c r="B3" s="98" t="s">
+      <c r="B3" s="86" t="s">
         <v>166</v>
       </c>
-      <c r="C3" s="98" t="s">
+      <c r="C3" s="86" t="s">
         <v>167</v>
       </c>
-      <c r="D3" s="98" t="s">
+      <c r="D3" s="86" t="s">
         <v>129</v>
       </c>
-      <c r="E3" s="98"/>
-      <c r="F3" s="98" t="s">
+      <c r="E3" s="86"/>
+      <c r="F3" s="86" t="s">
         <v>168</v>
       </c>
     </row>
     <row r="4" spans="1:6">
-      <c r="A4" s="98">
+      <c r="A4" s="86">
         <v>603</v>
       </c>
-      <c r="B4" s="98" t="s">
+      <c r="B4" s="86" t="s">
         <v>169</v>
       </c>
-      <c r="C4" s="98" t="s">
+      <c r="C4" s="86" t="s">
         <v>167</v>
       </c>
-      <c r="D4" s="98" t="s">
+      <c r="D4" s="86" t="s">
         <v>109</v>
       </c>
-      <c r="E4" s="98"/>
-      <c r="F4" s="98" t="s">
+      <c r="E4" s="86"/>
+      <c r="F4" s="86" t="s">
         <v>170</v>
       </c>
     </row>
     <row r="5" spans="1:6">
-      <c r="A5" s="98">
+      <c r="A5" s="86">
         <v>604</v>
       </c>
-      <c r="B5" s="98" t="s">
+      <c r="B5" s="86" t="s">
         <v>171</v>
       </c>
-      <c r="C5" s="98" t="s">
+      <c r="C5" s="86" t="s">
         <v>109</v>
       </c>
-      <c r="D5" s="98"/>
-      <c r="E5" s="98"/>
-      <c r="F5" s="98" t="s">
+      <c r="D5" s="86"/>
+      <c r="E5" s="86"/>
+      <c r="F5" s="86" t="s">
         <v>172</v>
       </c>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="98">
+      <c r="A6" s="86">
         <v>605</v>
       </c>
-      <c r="B6" s="98" t="s">
+      <c r="B6" s="86" t="s">
         <v>173</v>
       </c>
-      <c r="C6" s="98" t="s">
+      <c r="C6" s="86" t="s">
         <v>174</v>
       </c>
-      <c r="D6" s="98"/>
-      <c r="E6" s="98"/>
-      <c r="F6" s="98" t="s">
+      <c r="D6" s="86"/>
+      <c r="E6" s="86"/>
+      <c r="F6" s="86" t="s">
         <v>175</v>
       </c>
     </row>
     <row r="7" spans="1:6">
-      <c r="A7" s="98">
+      <c r="A7" s="86">
         <v>611</v>
       </c>
-      <c r="B7" s="98" t="s">
+      <c r="B7" s="86" t="s">
         <v>176</v>
       </c>
-      <c r="C7" s="98" t="s">
+      <c r="C7" s="86" t="s">
         <v>129</v>
       </c>
-      <c r="D7" s="98"/>
-      <c r="E7" s="98"/>
-      <c r="F7" s="98" t="s">
+      <c r="D7" s="86"/>
+      <c r="E7" s="86"/>
+      <c r="F7" s="86" t="s">
         <v>177</v>
       </c>
     </row>
     <row r="8" spans="1:6">
-      <c r="A8" s="98">
+      <c r="A8" s="86">
         <v>612</v>
       </c>
-      <c r="B8" s="98" t="s">
+      <c r="B8" s="86" t="s">
         <v>178</v>
       </c>
-      <c r="C8" s="98" t="s">
+      <c r="C8" s="86" t="s">
         <v>167</v>
       </c>
-      <c r="D8" s="98" t="s">
+      <c r="D8" s="86" t="s">
         <v>129</v>
       </c>
-      <c r="E8" s="98"/>
-      <c r="F8" s="98" t="s">
+      <c r="E8" s="86"/>
+      <c r="F8" s="86" t="s">
         <v>179</v>
       </c>
     </row>
     <row r="9" spans="1:6">
-      <c r="A9" s="98">
+      <c r="A9" s="86">
         <v>613</v>
       </c>
-      <c r="B9" s="98" t="s">
+      <c r="B9" s="86" t="s">
         <v>180</v>
       </c>
-      <c r="C9" s="98" t="s">
+      <c r="C9" s="86" t="s">
         <v>167</v>
       </c>
-      <c r="D9" s="98" t="s">
+      <c r="D9" s="86" t="s">
         <v>109</v>
       </c>
-      <c r="E9" s="98"/>
-      <c r="F9" s="98" t="s">
+      <c r="E9" s="86"/>
+      <c r="F9" s="86" t="s">
         <v>181</v>
       </c>
     </row>
     <row r="10" spans="1:6">
-      <c r="A10" s="98">
+      <c r="A10" s="86">
         <v>614</v>
       </c>
-      <c r="B10" s="98" t="s">
+      <c r="B10" s="86" t="s">
         <v>182</v>
       </c>
-      <c r="C10" s="98" t="s">
+      <c r="C10" s="86" t="s">
         <v>109</v>
       </c>
-      <c r="D10" s="98"/>
-      <c r="E10" s="98"/>
-      <c r="F10" s="98" t="s">
+      <c r="D10" s="86"/>
+      <c r="E10" s="86"/>
+      <c r="F10" s="86" t="s">
         <v>183</v>
       </c>
     </row>
     <row r="11" spans="1:6">
-      <c r="A11" s="98">
+      <c r="A11" s="86">
         <v>615</v>
       </c>
-      <c r="B11" s="98" t="s">
+      <c r="B11" s="86" t="s">
         <v>184</v>
       </c>
-      <c r="C11" s="98" t="s">
+      <c r="C11" s="86" t="s">
         <v>174</v>
       </c>
-      <c r="D11" s="98"/>
-      <c r="E11" s="98"/>
-      <c r="F11" s="98" t="s">
+      <c r="D11" s="86"/>
+      <c r="E11" s="86"/>
+      <c r="F11" s="86" t="s">
         <v>185</v>
       </c>
     </row>
     <row r="12" spans="1:6">
-      <c r="A12" s="98">
+      <c r="A12" s="86">
         <v>621</v>
       </c>
-      <c r="B12" s="98" t="s">
+      <c r="B12" s="86" t="s">
         <v>186</v>
       </c>
-      <c r="C12" s="98" t="s">
+      <c r="C12" s="86" t="s">
         <v>129</v>
       </c>
-      <c r="D12" s="98"/>
-      <c r="E12" s="98"/>
-      <c r="F12" s="98" t="s">
+      <c r="D12" s="86"/>
+      <c r="E12" s="86"/>
+      <c r="F12" s="86" t="s">
         <v>187</v>
       </c>
     </row>
     <row r="13" spans="1:6">
-      <c r="A13" s="98">
+      <c r="A13" s="86">
         <v>624</v>
       </c>
-      <c r="B13" s="98" t="s">
+      <c r="B13" s="86" t="s">
         <v>188</v>
       </c>
-      <c r="C13" s="98" t="s">
+      <c r="C13" s="86" t="s">
         <v>109</v>
       </c>
-      <c r="D13" s="98"/>
-      <c r="E13" s="98"/>
-      <c r="F13" s="98" t="s">
+      <c r="D13" s="86"/>
+      <c r="E13" s="86"/>
+      <c r="F13" s="86" t="s">
         <v>189</v>
       </c>
     </row>
     <row r="14" spans="1:6">
-      <c r="A14" s="98">
+      <c r="A14" s="86">
         <v>625</v>
       </c>
-      <c r="B14" s="98" t="s">
+      <c r="B14" s="86" t="s">
         <v>190</v>
       </c>
-      <c r="C14" s="98" t="s">
+      <c r="C14" s="86" t="s">
         <v>174</v>
       </c>
-      <c r="D14" s="98"/>
-      <c r="E14" s="98"/>
-      <c r="F14" s="98" t="s">
+      <c r="D14" s="86"/>
+      <c r="E14" s="86"/>
+      <c r="F14" s="86" t="s">
         <v>191</v>
       </c>
     </row>
@@ -6416,66 +6407,76 @@
       </c>
     </row>
     <row r="18" ht="18.75" spans="1:6">
-      <c r="A18" s="94">
+      <c r="A18" s="92">
         <v>717</v>
       </c>
-      <c r="B18" s="94" t="s">
+      <c r="B18" s="92" t="s">
         <v>231</v>
       </c>
-      <c r="C18" s="94" t="s">
+      <c r="C18" s="92" t="s">
         <v>109</v>
       </c>
-      <c r="D18" s="94"/>
-      <c r="E18" s="95">
+      <c r="D18" s="92"/>
+      <c r="E18" s="93">
         <v>1830</v>
       </c>
-      <c r="F18" s="95" t="s">
+      <c r="F18" s="93" t="s">
         <v>232</v>
       </c>
     </row>
     <row r="19" ht="18.75" spans="1:6">
-      <c r="A19" s="94">
+      <c r="A19" s="92">
         <v>718</v>
       </c>
-      <c r="B19" s="94" t="s">
+      <c r="B19" s="92" t="s">
         <v>233</v>
       </c>
-      <c r="C19" s="94" t="s">
+      <c r="C19" s="92" t="s">
         <v>109</v>
       </c>
-      <c r="D19" s="94"/>
-      <c r="E19" s="95">
+      <c r="D19" s="92"/>
+      <c r="E19" s="93">
         <v>1831</v>
       </c>
-      <c r="F19" s="94" t="s">
+      <c r="F19" s="92" t="s">
         <v>234</v>
       </c>
     </row>
     <row r="20" ht="18.75" spans="1:6">
-      <c r="A20" s="94">
+      <c r="A20" s="92">
         <v>719</v>
       </c>
-      <c r="B20" s="94" t="s">
+      <c r="B20" s="92" t="s">
         <v>235</v>
       </c>
-      <c r="C20" s="94" t="s">
+      <c r="C20" s="92" t="s">
         <v>167</v>
       </c>
-      <c r="D20" s="94" t="s">
+      <c r="D20" s="92" t="s">
         <v>129</v>
       </c>
-      <c r="E20" s="95"/>
-      <c r="F20" s="95" t="s">
+      <c r="E20" s="93"/>
+      <c r="F20" s="93" t="s">
         <v>236</v>
       </c>
     </row>
-    <row r="21" spans="1:6">
-      <c r="A21" s="96"/>
-      <c r="B21" s="96"/>
-      <c r="C21" s="96"/>
-      <c r="D21" s="96"/>
-      <c r="E21" s="96"/>
-      <c r="F21" s="96"/>
+    <row r="21" ht="37.5" spans="1:6">
+      <c r="A21" s="92">
+        <v>720</v>
+      </c>
+      <c r="B21" s="92" t="s">
+        <v>237</v>
+      </c>
+      <c r="C21" s="92" t="s">
+        <v>129</v>
+      </c>
+      <c r="D21" s="92"/>
+      <c r="E21" s="93" t="s">
+        <v>238</v>
+      </c>
+      <c r="F21" s="93" t="s">
+        <v>239</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6500,27 +6501,27 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="89" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="B1" s="89" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="C1" s="89" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="D1" s="89" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="E1" s="89" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
     </row>
     <row r="2" s="81" customFormat="1" spans="1:5">
       <c r="A2" s="86" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="B2" s="86" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="C2" s="90" t="s">
         <v>150</v>
@@ -6529,15 +6530,15 @@
         <v>129</v>
       </c>
       <c r="E2" s="90" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
     </row>
     <row r="3" s="81" customFormat="1" spans="1:5">
       <c r="A3" s="86" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="B3" s="86" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="C3" s="90" t="s">
         <v>136</v>
@@ -6546,7 +6547,7 @@
         <v>129</v>
       </c>
       <c r="E3" s="90" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
     </row>
     <row r="4" s="81" customFormat="1" spans="1:5">
@@ -6556,7 +6557,7 @@
         <v>138</v>
       </c>
       <c r="D4" s="90" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="E4" s="90" t="s">
         <v>139</v>
@@ -6588,13 +6589,13 @@
   <sheetData>
     <row r="1" s="81" customFormat="1" spans="1:3">
       <c r="A1" s="88" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="B1" s="88" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="C1" s="88" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
     </row>
     <row r="2" s="81" customFormat="1" spans="1:3">
@@ -6692,16 +6693,16 @@
   <sheetData>
     <row r="1" s="81" customFormat="1" spans="1:5">
       <c r="A1" s="82" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="B1" s="82" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="C1" s="82" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="D1" s="82" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="E1" s="82" t="s">
         <v>2</v>
@@ -6709,211 +6710,211 @@
     </row>
     <row r="2" s="81" customFormat="1" spans="1:5">
       <c r="A2" s="83" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="B2" s="84" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="C2" s="84">
         <v>1</v>
       </c>
       <c r="D2" s="84" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="E2" s="84" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
     </row>
     <row r="3" s="81" customFormat="1" spans="1:5">
       <c r="A3" s="85" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="B3" s="85" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="C3" s="86">
         <v>1</v>
       </c>
       <c r="D3" s="86" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="E3" s="86" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
     </row>
     <row r="4" s="81" customFormat="1" spans="1:5">
       <c r="A4" s="85" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="B4" s="86" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="C4" s="86">
         <v>2</v>
       </c>
       <c r="D4" s="86" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="E4" s="86" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
     </row>
     <row r="5" s="81" customFormat="1" spans="1:5">
       <c r="A5" s="85" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="B5" s="86" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="C5" s="86">
         <v>20</v>
       </c>
       <c r="D5" s="86" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="E5" s="86" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
     </row>
     <row r="6" s="81" customFormat="1" spans="1:5">
       <c r="A6" s="83" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="B6" s="84" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="C6" s="84">
         <v>1</v>
       </c>
       <c r="D6" s="84" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="E6" s="84" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
     </row>
     <row r="7" s="81" customFormat="1" spans="1:5">
       <c r="A7" s="83" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="B7" s="84" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="C7" s="84">
         <v>80</v>
       </c>
       <c r="D7" s="84" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="E7" s="84" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
     </row>
     <row r="8" s="81" customFormat="1" spans="1:5">
       <c r="A8" s="83" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="B8" s="84" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="C8" s="84">
         <v>80</v>
       </c>
       <c r="D8" s="84" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="E8" s="84" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
     </row>
     <row r="9" s="81" customFormat="1" spans="1:5">
       <c r="A9" s="83" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="B9" s="84" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="C9" s="84">
         <v>4</v>
       </c>
       <c r="D9" s="84" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="E9" s="84" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
     </row>
     <row r="10" s="81" customFormat="1" spans="1:5">
       <c r="A10" s="83" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="B10" s="86" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="C10" s="86">
         <v>2</v>
       </c>
       <c r="D10" s="86" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="E10" s="86" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
     </row>
     <row r="11" s="81" customFormat="1" spans="1:5">
       <c r="A11" s="83" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="B11" s="84" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="C11" s="84">
         <v>2</v>
       </c>
       <c r="D11" s="84" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="E11" s="84" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
     </row>
     <row r="12" s="81" customFormat="1" spans="1:5">
       <c r="A12" s="83" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="B12" s="84" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="C12" s="84">
         <v>80</v>
       </c>
       <c r="D12" s="84" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="E12" s="84" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
     </row>
     <row r="13" s="81" customFormat="1" spans="1:5">
       <c r="A13" s="83" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="B13" s="84" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="C13" s="84">
         <v>2</v>
       </c>
       <c r="D13" s="84" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="E13" s="84" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
     </row>
     <row r="14" s="81" customFormat="1" spans="1:5">
       <c r="A14" s="87" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="B14" s="86"/>
       <c r="C14" s="86"/>
@@ -6922,70 +6923,70 @@
     </row>
     <row r="15" s="81" customFormat="1" spans="1:5">
       <c r="A15" s="85" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="B15" s="86" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="C15" s="86">
         <v>2</v>
       </c>
       <c r="D15" s="86" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="E15" s="86" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
     </row>
     <row r="16" s="81" customFormat="1" spans="1:5">
       <c r="A16" s="85" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="B16" s="86" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="C16" s="86">
         <v>80</v>
       </c>
       <c r="D16" s="86" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="E16" s="86" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
     </row>
     <row r="17" s="81" customFormat="1" ht="12" customHeight="1" spans="1:5">
       <c r="A17" s="83" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="B17" s="84" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="C17" s="84">
         <v>2</v>
       </c>
       <c r="D17" s="84" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="E17" s="84" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
     </row>
     <row r="18" s="81" customFormat="1" spans="1:5">
       <c r="A18" s="85" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="B18" s="84" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="C18" s="84">
         <v>2</v>
       </c>
       <c r="D18" s="84" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="E18" s="84" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
     </row>
   </sheetData>
@@ -7009,13 +7010,13 @@
   <sheetData>
     <row r="1" ht="16.5" spans="1:4">
       <c r="A1" s="5" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
     </row>
     <row r="2" ht="16.5" spans="1:4">
@@ -7023,10 +7024,10 @@
         <v>0</v>
       </c>
       <c r="B2" s="78" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="C2" s="26" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
     </row>
     <row r="3" ht="16.5" spans="1:4">
@@ -7034,13 +7035,13 @@
         <v>1</v>
       </c>
       <c r="B3" s="78" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="C3" s="79" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="D3" s="80" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
     </row>
     <row r="4" ht="16.5" spans="1:4">
@@ -7048,10 +7049,10 @@
         <v>10</v>
       </c>
       <c r="B4" s="78" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="C4" s="26" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="D4" s="80"/>
     </row>
@@ -7060,10 +7061,10 @@
         <v>100</v>
       </c>
       <c r="B5" s="24" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="C5" s="26" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="D5" s="80"/>
     </row>
@@ -7072,10 +7073,10 @@
         <v>200</v>
       </c>
       <c r="B6" s="24" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="C6" s="26" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="D6" s="80"/>
     </row>
